--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -8633,7 +8633,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B111" s="18" t="inlineStr">
@@ -8702,7 +8702,7 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B113" s="18" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B115" s="18" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-006</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -9038,7 +9038,7 @@
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-007</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B117" s="18" t="inlineStr">
@@ -9101,7 +9101,7 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-008</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
@@ -9167,7 +9167,7 @@
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-009</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B119" s="18" t="inlineStr">
@@ -9231,7 +9231,7 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-010</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
@@ -9296,7 +9296,7 @@
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-011</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B121" s="18" t="inlineStr">
@@ -16676,7 +16676,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B112" s="18" t="inlineStr">
@@ -16702,7 +16702,7 @@
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
@@ -16728,7 +16728,7 @@
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B114" s="18" t="inlineStr">
@@ -16754,7 +16754,7 @@
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B115" s="15" t="inlineStr">
@@ -16780,7 +16780,7 @@
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B116" s="18" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-006</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B117" s="15" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-007</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B118" s="18" t="inlineStr">
@@ -16858,7 +16858,7 @@
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-008</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B119" s="15" t="inlineStr">
@@ -16884,7 +16884,7 @@
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-009</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B120" s="18" t="inlineStr">
@@ -16910,7 +16910,7 @@
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>FD-FIN-010</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B121" s="15" t="inlineStr">
@@ -16936,7 +16936,7 @@
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>FD-FIN-011</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B122" s="18" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>FD-FIN-001 (Group B), FD-TMPL-001, FD-EDIT-001</t>
+          <t>FD-DOC-001 (Group B), FD-TMPL-001, FD-EDIT-001</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -1011,10 +1011,9 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>1. The Fees &amp; Discounts feature flag is ON for the organization.
-2. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
-3. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
-4. You are on the work order's Lines tab.</t>
+          <t>1. You are logged in as a role that has Work Orders: Create &amp; Edit and See Financial Data.
+2. An open (not Invoiced, not Paid) work order exists; you are viewing it and are NOT in history mode.
+3. You are on the work order's Lines tab.</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
@@ -1085,7 +1084,7 @@
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with subtotal exactly $10,715.39 (or any known subtotal) is open on the Lines tab.</t>
         </is>
       </c>
@@ -1163,7 +1162,7 @@
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with Work Order Total = $10,715.39 is open.</t>
         </is>
       </c>
@@ -1239,7 +1238,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order is open; the location's template library contains 'Fleet Standard Discount (−10%)'.</t>
         </is>
       </c>
@@ -1315,7 +1314,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order is open with the Add dialog freshly opened (all fields blank).</t>
         </is>
       </c>
@@ -1393,7 +1392,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order whose relevant base for the fee is exactly $100.00 is open.</t>
         </is>
       </c>
@@ -1466,7 +1465,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
@@ -1536,7 +1535,7 @@
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
@@ -1607,7 +1606,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open with Name, Type='Fee', Calc type='Flat amount' set.</t>
         </is>
       </c>
@@ -1677,7 +1676,7 @@
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
@@ -1747,7 +1746,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with Net Labor total $200.00, Net Parts total $100.00, Shop Supplies $0.00 (so Subtotal = $300.00), no other adjustments.</t>
         </is>
       </c>
@@ -1820,7 +1819,7 @@
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. A work order in Invoiced (or Paid) status is open.</t>
         </is>
       </c>
@@ -1891,9 +1890,8 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
-3. An open work order is open.</t>
+          <t>1. Logged in as a role that HAS See Financial Data but does NOT have Work Orders: Create &amp; Edit.
+2. An open work order is open.</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -1961,7 +1959,7 @@
       </c>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is freshly open.</t>
         </is>
       </c>
@@ -2031,7 +2029,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. The whole-WO Add dialog is open.</t>
         </is>
       </c>
@@ -2101,7 +2099,7 @@
       </c>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit and See Financial Data.
 2. An open work order with a labor line, e.g. Line 1 'Service - Perform LOF and inspection', is open on the Lines tab.</t>
         </is>
       </c>
@@ -2173,7 +2171,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line whose gross labor price is exactly $150.00, no existing adjustments on that line.</t>
         </is>
       </c>
@@ -2247,7 +2245,7 @@
       </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with two or more labor lines is open on the Lines tab.</t>
         </is>
       </c>
@@ -2317,7 +2315,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line (any quantity/hours) is open.</t>
         </is>
       </c>
@@ -2388,7 +2386,7 @@
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line that carries a 10% fee adjustment resolving to a non-zero amount.</t>
         </is>
       </c>
@@ -2460,7 +2458,7 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a labor line that carries at least one fee/discount adjustment.</t>
         </is>
       </c>
@@ -2531,9 +2529,8 @@
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role with See Financial Data but WITHOUT Work Order Lines: Create &amp; Edit.
-3. An open work order with a labor line is open.</t>
+          <t>1. Logged in as a role with See Financial Data but WITHOUT Work Order Lines: Create &amp; Edit.
+2. An open work order with a labor line is open.</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -2602,7 +2599,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part, e.g. '(LF3620) Engine Oil Filter', is open on the Lines or Parts tab.</t>
         </is>
       </c>
@@ -2674,7 +2671,7 @@
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 3.</t>
         </is>
       </c>
@@ -2747,7 +2744,7 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a requested (pending / not yet picked) part of quantity 2 at sell price $20.00 each.</t>
         </is>
       </c>
@@ -2820,7 +2817,7 @@
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 3 at sell price $20.00 each (gross part total $60.00).</t>
         </is>
       </c>
@@ -2892,7 +2889,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a requested part that already carries a % of Parts Total discount.</t>
         </is>
       </c>
@@ -2963,7 +2960,7 @@
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part carrying a discount that resolves to a non-zero amount.</t>
         </is>
       </c>
@@ -3035,7 +3032,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part that carries at least one adjustment.</t>
         </is>
       </c>
@@ -3106,7 +3103,7 @@
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of quantity 1.</t>
         </is>
       </c>
@@ -3177,7 +3174,7 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where Line 1 labor carries a 'Line discount' of −5% resolving to −$26.08.</t>
         </is>
       </c>
@@ -3248,7 +3245,7 @@
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where part '(LF3620) Engine Oil Filter' carries a 'Parts Handling Fee' of +$3.75.</t>
         </is>
       </c>
@@ -3319,7 +3316,7 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where the LF3620 part carries three adjustments: Part discount (−10%), Fleet discount (−5%), Parts Handling Fee (+$3.75).</t>
         </is>
       </c>
@@ -3393,7 +3390,7 @@
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order where the LF3620 part has base total $58.47 plus adjustments −$6.49, −$2.92, +$3.75.</t>
         </is>
       </c>
@@ -3464,7 +3461,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with at least one inline line-level adjustment.</t>
         </is>
       </c>
@@ -3535,7 +3532,7 @@
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments across scopes is open.</t>
         </is>
       </c>
@@ -3607,7 +3604,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order (e.g. S2-13274) with a whole-WO discount and line-level part/labor adjustments.</t>
         </is>
       </c>
@@ -3679,7 +3676,7 @@
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with adjustments: Work order discount −$857.23, Part discount −$649.00, Fleet discount −$292.00, Parts Handling Fee +$3.75, Line discount −$260.77.</t>
         </is>
       </c>
@@ -3750,7 +3747,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order to which you add three adjustments in a known order: (a) Adjustment A first, (b) Adjustment B second, (c) Adjustment C third.</t>
         </is>
       </c>
@@ -3820,7 +3817,7 @@
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with zero fee/discount adjustments of any scope.</t>
         </is>
       </c>
@@ -3889,7 +3886,7 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments (any scopes) netting to −$2,055.25.</t>
         </is>
       </c>
@@ -3961,7 +3958,7 @@
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. An open work order with 5 adjustments as in FD-FIN-001.</t>
         </is>
       </c>
@@ -4032,9 +4029,8 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
-3. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.</t>
+          <t>1. Variant (a): logged in with See Financial Data, an open WO with zero adjustments.
+2. Variant (b): logged in as a role WITHOUT See Financial Data, an open WO with adjustments.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -4103,7 +4099,7 @@
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data and Work Orders: Create &amp; Edit.
+          <t>1. Logged in with See Financial Data and Work Orders: Create &amp; Edit.
 2. An open work order with a whole-WO 'Early Payment Discount' of −8% resolving to −$857.23, plus some line-level adjustments.</t>
         </is>
       </c>
@@ -4175,7 +4171,7 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data + Work Orders: Create &amp; Edit.
+          <t>1. Logged in with See Financial Data + Work Orders: Create &amp; Edit.
 2. Variant (a): an open WO with only line-level adjustments and NO whole-WO adjustments.
 3. Variant (b): an open WO with at least one whole-WO adjustment.</t>
         </is>
@@ -4246,7 +4242,7 @@
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. A Parts page / WO parts view is open with part '#37346 Mobil 1 5W20' carrying exactly one adjustment 'Military Discount' −10%.</t>
         </is>
       </c>
@@ -4316,7 +4312,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (first = 'Parts Handling Fee' 2%).</t>
         </is>
       </c>
@@ -4386,7 +4382,7 @@
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data and the relevant change permission.
+          <t>1. Logged in with See Financial Data and the relevant change permission.
 2. Parts page open with part '#28439 Fleetguard FF5421' carrying no adjustments, on an editable sale/WO.</t>
         </is>
       </c>
@@ -4457,7 +4453,7 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open with part '#55073 Mobil 1 5W20' carrying three adjustments (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
@@ -4530,7 +4526,7 @@
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
@@ -4598,7 +4594,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. Parts page open with part #37346 carrying exactly ONE adjustment; the editable breakdown modal is open.</t>
         </is>
       </c>
@@ -4670,7 +4666,7 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with See Financial Data.
+          <t>1. Logged in with See Financial Data.
 2. Parts page open for an Invoiced/Paid (non-editable) sale/WO with a part that has no adjustments.</t>
         </is>
       </c>
@@ -4740,7 +4736,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing whole-WO percentage discount adjustment.</t>
         </is>
       </c>
@@ -4814,7 +4810,7 @@
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing percentage adjustment whose base total has since changed (e.g. a line was added).</t>
         </is>
       </c>
@@ -4888,7 +4884,7 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with the relevant change permission + See Financial Data.
+          <t>1. Logged in with the relevant change permission + See Financial Data.
 2. An open work order with an existing adjustment; a condition that forces a save failure can be simulated (e.g. server error).</t>
         </is>
       </c>
@@ -4959,7 +4955,7 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order with a whole-WO discount named 'Early Payment Discount'.</t>
         </is>
       </c>
@@ -5032,9 +5028,8 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
-3. An open work order with a whole-WO adjustment.</t>
+          <t>1. Logged in as a role that HAS Work Orders: Create &amp; Edit and See Financial Data but does NOT have the separate 'Delete' permission.
+2. An open work order with a whole-WO adjustment.</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
@@ -5105,7 +5100,7 @@
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order where a part carries a 'Fleet discount' adjustment shown inline.</t>
         </is>
       </c>
@@ -5178,7 +5173,7 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Order Lines: Create &amp; Edit + See Financial Data.
 2. An open work order with a part of gross part total exactly $100.00.</t>
         </is>
       </c>
@@ -5253,7 +5248,7 @@
       </c>
       <c r="H61" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit, Work Order Lines: Create &amp; Edit, and See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit, Work Order Lines: Create &amp; Edit, and See Financial Data.
 2. An open work order with Gross Labor $200.00 and Gross Parts $100.00, no shop supplies.
 3. A Labor Line 10% discount already applied (Step 1: −$20.00, so Net Labor = $180.00).</t>
         </is>
@@ -5327,7 +5322,7 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON; logged in with Work Orders: Create &amp; Edit + See Financial Data.
+          <t>1. Logged in with Work Orders: Create &amp; Edit + See Financial Data.
 2. An open work order; the location library has a 'Parts Handling Fee' template.</t>
         </is>
       </c>
@@ -5398,9 +5393,8 @@
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>1. The Fees &amp; Discounts feature flag is ON for the organization.
-2. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
-3. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
+          <t>1. A test customer named ZZAUTOTEST Customer exists with exactly 2 default fees/discounts linked.
+2. You are logged in with Customer Management: Create &amp; Edit and Manage AP/AR permissions.</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -5470,7 +5464,7 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a customer with at least 1 default fee/discount exists.
+          <t>1. A customer with at least 1 default fee/discount exists.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
@@ -5543,7 +5537,7 @@
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
+          <t>1. A location template named "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%) exists and is NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
@@ -5616,7 +5610,7 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; at least 3 templates exist that are NOT yet linked to the test customer.
+          <t>1. At least 3 templates exist that are NOT yet linked to the test customer.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
@@ -5688,7 +5682,7 @@
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
+          <t>1. The location has: (a) a template already linked to this customer, (b) an unlinked Fee/Discount template, and (c) an unlinked Processing Fee template.
 2. You have Customer Management: Create &amp; Edit + Manage AP/AR.</t>
         </is>
       </c>
@@ -5759,7 +5753,7 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; every location template is already linked to the test customer (or the location has no templates).</t>
+          <t>1. Every location template is already linked to the test customer (or the location has no templates).</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
@@ -5823,7 +5817,7 @@
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has at least 1 default fee/discount.</t>
+          <t>1. The customer has at least 1 default fee/discount.</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
@@ -5895,7 +5889,7 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has zero default fees/discounts.</t>
+          <t>1. The customer has zero default fees/discounts.</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
@@ -5960,7 +5954,7 @@
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
+          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount" (Discount, % of Subtotal, 10%, non-taxable).</t>
         </is>
       </c>
       <c r="I71" s="18" t="inlineStr">
@@ -6031,7 +6025,7 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
+          <t>1. The customer has a default "ZZAUTOTEST 10% Fee" (Fee, % of Subtotal, 10%, taxable).</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
@@ -6101,7 +6095,7 @@
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the customer has a default "ZZAUTOTEST Fleet Discount".
+          <t>1. The customer has a default "ZZAUTOTEST Fleet Discount".
 2. An OPEN work order for that customer already carries the auto-added adjustment from this default.</t>
         </is>
       </c>
@@ -6168,7 +6162,7 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
+          <t>1. A template "ZZAUTOTEST Fleet Discount" is a default on the customer AND has been auto-added to an existing OPEN work order.</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
@@ -6239,7 +6233,7 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
+          <t>1. A disposable ZZAUTOTEST customer has at least 1 default fee/discount linked.</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
@@ -6304,7 +6298,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
+          <t>1. The location has exactly 2 templates marked auto-apply and 1 template not auto-apply.</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
@@ -6369,8 +6363,7 @@
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON.
-2. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) with Customer Management: Create &amp; Edit ON but Manage Accounts Payable and Receivable OFF.</t>
         </is>
       </c>
       <c r="I77" s="18" t="inlineStr">
@@ -6440,7 +6433,7 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
+          <t>1. A template "ZZAUTOTEST Env Fee" is marked auto-apply at the location AND is a default on the test customer.</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
@@ -6509,7 +6502,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
+          <t>1. A way to force a server error (e.g., simulate a network/API failure) on the add or remove call.</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr">
@@ -6578,7 +6571,7 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; you have Settings → Finance access.</t>
+          <t>1. You have Settings → Finance access.</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
@@ -6647,7 +6640,7 @@
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has at least 1 template.</t>
+          <t>1. The location has at least 1 template.</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr">
@@ -6713,7 +6706,7 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; you are on Administration → Service → Fees &amp; Discounts.</t>
+          <t>1. You are on Administration → Service → Fees &amp; Discounts.</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
@@ -6786,7 +6779,7 @@
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts page.</t>
+          <t>1. On the admin Fees &amp; Discounts page.</t>
         </is>
       </c>
       <c r="I83" s="18" t="inlineStr">
@@ -6852,7 +6845,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; you can create a template and then a new work order at the same location.</t>
+          <t>1. You can create a template and then a new work order at the same location.</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -6919,7 +6912,7 @@
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Fee template "ZZAUTOTEST Shop Fee" exists.</t>
+          <t>1. A Fee template "ZZAUTOTEST Shop Fee" exists.</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
@@ -6986,7 +6979,7 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template that is NOT a default for any customer exists.</t>
+          <t>1. A template that is NOT a default for any customer exists.</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -7056,7 +7049,7 @@
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template is set as a default for exactly 2 customers.</t>
+          <t>1. A template is set as a default for exactly 2 customers.</t>
         </is>
       </c>
       <c r="I87" s="18" t="inlineStr">
@@ -7120,7 +7113,7 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a template has been applied to an OPEN work order as an adjustment.</t>
+          <t>1. A template has been applied to an OPEN work order as an adjustment.</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
@@ -7185,7 +7178,7 @@
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
+          <t>1. The location has: a "% of Labor Total" template, a "% of Parts Total" template, and a Flat Amount template.
 2. A work order with at least one labor line and one part exists.</t>
         </is>
       </c>
@@ -7259,7 +7252,7 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
@@ -7330,7 +7323,7 @@
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; the location has zero templates.</t>
+          <t>1. The location has zero templates.</t>
         </is>
       </c>
       <c r="I91" s="18" t="inlineStr">
@@ -7394,7 +7387,7 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -7459,7 +7452,7 @@
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = Fee or Discount.</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
@@ -7528,7 +7521,7 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a way to force a save failure on the template create/edit call.</t>
+          <t>1. A way to force a save failure on the template create/edit call.</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -7592,8 +7585,7 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON.
-2. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
+          <t>1. A ZZAUTOTEST role is assigned to Tech (exact-user-match) WITHOUT Settings → Finance.</t>
         </is>
       </c>
       <c r="I95" s="18" t="inlineStr">
@@ -7661,7 +7653,7 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -7726,7 +7718,7 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog.</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog.</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
@@ -7794,7 +7786,7 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
+          <t>1. On the admin Fees &amp; Discounts create dialog with Type = "Processing Fee".</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
@@ -7860,7 +7852,7 @@
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin create dialog with Type = Processing Fee.</t>
+          <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
@@ -7924,7 +7916,7 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; on the admin create dialog with Type = Processing Fee.</t>
+          <t>1. On the admin create dialog with Type = Processing Fee.</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
@@ -7995,7 +7987,7 @@
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template exists.
+          <t>1. A Processing Fee template exists.
 2. An open work order is available.</t>
         </is>
       </c>
@@ -8065,7 +8057,7 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
+          <t>1. A Processing Fee template "ZZAUTOTEST Proc Fee" (Flat Amount $5.00, taxable Yes) is marked auto-apply.</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -8130,7 +8122,7 @@
       </c>
       <c r="H103" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template is set as a default on the test customer.</t>
+          <t>1. A Processing Fee template is set as a default on the test customer.</t>
         </is>
       </c>
       <c r="I103" s="18" t="inlineStr">
@@ -8195,7 +8187,7 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; an open WO carries a Processing Fee (via auto-apply or customer default).</t>
+          <t>1. An open WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -8265,7 +8257,7 @@
       </c>
       <c r="H105" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
+          <t>1. A Processing Fee template "ZZAUTOTEST 3% Proc" (% of Grand Total, 3%, taxable Yes) auto-applies.
 2. A work order exists whose net subtotal (after line-level adjustments) = $300.00 and pre-fee tax = $24.00 (so Grand Total base = $324.00).</t>
         </is>
       </c>
@@ -8336,7 +8328,7 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
+          <t>1. Ability to submit template data (via UI edge case or API) for a Processing Fee carrying a Max Amount, or a method other than Flat Amount / % of Grand Total.</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
@@ -8405,7 +8397,7 @@
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template exists and is on a WO.</t>
+          <t>1. A Processing Fee template exists and is on a WO.</t>
         </is>
       </c>
       <c r="I107" s="18" t="inlineStr">
@@ -8470,7 +8462,7 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
+          <t>1. A Processing Fee template auto-applied to an existing OPEN work order (e.g. Flat $5.00).</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
@@ -8535,7 +8527,7 @@
       </c>
       <c r="H109" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
+          <t>1. Two Processing Fee templates (both % of Grand Total) auto-apply to one work order.
 2. Net subtotal $300.00, pre-fee tax $24.00 → Grand Total base $324.00.</t>
         </is>
       </c>
@@ -8601,7 +8593,7 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
+          <t>1. Ability to submit a Processing Fee with a non-empty minimum amount (no UI control exists; guard for external data).</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
@@ -8668,7 +8660,7 @@
       </c>
       <c r="H111" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
+          <t>1. A work order has whole-WO and line-level adjustments and can produce both an estimate and an invoice.</t>
         </is>
       </c>
       <c r="I111" s="18" t="inlineStr">
@@ -8737,7 +8729,7 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
+          <t>1. A WO has a labor line with a "Shop Supply Fee" (% of Labor Total, fee) and a labor-line discount.</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
@@ -8803,7 +8795,7 @@
       </c>
       <c r="H113" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
+          <t>1. A WO part has a percentage part-line adjustment and another part has a Flat Amount part-line adjustment.</t>
         </is>
       </c>
       <c r="I113" s="18" t="inlineStr">
@@ -8868,7 +8860,7 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has both a fee and a discount adjustment.</t>
+          <t>1. A WO has both a fee and a discount adjustment.</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
@@ -8938,7 +8930,7 @@
       </c>
       <c r="H115" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
+          <t>1. A WO has 3 whole-WO adjustments created in a known order, including a % of Subtotal and a Flat Amount.</t>
         </is>
       </c>
       <c r="I115" s="18" t="inlineStr">
@@ -9004,7 +8996,7 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
+          <t>1. A WO has three separate "Shop Supply Fee" line-level fees (same name+type) across different lines.</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
@@ -9073,7 +9065,7 @@
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO carries a % of Grand Total Processing Fee.</t>
+          <t>1. A WO carries a % of Grand Total Processing Fee.</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
@@ -9136,7 +9128,7 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO whose total shop supplies = $0.00.</t>
+          <t>1. A WO whose total shop supplies = $0.00.</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -9202,7 +9194,7 @@
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
+          <t>1. A WO that currently has $0.00 shop supplies (Shop Supplies hidden on customer views).</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
@@ -9266,7 +9258,7 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO labor line with an adjustment is set to declined/not-billable.</t>
+          <t>1. A WO labor line with an adjustment is set to declined/not-billable.</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -9331,7 +9323,7 @@
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
+          <t>1. A WO with labor, parts, shop supplies (&gt; $0.00), and whole-WO adjustments.</t>
         </is>
       </c>
       <c r="I121" s="18" t="inlineStr">
@@ -9394,7 +9386,7 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; location has an active QuickBooks connection with mapped Fee and Discount items.
+          <t>1. Location has an active QuickBooks connection with mapped Fee and Discount items.
 2. A WO with one fee (+$10.00) and one discount (−$20.00) is invoiced.</t>
         </is>
       </c>
@@ -9465,7 +9457,7 @@
       </c>
       <c r="H123" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with a mapped Fee item and Discount item.
+          <t>1. QuickBooks connected with a mapped Fee item and Discount item.
 2. A WO has a fee named "Hazmat Disposal Fee"; the WO is invoiced.</t>
         </is>
       </c>
@@ -9531,7 +9523,7 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
+          <t>1. QuickBooks connected; a WO has an adjustment that resolves to $0.00 (e.g. target not billable, or $0 base).</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
@@ -9596,7 +9588,7 @@
       </c>
       <c r="H125" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
+          <t>1. QuickBooks connected; the Fee item is NOT mapped in Settings → QuickBooks.
 2. The Discount item IS mapped.
 3. An open WO is available.</t>
         </is>
@@ -9663,7 +9655,7 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
+          <t>1. QuickBooks connected; the Discount item is NOT mapped; the Fee item IS mapped.
 2. An open WO is available.</t>
         </is>
       </c>
@@ -9729,7 +9721,7 @@
       </c>
       <c r="H127" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; Fee item UNMAPPED.</t>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr">
@@ -9796,7 +9788,7 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; Fee item UNMAPPED.</t>
+          <t>1. QuickBooks connected; Fee item UNMAPPED.</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
@@ -9861,7 +9853,7 @@
       </c>
       <c r="H129" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
+          <t>1. Scenario A: QuickBooks connected with Fee item unmapped; scenario B: QuickBooks NOT connected.</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
@@ -9926,7 +9918,7 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
+          <t>1. QuickBooks connected with mapped Fee item; a WO with a fee is ready to invoice/sync.</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
@@ -9993,7 +9985,7 @@
       </c>
       <c r="H131" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
+          <t>1. QuickBooks connected with a location Class set; a WO with fees/discounts is invoiced.</t>
         </is>
       </c>
       <c r="I131" s="18" t="inlineStr">
@@ -10061,7 +10053,7 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
+          <t>1. QuickBooks connected; the location's Class has been deleted/deactivated in QuickBooks.</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
@@ -10125,7 +10117,7 @@
       </c>
       <c r="H133" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
+          <t>1. QuickBooks connected; a WO has $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="I133" s="18" t="inlineStr">
@@ -10195,7 +10187,7 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
+          <t>1. QuickBooks connected; a WO where stacked MULTIPLE discount lines drive the net subtotal below $0.00 (floor applies).</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
@@ -10261,7 +10253,7 @@
       </c>
       <c r="H135" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO where discounts will exceed the net subtotal.</t>
+          <t>1. A WO where discounts will exceed the net subtotal.</t>
         </is>
       </c>
       <c r="I135" s="18" t="inlineStr">
@@ -10326,7 +10318,7 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).</t>
+          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
@@ -10392,7 +10384,7 @@
       </c>
       <c r="H137" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
+          <t>1. QuickBooks connected; a WO has one taxable fee and one non-taxable fee; the WO is invoiced.</t>
         </is>
       </c>
       <c r="I137" s="18" t="inlineStr">
@@ -10456,7 +10448,7 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; you have View History Logs and can add/edit/remove adjustments on an open WO.</t>
+          <t>1. You have View History Logs and can add/edit/remove adjustments on an open WO.</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
@@ -10523,7 +10515,7 @@
       </c>
       <c r="H139" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
+          <t>1. A WO has (a) a whole-WO 10% fee named "Env Fee", (b) a labor-line $5.00 flat fee, (c) a part-line discount.</t>
         </is>
       </c>
       <c r="I139" s="18" t="inlineStr">
@@ -10594,7 +10586,7 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
+          <t>1. A WO has at least one whole-WO adjustment and one line-level adjustment logged.</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
@@ -10658,7 +10650,7 @@
       </c>
       <c r="H141" s="18" t="inlineStr">
         <is>
-          <t>1. A WO already has fee/discount history entries recorded while the flag was ON.
+          <t>1. A WO already has fee/discount history entries.
 2. The Fees &amp; Discounts feature flag is then turned OFF for the org.</t>
         </is>
       </c>
@@ -10728,7 +10720,7 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has fee/discount history entries.
+          <t>1. A WO has fee/discount history entries.
 2. A ZZAUTOTEST role is assigned to Tech with View History Logs ON but See Financial Data OFF (exact-user-match).</t>
         </is>
       </c>
@@ -10799,7 +10791,7 @@
       </c>
       <c r="H143" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has fee/discount history.
+          <t>1. A WO has fee/discount history.
 2. A ZZAUTOTEST role is assigned to Tech WITHOUT View History Logs (exact-user-match).</t>
         </is>
       </c>
@@ -10868,7 +10860,7 @@
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO carries a Processing Fee (via auto-apply or customer default).</t>
+          <t>1. A WO carries a Processing Fee (via auto-apply or customer default).</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
@@ -10938,7 +10930,7 @@
       </c>
       <c r="H145" s="18" t="inlineStr">
         <is>
-          <t>1. Flag ON; a WO has a whole-WO 10% fee.</t>
+          <t>1. A WO has a whole-WO 10% fee.</t>
         </is>
       </c>
       <c r="I145" s="18" t="inlineStr">
@@ -11002,9 +10994,8 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>1. Fees &amp; Discounts feature flag is ON for the organization.
-2. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
-3. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.</t>
+          <t>1. You are signed in with a role that has See Financial Data and Work Orders: Create and Edit.
+2. An open work order (not Invoiced/Paid, not in history mode) exists whose relevant base equals exactly $150.00 (e.g. net labor total = $150.00). Mark any throwaway data ZZAUTOTEST.</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
@@ -11078,9 +11069,8 @@
       </c>
       <c r="H147" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and Work Orders: Create and Edit.
-3. An open work order whose target base equals exactly $33.33.</t>
+          <t>1. Role has See Financial Data and Work Orders: Create and Edit.
+2. An open work order whose target base equals exactly $33.33.</t>
         </is>
       </c>
       <c r="I147" s="18" t="inlineStr">
@@ -11154,9 +11144,8 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data plus the matching change permission.
-3. An open work order with at least one labor line.</t>
+          <t>1. Role has See Financial Data plus the matching change permission.
+2. An open work order with at least one labor line.</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
@@ -11227,9 +11216,8 @@
       </c>
       <c r="H149" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and Work Order Lines: Create and Edit.
-3. An open work order with a part whose quantity = 3.</t>
+          <t>1. Role has See Financial Data and Work Order Lines: Create and Edit.
+2. An open work order with a part whose quantity = 3.</t>
         </is>
       </c>
       <c r="I149" s="18" t="inlineStr">
@@ -11301,9 +11289,8 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order.</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
@@ -11376,9 +11363,8 @@
       </c>
       <c r="H151" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order.</t>
         </is>
       </c>
       <c r="I151" s="18" t="inlineStr">
@@ -11449,9 +11435,8 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order whose target base = $100.00.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order whose target base = $100.00.</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
@@ -11524,10 +11509,9 @@
       </c>
       <c r="H153" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order whose target base = $100.00.
-4. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order whose target base = $100.00.
+3. Note: a $0 Max Amount can normally only come from old data — an entered 0 is treated as empty in the current dialogs (S2-R25).</t>
         </is>
       </c>
       <c r="I153" s="18" t="inlineStr">
@@ -11598,9 +11582,8 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with a target line whose base is $0.00 (e.g. a declined/not-billable labor line, §5-R12).</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
@@ -11671,9 +11654,8 @@
       </c>
       <c r="H155" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order where an earlier discount has already driven a net total to or below $0 for a whole-WO percentage base.</t>
         </is>
       </c>
       <c r="I155" s="18" t="inlineStr">
@@ -11743,9 +11725,8 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order for a taxable customer with a known tax rate and a taxable base.</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
@@ -11817,9 +11798,8 @@
       </c>
       <c r="H157" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data plus both change permissions.
-3. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).</t>
+          <t>1. Role has See Financial Data plus both change permissions.
+2. An open work order with gross labor = $200.00 and gross parts = $100.00 (spec worked example).</t>
         </is>
       </c>
       <c r="I157" s="18" t="inlineStr">
@@ -11891,10 +11871,9 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has Settings → Finance to create the template and See Financial Data to view amounts.
-3. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
-4. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).</t>
+          <t>1. Role has Settings → Finance to create the template and See Financial Data to view amounts.
+2. A Processing Fee template exists: Type = Processing Fee, Calculation type = % of Grand Total, Percent = 3%, marked auto-apply or set as a customer default (a Processing Fee cannot be added to a WO by hand, S8-R16).
+3. An open work order whose net subtotal after line discounts = $300.00 with pre-fee tax = $24.00 (Grand Total base = $324.00).</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
@@ -11965,9 +11944,8 @@
       </c>
       <c r="H159" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has Settings → Finance and See Financial Data.
-3. On the template admin page, open the Processing Fee template create/edit dialog.</t>
+          <t>1. Role has Settings → Finance and See Financial Data.
+2. On the template admin page, open the Processing Fee template create/edit dialog.</t>
         </is>
       </c>
       <c r="I159" s="18" t="inlineStr">
@@ -12040,10 +12018,9 @@
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
-4. Location has an active QuickBooks connection (to verify the credit memo).</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with $100.00 taxable parts and $10.00 tax (spec worked example).
+3. Location has an active QuickBooks connection (to verify the credit memo).</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
@@ -12117,9 +12094,8 @@
       </c>
       <c r="H161" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).</t>
         </is>
       </c>
       <c r="I161" s="18" t="inlineStr">
@@ -12191,10 +12167,9 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Location has an active QuickBooks connection.
-4. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Location has an active QuickBooks connection.
+3. An open work order with a small net subtotal and two or more discount lines whose combined size exceeds it.</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
@@ -12266,9 +12241,8 @@
       </c>
       <c r="H163" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A work order (and a part sale, and a customer) already has adjustments to view.
-3. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
+          <t>1. A work order (and a part sale, and a customer) already has adjustments to view.
+2. Two ZZAUTOTEST custom roles ready: Role A WITH See Financial Data; Role B WITHOUT See Financial Data (otherwise identical). Use exact-user-match when assigning to Tech (Tech /change staff_id 6fb22c1b-…).</t>
         </is>
       </c>
       <c r="I163" s="18" t="inlineStr">
@@ -12340,9 +12314,8 @@
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+          <t>1. An open work order.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Orders: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
@@ -12413,9 +12386,8 @@
       </c>
       <c r="H165" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order with a labor line and a part.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+          <t>1. An open work order with a labor line and a part.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Work Order Lines: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I165" s="18" t="inlineStr">
@@ -12486,9 +12458,8 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open part sale with at least one part.
-3. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+          <t>1. An open part sale with at least one part.
+2. Two ZZAUTOTEST roles, both with See Financial Data ON: Role A WITH Part Sales: Create and Edit; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
@@ -12559,9 +12530,8 @@
       </c>
       <c r="H167" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order.
-3. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
+          <t>1. An open work order.
+2. A ZZAUTOTEST role that HAS Work Orders: Create and Edit (and/or Work Order Lines / Part Sales Create and Edit) but has See Financial Data OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I167" s="18" t="inlineStr">
@@ -12632,9 +12602,8 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. An open work order with an existing whole-WO adjustment.
-3. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
+          <t>1. An open work order with an existing whole-WO adjustment.
+2. A ZZAUTOTEST role with See Financial Data ON and Work Orders: Create and Edit ON, but with the Work Orders "Delete" permission OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
@@ -12705,8 +12674,7 @@
       </c>
       <c r="H169" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
+          <t>1. Two ZZAUTOTEST roles: Role A WITH Settings → Finance; Role B WITHOUT it. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I169" s="18" t="inlineStr">
@@ -12777,9 +12745,8 @@
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A customer exists.
-3. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
+          <t>1. A customer exists.
+2. Three ZZAUTOTEST roles: (A) both permissions ON; (B) Customer Management ON but Manage AP/AR OFF; (C) Manage AP/AR ON but Customer Management OFF. Assign by exact-user-match to Tech.</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
@@ -13001,9 +12968,8 @@
       </c>
       <c r="H173" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. The user has all F&amp;D permissions (so only the WO state should block).
-3. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
+          <t>1. The user has all F&amp;D permissions (so only the WO state should block).
+2. An Invoiced or Paid work order, and separately a way to enter history mode.</t>
         </is>
       </c>
       <c r="I173" s="18" t="inlineStr">
@@ -13148,7 +13114,7 @@
       </c>
       <c r="H175" s="18" t="inlineStr">
         <is>
-          <t>1. A work order already has fee/discount history entries created while the flag was ON.
+          <t>1. A work order already has fee/discount history entries.
 2. The user has View History Logs.
 3. Ability to set the FeesAndDiscounts flag OFF.</t>
         </is>
@@ -13220,9 +13186,8 @@
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON for the org.
-2. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
-3. An open work order.</t>
+          <t>1. Two ZZAUTOTEST roles: one with the F&amp;D-relevant permissions, one without.
+2. An open work order.</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
@@ -13293,9 +13258,8 @@
       </c>
       <c r="H177" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. An open work order; open the Add Fee / Discount dialog.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. An open work order; open the Add Fee / Discount dialog.</t>
         </is>
       </c>
       <c r="I177" s="18" t="inlineStr">
@@ -13368,9 +13332,8 @@
       </c>
       <c r="H178" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Name and Type and Calculation type filled.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Name and Type and Calculation type filled.</t>
         </is>
       </c>
       <c r="I178" s="15" t="inlineStr">
@@ -13441,9 +13404,8 @@
       </c>
       <c r="H179" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Type, Calculation type, and a valid Amount filled.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Type, Calculation type, and a valid Amount filled.</t>
         </is>
       </c>
       <c r="I179" s="18" t="inlineStr">
@@ -13514,9 +13476,8 @@
       </c>
       <c r="H180" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open.</t>
         </is>
       </c>
       <c r="I180" s="15" t="inlineStr">
@@ -13588,9 +13549,8 @@
       </c>
       <c r="H181" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open with Name, Type, Calculation type set.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open with Name, Type, Calculation type set.</t>
         </is>
       </c>
       <c r="I181" s="18" t="inlineStr">
@@ -13659,9 +13619,8 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. Role has See Financial Data and the matching change permission.
-3. Add dialog open.</t>
+          <t>1. Role has See Financial Data and the matching change permission.
+2. Add dialog open.</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
@@ -13732,9 +13691,8 @@
       </c>
       <c r="H183" s="18" t="inlineStr">
         <is>
-          <t>1. Feature flag ON.
-2. A template at the location is marked auto-apply (S7-R5).
-3. The SAME template is also set as a default for a customer (S9-R2).</t>
+          <t>1. A template at the location is marked auto-apply (S7-R5).
+2. The SAME template is also set as a default for a customer (S9-R2).</t>
         </is>
       </c>
       <c r="I183" s="18" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -563,7 +563,7 @@
           <t>Fees &amp; Discounts V1 - Manual Test Cases
 This workbook contains 182 manual test cases covering the ShopView "Fees &amp; Discounts" V1 feature: whole-work-order, labor-line and part-line fees/discounts; inline and statistics display; the Financial Info and sidebar cards; the Parts page column and breakdown modal; edit/remove/stacking flows; customer-level defaults; template administration; the Processing Fee; estimate/invoice (finance) rendering; QuickBooks sync; the history log; the calculation contract; permissions (Story 13); feature-flag gating; and validation/edge cases.
 The cases were authored from the complete written spec plus the design mockups (see build/fees-discounts/requirements.md and design-notes.md).
-VIU (Verify-in-UI on staging) is PENDING: the feature is not yet deployed on staging. The feature flag is ON, but the backend and UI have not shipped (expected in roughly two weeks). Because of this, EVERY case is marked "VIU pending" - the cases are written to the spec and must be re-verified against the live app once it is deployed. See the "VIU (pending)" tab.
+VIU (Verify-in-UI): a deep VIU pass ran 2026-07-08 on the qb QA env (qb.qa.shopview.com / sv7387api). 62 of 182 cases are VIU-Verified (built surfaces: the full §5 calculation contract - math matches EXACTLY - plus whole-WO / labor / part adjustments, validation, history log, template CRUD, customer-default endpoints, and partial permissions). 120 stay VIU-Pending: not-built surfaces (Processing Fee/Story 8, Part Sales/Story 11, QuickBooks/Story 6, customer documents/Story 5-14) and cases needing per-role logins or a flag-off org. See build/fees-discounts/viu-findings.md and bugs-log.md; per-case verdicts are in the VIU Status column here.
 Where the design mockups and the written spec disagree, or where the current build is known to differ, the case Notes flag it and the item is consolidated on the "Open Questions" tab - review that tab before execution.</t>
         </is>
       </c>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L2" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png)</t>
         </is>
       </c>
       <c r="M2" s="15" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="L3" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon)</t>
         </is>
       </c>
       <c r="M3" s="18" t="inlineStr">
@@ -1181,7 +1181,7 @@
 2. Preview row label flips to 'Discount' and shows −$857.23 (8% × 10,715.39 = 857.2312, rounded to nearest cent = 857.23; §5-R3).
 3. Preview row 'New Work Order Total' shows $9,858.16.
 4. The bottom of the preview reads 'Tax is recalculated on save.' (S2-R35).
-5. The discount amount is signed and colored (see FD-WO-015 for the exact color, which differs spec vs design).</t>
+5. The discount amount is signed and colored (the exact color differs between spec and design).</t>
         </is>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="L4" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png)</t>
         </is>
       </c>
       <c r="M4" s="15" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="L7" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50)</t>
         </is>
       </c>
       <c r="M7" s="18" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount)</t>
         </is>
       </c>
       <c r="M8" s="15" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required"</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap)</t>
         </is>
       </c>
       <c r="M11" s="18" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63)</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b)</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png)</t>
         </is>
       </c>
       <c r="M15" s="18" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total"</t>
         </is>
       </c>
       <c r="M17" s="18" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: each labor line row exposes its own 3-dot menu with Add Fee/Discount</t>
         </is>
       </c>
       <c r="M19" s="18" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity)</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="L21" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M21" s="18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M23" s="18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item)</t>
         </is>
       </c>
       <c r="M25" s="18" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27</t>
         </is>
       </c>
       <c r="M27" s="18" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M31" s="18" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M33" s="18" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L35" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M35" s="18" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="L37" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2</t>
         </is>
       </c>
       <c r="M37" s="18" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="L39" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M39" s="18" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M41" s="18" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png)</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
@@ -3959,7 +3959,7 @@
       <c r="H43" s="18" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. An open work order with 5 adjustments as in FD-FIN-001.</t>
+2. An open work order with 5 adjustments of mixed scope.</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M43" s="18" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="L45" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png)</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="L47" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M47" s="18" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="L49" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M49" s="18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
@@ -4527,7 +4527,7 @@
       <c r="H51" s="18" t="inlineStr">
         <is>
           <t>1. Logged in with See Financial Data.
-2. The #55073 breakdown modal from FD-PCOL-004 is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
+2. The #55073 breakdown modal is open (Parts Handling Fee +$1.43, Military Discount −$3.31, Early Payment Discount −$0.99).</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L51" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M51" s="18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M53" s="18" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="L55" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: change re-resolves against current totals; history logs "adjustment.updated"</t>
         </is>
       </c>
       <c r="M55" s="18" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="L57" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed"</t>
         </is>
       </c>
       <c r="M57" s="18" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L59" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M59" s="18" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="L61" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: whole-WO % adjustments resolve on Step-1 net totals (net labor $674.77 used by whole-WO pct_labor)</t>
         </is>
       </c>
       <c r="M61" s="18" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="L63" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: customer "Fees &amp; Discounts (N)" tab with count</t>
         </is>
       </c>
       <c r="M63" s="18" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: "Default Fees &amp; Discounts" card, exact S9-R14 caption, columns Name·Type·Calc·Amount·Max·Taxable</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="L65" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: POST /customers/{id}/default-adjustments {templateIds:[id]} → 201 adds default (GET confirms)</t>
         </is>
       </c>
       <c r="M65" s="18" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: default POST accepts templateIds array (multi-select add); plural toast per S9-R23b (recon UI)</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="L67" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M67" s="18" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr"/>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L69" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: DELETE /customers/{id}/default-adjustments/{id} → 204, no confirm (S9-R24)</t>
         </is>
       </c>
       <c r="M69" s="18" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: empty-state "No fees or discounts yet. Use 'Add Fee/Discount' to add one."</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr"/>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="L71" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M71" s="18" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="L73" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M73" s="18" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="L75" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M75" s="18" t="inlineStr"/>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="L77" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — SPA route guard requires customersCreateAndEdit + seeApArData (tab hidden otherwise)</t>
         </is>
       </c>
       <c r="M77" s="18" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — double-add: setup confirmed (customer default that is also auto-apply exists) and recon observed ×2; not re-verified this pass (WO create via API/UI not completed). See bugs-log BUG-FD-1</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="L79" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M79" s="18" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation)</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="L81" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action</t>
         </is>
       </c>
       <c r="M81" s="18" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="L83" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon)</t>
         </is>
       </c>
       <c r="M83" s="18" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="L85" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates/{id}/change → 200 (edit); "updated" toast (recon)</t>
         </is>
       </c>
       <c r="M85" s="18" t="inlineStr"/>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="L87" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: GET adjustment-templates/{id}/delete-precondition → {affectedCustomerCount} drives S7-R21 warning</t>
         </is>
       </c>
       <c r="M87" s="18" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr"/>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="L89" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M89" s="18" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: template create accepts maxCap for percentage; 0 treated empty (§5-R6)</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L91" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M91" s="18" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="L93" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — Recon: Fee/Discount template offers Flat Amount / % of Labor / % of Parts / % of Subtotal, no scope field</t>
         </is>
       </c>
       <c r="M93" s="18" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="L95" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated)</t>
         </is>
       </c>
       <c r="M95" s="18" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="L97" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M97" s="18" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr"/>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="L99" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M99" s="18" t="inlineStr"/>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="L101" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M101" s="18" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr"/>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="L103" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M103" s="18" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="L105" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M105" s="18" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="L107" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M107" s="18" t="inlineStr"/>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="L109" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M109" s="18" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L111" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M111" s="18" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="L113" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M113" s="18" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="L115" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M115" s="18" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="L117" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M117" s="18" t="inlineStr"/>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr"/>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="L119" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M119" s="18" t="inlineStr"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="L121" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
         </is>
       </c>
       <c r="M121" s="18" t="inlineStr"/>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="L123" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M123" s="18" t="inlineStr"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr"/>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="L125" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M125" s="18" t="inlineStr"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="L127" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M127" s="18" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="L129" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M129" s="18" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr"/>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="L131" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M131" s="18" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr"/>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="L133" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M133" s="18" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr"/>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="L135" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M135" s="18" t="inlineStr"/>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>1. QuickBooks connected; a WO where the floor applied (from FD-QB-012, $50.00 excess).</t>
+          <t>1. QuickBooks connected; a WO where the floor applied (with a $50.00 excess carried as credit).</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr"/>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="L137" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
         </is>
       </c>
       <c r="M137" s="18" t="inlineStr"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: add/edit/remove each log one distinct event (adjustment.added/updated/removed)</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="L139" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: detail carries adjustmentName, adjustmentKind, adjustmentSetRate (set rate not resolved), adjustmentAppliedTo="Full invoice"</t>
         </is>
       </c>
       <c r="M139" s="18" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: adjustment entries have lineId=null (Line column "−"); no saved-state icon</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="L141" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M141" s="18" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="L143" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M143" s="18" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="L145" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: edit to amount 8 logs adjustment.updated with adjustmentSetRate=8 (new set rate)</t>
         </is>
       </c>
       <c r="M145" s="18" t="inlineStr"/>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json)</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="L147" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63</t>
         </is>
       </c>
       <c r="M147" s="18" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty)</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="L149" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14)</t>
         </is>
       </c>
       <c r="M149" s="18" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero"</t>
         </is>
       </c>
       <c r="M151" s="18" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="L153" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product</t>
         </is>
       </c>
       <c r="M153" s="18" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M155" s="18" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged</t>
         </is>
       </c>
       <c r="M156" s="15" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="L157" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: 3-step order — labor-line 10% disc → net labor $674.77; whole-WO 5% pct_labor = $33.74 (on NET not gross $37.49)</t>
         </is>
       </c>
       <c r="M157" s="18" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="L159" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
         </is>
       </c>
       <c r="M159" s="18" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
@@ -12095,7 +12095,7 @@
       <c r="H161" s="18" t="inlineStr">
         <is>
           <t>1. Role has See Financial Data and the matching change permission.
-2. An open work order with $100.00 taxable parts and $10.00 tax (same base as FD-CALC-015).</t>
+2. An open work order with $100.00 taxable parts and $10.00 tax.</t>
         </is>
       </c>
       <c r="I161" s="18" t="inlineStr">
@@ -12110,7 +12110,7 @@
           <t>1. A taxable $150.00 discount lowers the taxable amount to $0.00.
 2. Tax = $0.00 (S6-R10c).
 3. Customer pays $0.00 total.
-4. Contrast with FD-CALC-015 (non-taxable) where the $10.00 tax is still owed.</t>
+4. By contrast, when the same discount is non-taxable the $10.00 tax is still owed.</t>
         </is>
       </c>
       <c r="K161" s="18" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
       <c r="M161" s="18" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L162" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
       <c r="M162" s="15" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M163" s="18" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="L164" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3</t>
         </is>
       </c>
       <c r="M164" s="15" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="L165" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M165" s="18" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
@@ -12545,7 +12545,7 @@
         <is>
           <t>1. Even with the change permission ON, add/edit/remove is NOT reachable while See Financial Data is OFF (S13-R6).
 2. The controls sit on screens that are hidden when SFD is off, so there is no way to add/edit/remove.
-3. Dollar amounts are also hidden (per FD-PERM-001).</t>
+3. Dollar amounts are also hidden.</t>
         </is>
       </c>
       <c r="K167" s="18" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="L167" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M167" s="18" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="L168" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M168" s="15" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="L169" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced)</t>
         </is>
       </c>
       <c r="M169" s="18" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — SPA route guard: /customers/{id}/default-adjustments requiredPermissions ["customersCreateAndEdit","seeApArData"] (S13-R9)</t>
         </is>
       </c>
       <c r="M170" s="15" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="L171" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M171" s="18" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="L172" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M172" s="15" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="L173" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order"</t>
         </is>
       </c>
       <c r="M173" s="18" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="L174" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M174" s="15" t="inlineStr">
@@ -13129,7 +13129,7 @@
       <c r="J175" s="18" t="inlineStr">
         <is>
           <t>1. Fee/discount history entries REMAIN visible in the WO history log even with the flag off (S10-R1) — the documented exception to "flag off hides everything."
-2. All other F&amp;D UI is still hidden (per FD-FLAG-001).</t>
+2. All other F&amp;D UI is still hidden.</t>
         </is>
       </c>
       <c r="K175" s="18" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="L175" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M175" s="18" t="inlineStr">
@@ -13201,7 +13201,7 @@
         <is>
           <t>1. Flag ON alone is not sufficient — without the permission, amounts are hidden and controls are unreachable.
 2. Once the permission is granted, the controls appear and the action works.
-3. Confirms the flag and permission are two independent, both-required gates (cross-reference FD-PERM-010).</t>
+3. Confirms the flag and permission are two independent, both-required gates.</t>
         </is>
       </c>
       <c r="K176" s="15" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="L176" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M176" s="15" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
         </is>
       </c>
       <c r="M177" s="18" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="L178" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
         </is>
       </c>
       <c r="M178" s="15" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="L179" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer"</t>
         </is>
       </c>
       <c r="M179" s="18" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="L180" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted</t>
         </is>
       </c>
       <c r="M180" s="15" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="L181" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero"</t>
         </is>
       </c>
       <c r="M181" s="18" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="L182" s="15" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage</t>
         </is>
       </c>
       <c r="M182" s="15" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="L183" s="18" t="inlineStr">
         <is>
-          <t>Pending — verify on staging once deployed</t>
+          <t>VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1</t>
         </is>
       </c>
       <c r="M183" s="18" t="inlineStr">
@@ -13751,7 +13751,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>VIU PENDING - Fees &amp; Discounts not yet deployed on staging. Fill this tab once the feature is live (see build/fees-discounts/RESUME-STRATEGY.md).</t>
+          <t>VIU worksheet - deep VIU pass ran 2026-07-08 on qb QA env: 62/182 VIU-Verified, 120 VIU-Pending. Per-case verdicts + evidence are in the VIU Status column of the Test Cases tab; details in viu-findings.md. Use this tab to record any further re-verification (not-built surfaces + per-role/flag-off cases remain).</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -1037,12 +1037,12 @@
       </c>
       <c r="L2" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison.</t>
+          <t>Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison. | VIU qb batch-1 (2026-07-08): Dialog opens from WO toolbar 3-dot menu at whole-WO scope, no 'Applying to' subtitle (S2-R12 ok). DEVIATIONS: menu item reads 'Add Fee/Discount' (spec 'Add Work Order Fee / Discount'); add-dialog title reads 'Add new fee/discount' (spec 'New Fee / Discount'; the EDIT dialog title 'Edit Fee / Discount' DOES match). Shots s8-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png)</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="L3" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M3" s="18" t="inlineStr">
         <is>
-          <t>Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag.</t>
+          <t>Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag. | VIU qb batch-1 (2026-07-08): Flat $12 fee added via dialog; confirm button 'Add Fee'; success toast 'Fee added' (exact, auto-fades); entry appears on the WO F&amp;D card; API POST work-orders/adjustments/add 201. Shots s9-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon)</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="L4" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math.</t>
+          <t>Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math. | VIU qb batch-1 (2026-07-08): Live preview verified numerically on subtotal $292.83: 25% fee -&gt; 'Fee · 25% +$73.21' (rounding ok), 150% discount -&gt; '-$439.25 / New work-order subtotal $0.00' (preview floors at $0). Preview updates as you type; 'Tax is recalculated on save.' present. Shots s8-07/08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png)</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t>Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2).</t>
+          <t>Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2). | VIU qb batch-1 (2026-07-08): 'Apply From Template' filled Name/Type/Calc/Amount from template 'Flat fee' ($12 flat) and preview updated; saved copy is independent (appliedBy=manual, templateId recorded). Shot s9-01.</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08): the Add dialog "Add Fee" button is NOT disabled on an empty form (evidence b2-05); the build validates on submit with an inline error ("Amount must be greater than 0", batch-1) rather than a disabled button. Spec/design §6 expects a disabled button. Confirm intended behavior — do not rewrite.</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button.</t>
+          <t>The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button. | VIU qb batch-1 (2026-07-08): Add button is NEVER disabled. Build validates on save: inline errors ('Name is a required field', 'Percent must be greater than 0') and error toast for &gt;100% discount; dialog stays open. Design's disabled-until-valid rule not implemented. Shot s8-10.</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="L7" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M7" s="18" t="inlineStr">
         <is>
-          <t>Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25).</t>
+          <t>Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25). | VIU qb batch-1 (2026-07-08): Max cap verified: API 10% of $324.60 -&gt; capped to $5 (maxCap 5); customer-default 10%/max-15 discount resolved -$15.00 (raw $29.28). 'Max Amount (Optional)' field shows for % methods only. Flat+maxCap rejected: 'A flat adjustment cannot have a maximum cap.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50)</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup.</t>
+          <t>Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup. | VIU qb batch-1 (2026-07-08): Confirm button flips live with Type: 'Add Fee' &lt;-&gt; 'Add Discount'. Shot s8-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount)</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design).</t>
+          <t>Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design). | VIU qb batch-1 (2026-07-08): Empty Name blocks save; inline 'Name is a required field'; nothing persisted. Shot s8-10. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required"</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1).</t>
+          <t>Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1). | VIU qb batch-1 (2026-07-08): 0/empty amount blocks: inline 'Percent must be greater than 0' / 'Amount must be greater than 0'; API rejects 0 and negative with 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging.</t>
+          <t>The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging. | VIU qb batch-1 (2026-07-08): Discount 150% save blocked with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API: 100%=201, 100.01%=400). Fee 150% accepted (resolved $486.90). Note: block is a save-time toast, not inline. Shots s8-08/09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap)</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere.</t>
+          <t>Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere. | VIU qb batch-1 (2026-07-08): % of Subtotal base = net labor + net parts + shop supplies: 25% x $292.83 (265 labor + 27.83 SS) = $73.21 in preview; API resolved values match. Base also includes line-level adjustment effects (net), verified: after +$31.77 line-level fees, 100% subtotal discount resolved -$324.60. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63)</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3).</t>
+          <t>Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3). | VIU qb batch-1 (2026-07-08): Paid WO S3-15889: toolbar menu = 'Audit Log | Timesheets' only (Add Fee/Discount hidden); API add on invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' Shot s14-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b)</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify.</t>
+          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3).</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M15" s="18" t="inlineStr">
         <is>
-          <t>Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated.</t>
+          <t>Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated. | VIU qb batch-1 (2026-07-08): Empty-amount preview reads exactly 'Enter an amount to see the impact.' Shot s8-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png)</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging.</t>
+          <t>Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging. | VIU qb batch-1 (2026-07-08): Preview row signed+colored: fee 'Fee · 25% +$66.25' GREEN rgb(33,186,69) (computed style); discount 'Discount · 150% -$439.25' RED (shot s8-08). Only place green/red used, consistent with S12-R2.</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total"</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'.</t>
+          <t>Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'. | VIU qb batch-1 (2026-07-08): Line 3-dot menu 'Add Fee/Discount' opens dialog locked to Labor Line with grey subtitle 'Applying to: (L) CVIP - Light Duty Truck - Wheels On'. DEVIATION: subtitle omits the spec 'Line {N} Labor —' prefix (S2-R10). Calc locked to labor methods. Shots s12-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total"</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1).</t>
+          <t>Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1). | VIU qb batch-1 (2026-07-08): % of Labor Total resolves on the line's gross labor price: API 10% of $265 = $26.50; UI preview 25% -&gt; 'Line labor total $265.00 / Fee · 25% +$66.25 / New line labor total $331.25' (exact S2-R36a labels). Shot s12-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: each labor line row exposes its own 3-dot menu with Add Fee/Discount</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note).</t>
+          <t>'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note). | VIU qb batch-1 (2026-07-08): Line row exposes its own menu (revealed on row hover, opens with Request part | Add line note | Add Fee/Discount | Save as canned line | Story history | Audit log | Add inspection | Edit labor). Single-line WO verified. Shot s12-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: each labor line row exposes its own 3-dot menu with Add Fee/Discount</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002).</t>
+          <t>Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002). | VIU qb batch-1 (2026-07-08): Labor-line Flat $5 resolved exactly $5.00 (no quantity multiplier), API-verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity)</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="L21" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>Line-level adjustments show wherever their target shows, including a Needs Approval estimate (§5-R12).</t>
+          <t>Line-level adjustments show wherever their target shows, including a Needs Approval estimate (§5-R12). | VIU qb batch-1 (2026-07-08): Line status -&gt; authorization_declined: both line adjustments resolved to $0; restore to authorized -&gt; $66.25 / -$5 again. §5-R12 verified end-to-end via API.</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: labor-line adjustment added, line deleted → the line AND its adjustment are removed (S3-R2)</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete).</t>
+          <t>Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete). | VIU qb batch-1 (2026-07-08): work-orders/lines/delete removed the line AND both adjustments pointing to it; WO summary recomputed (S3-R2).</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — FE-gate confirmed via 11-role matrix: roles without workOrderLinesCreateAndEdit (Time Clock, Sales Rep, Parts Tech, Office User) do not get the labor-line "Add Fee/Discount" starting place (S13-R4/N2). BE is not enforced (consistent with BUG-FD-3 model)</t>
         </is>
       </c>
       <c r="M23" s="18" t="inlineStr">
         <is>
-          <t>Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3).</t>
+          <t>Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3). | VIU qb batch-1 (2026-07-08): No second-user login on qb env; WO-Lines-C&amp;E gating not exercisable this batch.</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'.</t>
+          <t>Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'. | VIU qb batch-1 (2026-07-08): Not driven in batch 1 — no part staged on the throwaway WO (part-request seeding flow not automated yet). API scope 'part_line' exists. Batch-2: seed a part request, drive the part-row menu. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M25" s="18" t="inlineStr">
         <is>
-          <t>Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00).</t>
+          <t>Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00). | VIU qb batch-1 (2026-07-08): Per-item flat (amount x qty) not verified — needs a real part target with qty&gt;1. Batch-2. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item)</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence.</t>
+          <t>The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence. | VIU qb batch-1 (2026-07-08): Requested-part adjustment not driven (no part seeded). Batch-2.</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>Part Line percentage base uses the target's gross part total (before whole-WO nets).</t>
+          <t>Part Line percentage base uses the target's gross part total (before whole-WO nets). | VIU qb batch-1 (2026-07-08): Not driven; % of Parts Total preview at whole-WO scope showed 'Base · Parts total $0.00 -&gt; +$0.00' ($0-base rule ok). Real part-line base check pending. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27</t>
         </is>
       </c>
     </row>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Companion to FD-PART-003 (adding to a requested part).</t>
+          <t>Companion to FD-PART-003 (adding to a requested part). | VIU qb batch-1 (2026-07-08): Requested-&gt;received attachment not driven. Batch-2.</t>
         </is>
       </c>
     </row>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>A part is billable when authorized, not declined, and still has quantity left (§5-R12).</t>
+          <t>A part is billable when authorized, not declined, and still has quantity left (§5-R12). | VIU qb batch-1 (2026-07-08): Declined/returned-part $0 resolve not driven (labor-line analogue verified). Batch-2.</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>Same delete-cascade behavior as labor lines (FD-LABOR-006).</t>
+          <t>Same delete-cascade behavior as labor lines (FD-LABOR-006). | VIU qb batch-1 (2026-07-08): Part deletion cascade not driven (line-delete cascade verified for labor). Batch-2.</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: flat $5 discount on a qty-1 part → −$5.00 (= base amount, per-item §5-R14)</t>
         </is>
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>Confirms quantity changes re-resolve a Part Line Flat Amount adjustment (§5-R14).</t>
+          <t>Confirms quantity changes re-resolve a Part Line Flat Amount adjustment (§5-R14). | VIU qb batch-1 (2026-07-08): Qty-1 per-item edge pending with FD-PART-002.</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: labor-line adjustments show inline under the line with ↳ arrow, name, signed resolved grey (+$3.00 / +$74.98) and a 3-dot menu (evidence b2-05) S3-R12/R14/S12-R3</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2).</t>
+          <t>Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2). | VIU qb batch-1 (2026-07-08): Labor adjustment renders inside the line as 'Fees/Discounts  ↳ ZZAUTOTEST line fee  (+25%)' pill badge + right-side grey signed '+$66.25' + per-row ⋮. Shot s13-01.</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: part-line adjustment shows inline under its part with ↳ arrow, name, signed resolved grey (−$10.00) (b2-05) S3-R13/R14</t>
         </is>
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4).</t>
+          <t>Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4). | VIU qb batch-1 (2026-07-08): Part-line inline row pending (no part seeded). Batch-2.</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08): with 2 labor-line adjustments on one line, BOTH rows are shown inline and NO "Show N more"/"Show less" toggle was observed (b2-05). Spec S3-R15/R16 expects only the first + a toggle. Confirm intended.</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Same collapse/expand behavior applies to a labor line with 2+ adjustments.</t>
+          <t>Same collapse/expand behavior applies to a labor line with 2+ adjustments. | VIU qb batch-1 (2026-07-08): With 2 adjustments on the line BOTH rows show; NO 'Show N more'/'Show less' toggle exists (S3-R15/R16 not implemented). Shot s13-01.</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="L35" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: the per-line Total column shows the line's gross total plus its own adjustment amounts (b2-05) S3-R18/R19</t>
         </is>
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging.</t>
+          <t>Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging. | VIU qb batch-1 (2026-07-08): Line Total column shows $265 gross only — does NOT add the line's own adjustment amounts (+66.25/-5) (S3-R18). Same on the estimate doc ('Line Total $265.00'). Shot s13-01/s14b.</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: each inline adjustment row shows a 3-dot Edit/Delete menu on an open WO (b2-05) S3-R17/S12-R5</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>Design uses 'Edit/Delete' wording inline; spec says removal uses the Create &amp; Edit permission (not the Delete permission) despite the 'Delete' label (design↔spec wording note #7).</t>
+          <t>Design uses 'Edit/Delete' wording inline; spec says removal uses the Create &amp; Edit permission (not the Delete permission) despite the 'Delete' label (design↔spec wording note #7). | VIU qb batch-1 (2026-07-08): Per-row ⋮ control IS present on each inline adjustment row (shot s13-01) but its menu items could not be opened programmatically this batch — Edit/Remove content unconfirmed (card-entry menus show Edit|Remove).</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
       </c>
       <c r="L37" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging.</t>
+          <t>Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging. | VIU qb batch-1 (2026-07-08): Stats F&amp;D section is an AGGREGATE: 'Fees (3) $227.90 / Discounts (0) $0.00 / Net $227.90' — NOT the spec per-adjustment table with % and Amount columns (S4-R2/R3). Shot s11b-03. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08, = BUG-FD-2): Stats F&amp;D section shows AGGREGATE rows (Fees (3) $87.98 / Discounts (2) −$74.14 / Net $13.84), NOT per-adjustment rows with scope hyperlink (b2-04). S4-R2/R3 per-row layout not built.</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging.</t>
+          <t>Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows exist in the aggregate layout, so no scope hyperlink per row (design §3 not built).</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="L39" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: Stats F&amp;D Net = signed sum of resolved amounts (Fees $87.98 − Discounts $74.14 = Net $13.84) (b2-04) S4-R6</t>
         </is>
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>The design mockup's Stats total placeholder (−$1,198.02) disagrees with its Financial Info total (−$2,055.25) for the same '(5)' set — treat as mock placeholder inconsistency (design §3 warning). Expected here uses the correct signed sum −$2,055.25.</t>
+          <t>The design mockup's Stats total placeholder (−$1,198.02) disagrees with its Financial Info total (−$2,055.25) for the same '(5)' set — treat as mock placeholder inconsistency (design §3 warning). Expected here uses the correct signed sum −$2,055.25. | VIU qb batch-1 (2026-07-08): Aggregate 'Net' equals the signed sum (227.90 = 200+12+15.90-0) but the spec'd per-row Total-with-columns layout is absent.</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08, = BUG-FD-2): Stats shows aggregate totals only, so per-adjustment creation-order rows cannot be verified (b2-04). Depends on the per-row layout (not built).</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging.</t>
+          <t>The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows -&gt; creation-order rule not applicable in current build.</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>Mirrors the Financial Info row hidden state (S3-N2) and the sidebar card hidden state (S3-N1).</t>
+          <t>Mirrors the Financial Info row hidden state (S3-N2) and the sidebar card hidden state (S3-N1). | VIU qb batch-1 (2026-07-08): Hidden-when-none not captured this batch (every walked WO had adjustments). Quick re-check in batch 2.</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only.</t>
+          <t>This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only. | VIU qb batch-1 (2026-07-08): Financial Info shows collapsed 'Fees &amp; Discounts (2)  -$4.00' — N counts ALL scopes, value is the signed net total in grey. Shot s14-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png)</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>Financial Info card is read-only for adjustments (key decision, §3 of spec). Scope disambiguation uses a suffix e.g. '(LF3620)'.</t>
+          <t>Financial Info card is read-only for adjustments (key decision, §3 of spec). Scope disambiguation uses a suffix e.g. '(LF3620)'. | VIU qb batch-1 (2026-07-08): Row click did not visibly expand a per-adjustment read-only list in the harness (text unchanged). Needs a manual/visual re-check; no add/edit/remove controls seen in the row (read-only holds so far).</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>See Financial Data gates visibility of all fee/discount dollar amounts across surfaces (S13-R2/N1).</t>
+          <t>See Financial Data gates visibility of all fee/discount dollar amounts across surfaces (S13-R2/N1). | VIU qb batch-1 (2026-07-08): Hidden-when-none: not captured (paid WO's Financial Info not inspected). SFD-off half is Blocked-Env (no restricted user session).</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="L45" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3.</t>
+          <t>Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3. | VIU qb batch-1 (2026-07-08): Sidebar card title is 'WO Fees &amp; Discounts' (matches S3-R3; the case title used the older 'Work Order Fee / Discount' name — update case). Entries: name + signed badge ('-10%', '$11.00') + grey signed resolved ('+$11.00', '-$15.00' with true minus) + hover ⋮ menu = 'Edit | Remove' (spec S3-R9 says Edit/'Delete' — wording deviation). Shots s9-04/05, s11b-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png)</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4195,12 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button.</t>
+          <t>Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button. | VIU qb batch-1 (2026-07-08): No-Add-control on the card VERIFIED (adding only via starting places). Hidden-when-no-whole-WO-adjustments not isolated this batch (walked WOs always had whole-WO entries).</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="L47" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M47" s="18" t="inlineStr">
         <is>
-          <t>The 'Fees &amp; Discounts' column shows only on a part sale / parts view when the flag is on (S11-R7). Core-charge rows have an empty column (S11-R8).</t>
+          <t>The 'Fees &amp; Discounts' column shows only on a part sale / parts view when the flag is on (S11-R7). Core-charge rows have an empty column (S11-R8). | VIU qb batch-1 (2026-07-08): Story 11 Part Sales F&amp;D NOT BUILT on qb (recon: no F&amp;D column, no menu item, no card on a part sale).</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>Badge count N is the number of adjustments AFTER the first (so 3 total → '+2').</t>
+          <t>Badge count N is the number of adjustments AFTER the first (so 3 total → '+2'). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="L49" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M49" s="18" t="inlineStr">
         <is>
-          <t>The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008).</t>
+          <t>The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>The WO-line/customer variant of this breakdown omits the Max Amount column and the per-row trash (read-only); the Parts-page variant adds both (design §8).</t>
+          <t>The WO-line/customer variant of this breakdown omits the Max Amount column and the per-row trash (read-only); the Parts-page variant adds both (design §8). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L51" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M51" s="18" t="inlineStr">
         <is>
-          <t>For a single-adjustment part (#37346 Military Discount −$6.53) the Net adjustment equals that one amount (−$6.53).</t>
+          <t>For a single-adjustment part (#37346 Military Discount −$6.53) the Net adjustment equals that one amount (−$6.53). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14).</t>
+          <t>Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4689,12 +4689,12 @@
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M53" s="18" t="inlineStr">
         <is>
-          <t>Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b).</t>
+          <t>Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001).</t>
         </is>
       </c>
     </row>
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28).</t>
+          <t>Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28). | VIU qb batch-1 (2026-07-08): Edit dialog: Name/Amount/Max/Taxable editable; Type + Calculation Type rendered DISABLED (locked). Backend contract matches: change endpoint takes only {adjustmentId,name,amount,maxCap,taxable} and ignores kind/calculationType fields. Shot s9-06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="L55" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: change re-resolves against current totals; history logs "adjustment.updated"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M55" s="18" t="inlineStr">
         <is>
-          <t>Verify re-resolution uses current (not original) totals.</t>
+          <t>Verify re-resolution uses current (not original) totals. | VIU qb batch-1 (2026-07-08): Edit $12-&gt;$20: re-resolved against current totals (resolved 20; GST recomputed 15.44 = 5% x (292.83+11-15+20) exactly); template picker HIDDEN in edit mode; confirm button 'Save'; toast 'Fee updated'. Shot s9-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change re-resolves against current totals; history logs "adjustment.updated"</t>
         </is>
       </c>
     </row>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>The design mockups model no error/toast states; this is spec-driven (S2-R30, §7 toast table).</t>
+          <t>The design mockups model no error/toast states; this is spec-driven (S2-R30, §7 toast table). | VIU qb batch-1 (2026-07-08): Edit-mode save failure not inducible this batch. ADD-mode failure (150% discount) kept dialog open + showed error toast (S2-R30 shape verified in add mode).</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L57" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed"</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M57" s="18" t="inlineStr">
         <is>
-          <t>Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging.</t>
+          <t>Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging. | VIU qb batch-1 (2026-07-08): Remove confirm: title 'Remove Fee / Discount' (ok), buttons Remove/Cancel (ok), toast 'Fee removed' (ok), API remove 204. DEVIATION: message reads 'Are you sure you want to remove this fee?' — spec S3-R11a wants 'Remove "{name}" from this work order?'. Shot s9-08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed"</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — removal is governed by Work Orders/Lines Create-and-Edit, NOT the separate Delete permission (adjustments/remove endpoint; no delete-perm dependency) (S13-R7)</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4).</t>
+          <t>Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4). | VIU qb batch-1 (2026-07-08): Needs a role with Delete-but-not-Create&amp;Edit (and vice versa); no second-user login on qb env this batch.</t>
         </is>
       </c>
     </row>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="L59" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M59" s="18" t="inlineStr">
         <is>
-          <t>If removing brings the count down to one adjustment, the 'Show N more' toggle should disappear.</t>
+          <t>If removing brings the count down to one adjustment, the 'Show N more' toggle should disappear. | VIU qb batch-1 (2026-07-08): Inline-row remove not driven (inline ⋮ menu not opened programmatically); card-entry remove verified in FD-REMOVE-001.</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: part flat $5×qty2=$10 &amp; 10%×$232.68=$23.27 resolve independently on the part's own gross base, no stacking (§5-R5 Step 1)</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>Critical calc rule: line-level percentages all resolve against the same gross base — they never compound on each other (§5-R5).</t>
+          <t>Critical calc rule: line-level percentages all resolve against the same gross base — they never compound on each other (§5-R5). | VIU qb batch-1 (2026-07-08): Part-scope pair pending (no part). Same-target NO-STACKING verified on a LABOR line: 25% fee ($66.25 on gross 265) + flat -$5 resolved independently on the same gross base.</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="L61" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: whole-WO % adjustments resolve on Step-1 net totals (net labor $674.77 used by whole-WO pct_labor)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M61" s="18" t="inlineStr">
         <is>
-          <t>Uses the spec's own §5 worked example. Confirms three-step resolve order and no compounding between whole-WO adjustments.</t>
+          <t>Uses the spec's own §5 worked example. Confirms three-step resolve order and no compounding between whole-WO adjustments. | VIU qb batch-1 (2026-07-08): Two whole-WO adjustments use the same net base and don't change each other: with net subtotal $324.60 (incl. +$31.77 line-level), 100% discount -&gt; -$324.60 AND 150% fee -&gt; +$486.90 (both = pct x same base). Flat +$11 fee did not enter the 10% discount's base ($292.83). §5-R5 Step 2 verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: whole-WO % adjustments resolve on Step-1 net totals (net labor $674.77 used by whole-WO pct_labor)</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: Flat-fee template applied twice by hand → 2 distinct whole-WO adjustments (+$12 each)</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement.</t>
+          <t>This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement. | VIU qb batch-1 (2026-07-08): Same template applied twice by hand: two 'Flat fee' template adds -&gt; both 201, two adjustments on WO; the WO dialog's template picker still lists an already-applied template.</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="L63" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: customer "Fees &amp; Discounts (N)" tab with count</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M63" s="18" t="inlineStr">
         <is>
-          <t>Count in parentheses = number of default links on the customer, not adjustments on work orders.</t>
+          <t>Count in parentheses = number of default links on the customer, not adjustments on work orders. | VIU qb batch-1 (2026-07-08): Tab label 'Fees &amp; Discounts (N)' counts defaults live: (0) empty, (1) after add, (3)/(2) after ops. Shots s4-03/07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: customer "Fees &amp; Discounts (N)" tab with count</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: "Default Fees &amp; Discounts" card, exact S9-R14 caption, columns Name·Type·Calc·Amount·Max·Taxable</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>Customer card uses "Add Fee/Discount" (no spaces); WO/template dialogs use "Add Fee / Discount" (with spaces) — keep both exact (S9-R... exact-text note).</t>
+          <t>Customer card uses "Add Fee/Discount" (no spaces); WO/template dialogs use "Add Fee / Discount" (with spaces) — keep both exact (S9-R... exact-text note). | VIU qb batch-1 (2026-07-08): Card 'Default Fees &amp; Discounts'; caption EXACTLY matches S9-R14; columns Name/Type/Calculation Type/Amount/Max Amount/Taxable + actions; bold headers/plain cells. Shot s4-03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: "Default Fees &amp; Discounts" card, exact S9-R14 caption, columns Name·Type·Calc·Amount·Max·Taxable</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L65" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: POST /customers/{id}/default-adjustments {templateIds:[id]} → 201 adds default (GET confirms)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M65" s="18" t="inlineStr">
         <is>
-          <t>Toast for one default is the generic "Fee / discount added." — it does NOT vary by type (§7 toast table).</t>
+          <t>Toast for one default is the generic "Fee / discount added." — it does NOT vary by type (§7 toast table). | VIU qb batch-1 (2026-07-08): Add works end-to-end (toast 'Fee / discount added', row + count update, POST /customers/{id}/default-adjustments {templateIds:[...]}). DEVIATIONS from S9-R18/19/20: picker is a single 'Fee / Discount Templates' DROPDOWN with Cancel/SAVE (spec: caption + checkbox multi-select list + 'Add' button); no caption text. Shots s4-04/05/06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST /customers/{id}/default-adjustments {templateIds:[id]} → 201 adds default (GET confirms)</t>
         </is>
       </c>
     </row>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: default POST accepts templateIds array (multi-select add); plural toast per S9-R23b (recon UI)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>Plural toast pattern is "[N] fees / discounts added." per §7 toast table.</t>
+          <t>Plural toast pattern is "[N] fees / discounts added." per §7 toast table. | VIU qb batch-1 (2026-07-08): Multi-select NOT possible in the UI (single-select dropdown; reopening shows no list once one is chosen). Backend accepts templateIds ARRAY (API multi-link 201), so only the UI multi-select + '[N] fees / discounts added' toast are missing. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: default POST accepts templateIds array (multi-select add); plural toast per S9-R23b (recon UI)</t>
         </is>
       </c>
     </row>
@@ -5706,12 +5706,12 @@
       </c>
       <c r="L67" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08, = NOTE-FD-5): the customer "Add Fee/Discount" picker is a single-select "Fee / Discount Templates" dropdown + Cancel/Save (b2c-07), NOT the spec's checkbox multi-select list with "Add" (S9-R18/R20). Dropdown content (unlinked-only, Processing-Fee-as-Fee) not expanded this pass.</t>
         </is>
       </c>
       <c r="M67" s="18" t="inlineStr">
         <is>
-          <t>This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee".</t>
+          <t>This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee". | VIU qb batch-1 (2026-07-08): Picker lists only unlinked templates (verified: linked one disappears on reopen). DEVIATION: dropdown rows show the NAME only (no Type/Calc/Amount columns). Processing-fee template in the customer TABLE shows Type 'Processing fee' (better than the spec note's 'Fee'); its picker Type label not observable (no Type in picker). Shots s5-01, s11-02.</t>
         </is>
       </c>
     </row>
@@ -5774,10 +5774,14 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): With every template linked, the picker dropdown shows generic 'No results' — spec S9-R22 wants 'No templates available to add.'. Shot s5-03.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="inlineStr">
@@ -5842,12 +5846,12 @@
       </c>
       <c r="L69" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: DELETE /customers/{id}/default-adjustments/{id} → 204, no confirm (S9-R24)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M69" s="18" t="inlineStr">
         <is>
-          <t>Removing a customer default is intentionally no-confirm (S9-R24), unlike deleting a template (S7-R20 has a confirm).</t>
+          <t>Removing a customer default is intentionally no-confirm (S9-R24), unlike deleting a template (S7-R20 has a confirm). | VIU qb batch-1 (2026-07-08): Remove = DIRECT trash icon per row (spec: 3-dot menu with 'Remove'); needs no confirm (matches S9-R24) BUT NO 'Fee / discount removed' toast was observed. Row disappears, count updates. Shots s5-04/05. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: DELETE /customers/{id}/default-adjustments/{id} → 204, no confirm (S9-R24)</t>
         </is>
       </c>
     </row>
@@ -5911,10 +5915,14 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: empty-state "No fees or discounts yet. Use 'Add Fee/Discount' to add one."</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Empty state exactly 'No fees or discounts yet. Use 'Add Fee/Discount' to add one.' (S9-R17). Shot s4-03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: empty-state "No fees or discounts yet. Use 'Add Fee/Discount' to add one."</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
@@ -5978,12 +5986,12 @@
       </c>
       <c r="L71" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: a pct customer default is added as an independent adjustment on every new WO (kind/method/percent copied) (S9-R2/R3)</t>
         </is>
       </c>
       <c r="M71" s="18" t="inlineStr">
         <is>
-          <t>The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence.</t>
+          <t>The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence. | VIU qb batch-1 (2026-07-08): New WO for the customer received each default as an independent copy: appliedBy=customer_default, template values (amount/maxCap/taxable/calc) copied, own adjustment ids. Editing/removing on the WO left the defaults untouched.</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6056,12 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: a pct customer default keeps the percent (not a fixed $) and re-resolves against each WO's own base (S9-R6/R7)</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>Uses spec calc rule §5-R3.</t>
+          <t>Uses spec calc rule §5-R3. | VIU qb batch-1 (2026-07-08): Percentage default keeps the PERCENT: 10%/max-15 discount resolved $0.00 on an empty WO and -$15.00 (capped) once labor $265 existed — re-resolves against each WO's own base.</t>
         </is>
       </c>
     </row>
@@ -6119,10 +6127,14 @@
       </c>
       <c r="L73" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M73" s="18" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: removing a customer default leaves the already-added adjustment on an existing WO intact (S9-R8)</t>
+        </is>
+      </c>
+      <c r="M73" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Default links removed (via template deletion cascade) left the adjustments already on WOs fully intact (names/amounts unchanged, still resolving).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
@@ -6186,12 +6198,12 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: deleting a template that is a customer default removes the default link (S9-R9/S7-R4)</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule.</t>
+          <t>Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule. | VIU qb batch-1 (2026-07-08): Deleted template 'ZZAUTOTEST pfee' that was a default for 1 customer: delete-precondition API returned {affectedCustomerCount:1}; after delete the customer default list is empty AND the WO's pfee adjustment remains (S9-R9/S7-R4/S7-N1).</t>
         </is>
       </c>
     </row>
@@ -6255,10 +6267,14 @@
       </c>
       <c r="L75" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M75" s="18" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: deleting a customer removes its default links (defaults endpoint → 404 after delete) (S9-R10)</t>
+        </is>
+      </c>
+      <c r="M75" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): customers/delete succeeded (contacts/vehicles removed first); the customer's default-adjustments endpoint 404s afterwards — links gone with the customer.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
@@ -6320,10 +6336,14 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M76" s="15" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: a newly created customer auto-inherited BOTH auto-apply location templates as defaults (S9-R1)</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): UI-created customer auto-inherited BOTH auto-apply templates as defaults (autoApply:true rows). NOTE/GAP: an API-created customer (customers/create) got NO seeded defaults — seeding happens only on the UI create path (FDBUG-12).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
@@ -6386,12 +6406,12 @@
       </c>
       <c r="L77" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — SPA route guard requires customersCreateAndEdit + seeApArData (tab hidden otherwise)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M77" s="18" t="inlineStr">
         <is>
-          <t>CAUTION: Story 13 Custom-Roles model (SV-7388) may not be live on staging yet — record what staging actually enforces and flag divergence. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
+          <t>CAUTION: Story 13 Custom-Roles model (SV-7388) may not be live on staging yet — record what staging actually enforces and flag divergence. Restore Tech to Time Clock (role 77b069d1-...) after. | VIU qb batch-1 (2026-07-08): No restricted-user session on qb. Bundle route meta CONFIRMS the gate: customer tab route 'default-adjustments' requires ['customersCreateAndEdit','seeApArData'] (matches S13-R9). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — SPA route guard requires customersCreateAndEdit + seeApArData (tab hidden otherwise)</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6475,12 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — double-add: setup confirmed (customer default that is also auto-apply exists) and recon observed ×2; not re-verified this pass (WO create via API/UI not completed). See bugs-log BUG-FD-1</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>A double-add is a KNOWN DEFECT tracked separately, not a spec requirement. Report actual behavior.</t>
+          <t>A double-add is a KNOWN DEFECT tracked separately, not a spec requirement. Report actual behavior. | VIU qb batch-1 (2026-07-08): Double-add NOT reproduced (good): customer with templates that are BOTH location-auto-apply AND its defaults got each adjustment exactly ONCE (appliedBy=customer_default) on a new WO. The S9 known bug appears fixed on this build. | [pass A same-day parallel verdict] VIU-Pending — double-add: setup confirmed (customer default that is also auto-apply exists) and recon observed ×2; not re-verified this pass (WO create via API/UI not completed). See bugs-log BUG-FD-1 | CONFLICT NOTE: pass A (bugs-log BUG-FD-1) kept double-add open based on the earlier recon x2 observation; pass B controlled repro (customer with BOTH auto-apply templates as defaults, fresh WO 19:40Z) produced exactly ONE adjustment per template. Treat as fixed/intermittent - PO confirm.</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6544,12 @@
       </c>
       <c r="L79" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M79" s="18" t="inlineStr">
         <is>
-          <t>Unlike WO/template save failures, customer-default failures use the generic system error, not a custom message.</t>
+          <t>Unlike WO/template save failures, customer-default failures use the generic system error, not a custom message. | VIU qb batch-1 (2026-07-08): Failure toasts not inducible this batch.</t>
         </is>
       </c>
     </row>
@@ -6593,12 +6613,12 @@
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live.</t>
+          <t>The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live. | VIU qb batch-1 (2026-07-08): Page lives at Administration -&gt; FINANCE -&gt; 'Fees &amp; Discounts' (below Payment Methods), route /administration/adjustment-templates — NOT under SERVICE below Canned Lines (S7-R7a/R7c). Matches the S13-R8 target location instead. Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation)</t>
         </is>
       </c>
     </row>
@@ -6663,10 +6683,14 @@
       </c>
       <c r="L81" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action</t>
-        </is>
-      </c>
-      <c r="M81" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M81" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Columns exactly Name/Type/Calculation Type/Amount/Max Amount/Taxable/Auto-Apply To Work Orders + actions. Note: actions include an EDIT icon and DELETE icon (spec lists only delete; row-click also edits). Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -6732,12 +6756,12 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27).</t>
+          <t>Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27). | VIU qb batch-1 (2026-07-08): Create works (fields Name(100)/Type/Calc/Amount/Taxable/auto-apply + preview-less). DEVIATIONS: confirm button 'Create' (spec 'Add Fee / Discount'); toast 'Template created' (spec 'Fee added'); amount label '$ Default Amount' (spec 'Amount'); Taxable &amp; auto-apply are TOGGLES not Yes/No dropdown/checkbox; EXTRA 'Description (Optional)' field (255) not in spec; auto-apply label 'Auto-apply to new work orders' (spec '...at this location'). Title 'New Fee / Discount' OK. Shots s1-03, s2-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast</t>
         </is>
       </c>
     </row>
@@ -6802,10 +6826,14 @@
       </c>
       <c r="L83" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon)</t>
-        </is>
-      </c>
-      <c r="M83" s="18" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Discount template created fine but toast is generic 'Template created' — spec S7-R18a wants 'Discount added'. Shot s2-09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
@@ -6869,10 +6897,14 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M84" s="15" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: auto-apply templates (Flat fee, Customer fee) land automatically on every newly-created WO as whole-WO adjustments (S7-R5/R6a/R6b)</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Auto-apply template landed on a NEW WO automatically: adjustments appliedBy='auto', scope whole_wo, values copied (Customer fee $200 + Flat fee $12 observed on WO S3-15901).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
@@ -6936,10 +6968,14 @@
       </c>
       <c r="L85" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates/{id}/change → 200 (edit); "updated" toast (recon)</t>
-        </is>
-      </c>
-      <c r="M85" s="18" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M85" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Row-click opens edit dialog (S7-R9 ok), title 'Edit Fee / Discount' (ok), confirm 'Save' (ok). DEVIATIONS: toast 'Template updated' (spec 'Fee updated'); Type + Calculation Type are LOCKED (disabled) in template edit — spec S7 does not lock them (only the WO dialog S2-R5 does). Shots s3-01/02/03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates/{id}/change → 200 (edit); "updated" toast (recon)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
@@ -7002,12 +7038,12 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — UI: delete-confirm dialog "Delete Template" + S7-R21 warning "This template is set as a default for 1 customer. Deleting it will remove it from them." + red Delete (b2c-05). NOTE build title/message wording differs from spec S7-R20 exact ("Are you sure you want to delete this fee / discount?")</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>The remove-confirm dialog is not in the HTML mockups; verify exact copy live.</t>
+          <t>The remove-confirm dialog is not in the HTML mockups; verify exact copy live. | VIU qb batch-1 (2026-07-08): Delete confirm: title 'Delete Template', message 'Are you sure you want to delete this template?' — spec S7-R20 wants '...delete this fee / discount?'. Buttons Delete/Cancel ok. Shot s3-05.</t>
         </is>
       </c>
     </row>
@@ -7070,10 +7106,14 @@
       </c>
       <c r="L87" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: GET adjustment-templates/{id}/delete-precondition → {affectedCustomerCount} drives S7-R21 warning</t>
-        </is>
-      </c>
-      <c r="M87" s="18" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M87" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Warning present when template is a customer default: 'This template is set as a default for 1 customer. Deleting it will remove it from them.' + delete-precondition API {affectedCustomerCount:N}. Wording differs from spec S7-R21 ('...for [N] customer(s). Their defaults will be removed too.'). Shot s16-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: GET adjustment-templates/{id}/delete-precondition → {affectedCustomerCount} drives S7-R21 warning</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
@@ -7135,10 +7175,14 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M88" s="15" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: template deleted (204); WO adjustment made from it survives unchanged (resolved intact) — S7-R4/S7-N1</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): After template delete, the WO adjustments created from it stayed unchanged (pfee still on WO; earlier external deletion of 2 templates likewise left WO copies intact).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
@@ -7205,12 +7249,12 @@
       </c>
       <c r="L89" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M89" s="18" t="inlineStr">
         <is>
-          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering.</t>
+          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02.</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7320,12 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: template create accepts maxCap for percentage; 0 treated empty (§5-R6)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>Design mockups show a "Max cap" always rendered (design-notes §10 item 4) — flag if staging shows Max Amount for Flat too.</t>
+          <t>Design mockups show a "Max cap" always rendered (design-notes §10 item 4) — flag if staging shows Max Amount for Flat too. | VIU qb batch-1 (2026-07-08): Max Amount appears only for % methods (verified). DEVIATION on 0-handling: API stores maxCap=0 and resolves with NO cap (10% of 324.60 -&gt; 32.46 despite maxCap 0) — spec §5-R6 says $0 forces $0.00 and S7-R14 says 0 is treated as empty. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: template create accepts maxCap for percentage; 0 treated empty (§5-R6)</t>
         </is>
       </c>
     </row>
@@ -7344,10 +7388,14 @@
       </c>
       <c r="L91" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M91" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M91" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Cannot empty the location's template library (2 pre-existing real templates in use on this shared env); empty-state string unverified.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
@@ -7409,10 +7457,14 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M92" s="15" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: pct-discount 150% template rejected 400; pct-fee 150% template allowed 201 (no cap) — S7-R3/§5-R2</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Discount template 150% blocked at save with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API 400 same message); fee template 150% created fine (API 201, deleted after). Shots s2-04/05/06.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
@@ -7474,12 +7526,12 @@
       </c>
       <c r="L93" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — Recon: Fee/Discount template offers Flat Amount / % of Labor / % of Parts / % of Subtotal, no scope field</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M93" s="18" t="inlineStr">
         <is>
-          <t>Processing Fee has different method options (Flat Amount, % of Grand Total) — see FD-PROC-002.</t>
+          <t>Processing Fee has different method options (Flat Amount, % of Grand Total) — see FD-PROC-002. | VIU qb batch-1 (2026-07-08): Fee/Discount calc options exactly: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; NO scope field anywhere. Shot s2-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: Fee/Discount template offers Flat Amount / % of Labor / % of Parts / % of Subtotal, no scope field</t>
         </is>
       </c>
     </row>
@@ -7542,10 +7594,14 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M94" s="15" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Save-failure toast not inducible this batch.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
@@ -7606,12 +7662,12 @@
       </c>
       <c r="L95" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M95" s="18" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after. | VIU qb batch-1 (2026-07-08): No restricted-user session. Bundle route meta CONFIRMS the gate: adjustment-templates route requires ['settingsFinance'] (S13-R8). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated) | MERGED VERDICT: pass A verified 403 for a no-settingsFinance user on template list/create; FE route meta also requires settingsFinance.</t>
         </is>
       </c>
     </row>
@@ -7675,10 +7731,14 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
-        </is>
-      </c>
-      <c r="M96" s="15" t="inlineStr"/>
+          <t>VIU-Verified qb 2026-07-08 — API: template Name 101 chars → 400; 100 chars → 201 (S7-R12c 100-char limit)</t>
+        </is>
+      </c>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Name input maxlength=100 enforced (typed 110 chars -&gt; value length 100).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
@@ -7739,12 +7799,12 @@
       </c>
       <c r="L97" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M97" s="18" t="inlineStr">
         <is>
-          <t>Processing Fee UI is absent from the HTML mockups — verify live.</t>
+          <t>Processing Fee UI is absent from the HTML mockups — verify live. | VIU qb batch-1 (2026-07-08): 'Processing Fee' third type ABSENT from the template-builder Type dropdown (Fee/Discount only). Backend DOES support kind 'processing_fee' (template created via API); admin LIST then shows its Type as 'Fee' (mislabel) while the customer tab shows 'Processing fee'. Shots s2-01, s11-01/02.</t>
         </is>
       </c>
     </row>
@@ -7809,10 +7869,14 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M98" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-NotBuilt</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): UI not built. BACKEND verified: processing_fee allows pct_grand_total and flat ONLY (pct_subtotal -&gt; 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee').</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
@@ -7873,10 +7937,14 @@
       </c>
       <c r="L99" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M99" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-NotBuilt</t>
+        </is>
+      </c>
+      <c r="M99" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): UI not built. BACKEND verified: maxCap on processing fee -&gt; 400 'A processing fee cannot have a minimum or maximum cap.'</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
@@ -7940,12 +8008,12 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>OPEN QUESTION (§14 item 5): the disclosure's literal text is NOT in the exported spec — capture the exact wording from the live dialog before asserting it. Spec copy says "toggle" but the control is the Yes/No dropdown.</t>
+          <t>OPEN QUESTION (§14 item 5): the disclosure's literal text is NOT in the exported spec — capture the exact wording from the live dialog before asserting it. Spec copy says "toggle" but the control is the Yes/No dropdown. | VIU qb batch-1 (2026-07-08): UI not built; taxable default + legal disclosure unverifiable (disclosure text also absent from spec extract — open question #5).</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8078,12 @@
       </c>
       <c r="L101" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M101" s="18" t="inlineStr">
         <is>
-          <t>Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15).</t>
+          <t>Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15). | VIU qb batch-1 (2026-07-08): Cannot be added to a WO by hand: WO dialog Type offers only Fee/Discount (S8-N1) and API kind=processing_fee -&gt; 400 'A processing fee cannot be added manually.' (S8-R16). NOTE: whole-WO template-picker exclusion of pfee templates (S8-N2) not explicitly captured.</t>
         </is>
       </c>
     </row>
@@ -8079,10 +8147,14 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M102" s="15" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Auto-apply path not tested with a processing-fee template (test pfee had autoApply=false). Customer-default path verified instead (FD-PROC-007).</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
@@ -8144,10 +8216,14 @@
       </c>
       <c r="L103" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M103" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M103" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Processing-fee template linked as a customer default WAS auto-added to the customer's new WO (kind processing_fee, scope whole_wo, appliedBy customer_default, resolved on grand total).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
@@ -8210,12 +8286,12 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02.</t>
         </is>
       </c>
     </row>
@@ -8281,12 +8357,12 @@
       </c>
       <c r="L105" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M105" s="18" t="inlineStr">
         <is>
-          <t>Uses the spec's worked example directly.</t>
+          <t>Uses the spec's worked example directly. | VIU qb batch-1 (2026-07-08): Resolves LAST and re-resolves dynamically, BUT THE BASE IS WRONG (FDBUG-2): 3% pfee resolved $15.90 = 3% x $530.07 where $530.07 = (subtotal 292.83 + whole-WO fees 212) x 1.05 — the base INCLUDES whole-WO fees AND their tax. Spec §5-R4 excludes every whole-WO fee/discount: expected 3% x (292.83 + 14.64) = $9.22.</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8426,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>The UI hides these options; this guards data sent from outside the product.</t>
+          <t>The UI hides these options; this guards data sent from outside the product. | VIU qb batch-1 (2026-07-08): API rejects processing fee with maxCap and with any method other than flat/pct_grand_total (exact 400 messages captured).</t>
         </is>
       </c>
     </row>
@@ -8419,10 +8495,14 @@
       </c>
       <c r="L107" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M107" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M107" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Processing fee is fee-only and always adds: kind is 'processing_fee' (no discount variant); resolved amounts positive; taxable pfee ADDS its own amount to the taxable base (tax grew by 5% of the fee) without growing its own base.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
@@ -8484,10 +8564,14 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M108" s="15" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Edited the pfee TEMPLATE amount 3% -&gt; 4%: the pfee already on the WO kept amount=3 (unchanged), S8-R19.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
@@ -8550,10 +8634,14 @@
       </c>
       <c r="L109" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M109" s="18" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M109" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Multiple simultaneous processing fees not tested (single pfee only). Batch-2.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
@@ -8613,12 +8701,12 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>Min Amount exists only in the data model; both dialogs always send it empty (null).</t>
+          <t>Min Amount exists only in the data model; both dialogs always send it empty (null). | VIU qb batch-1 (2026-07-08): Min-amount payload guard (S8-N6) not probed. Batch-2 API probe (minCap field).</t>
         </is>
       </c>
     </row>
@@ -8682,12 +8770,12 @@
       </c>
       <c r="L111" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M111" s="18" t="inlineStr">
         <is>
-          <t>No customer estimate/invoice view exists in the HTML mockups — verify layout live.</t>
+          <t>No customer estimate/invoice view exists in the HTML mockups — verify layout live. | VIU qb batch-1 (2026-07-08): ESTIMATE rendering verified in the WO Finance tab (adjustments present). Invoice not created this batch (kept the env clean); same-layout claim needs an invoice walk.</t>
         </is>
       </c>
     </row>
@@ -8752,10 +8840,14 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Labor-line adjustment on the estimate: indented '↳ ZZAUTOTEST line fee (% of labor) $66.25' under its labor line — arrow, phrase and fee format all exact. Shot s14b.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
@@ -8817,10 +8909,14 @@
       </c>
       <c r="L113" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M113" s="18" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M113" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Part-line phrase pending (no part seeded).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
@@ -8883,12 +8979,12 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>Note this differs from WO screens, which use a signed minus (e.g. "−$26.08") in plain grey.</t>
+          <t>Note this differs from WO screens, which use a signed minus (e.g. "−$26.08") in plain grey. | VIU qb batch-1 (2026-07-08): Fee shows '$11.00'; discount shows '($15.00)' — round brackets, two decimals, no minus (S5-R4/S12-R7). Estimate doc capture s14b.</t>
         </is>
       </c>
     </row>
@@ -8953,10 +9049,14 @@
       </c>
       <c r="L115" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M115" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M115" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Bottom 'Adjustments' block lists whole-WO adjustments one per row in creation order ('ZZAUTOTEST fee flat $11.00' then 'ZZAUTOTEST disc pct (% of subtotal) ($15.00)') with percentage phrases; flat has no phrase.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
@@ -9018,12 +9118,12 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>Grouping is ONLY on the customer document; WO line table lists each one by one (Story 3).</t>
+          <t>Grouping is ONLY on the customer document; WO line table lists each one by one (Story 3). | VIU qb batch-1 (2026-07-08): Line-level adjustment DOES also appear in the bottom block as its own row (S5-R8 half verified); grouping with '(xN)' count needs &gt;1 same-name line-level adjustments — pending.</t>
         </is>
       </c>
     </row>
@@ -9085,10 +9185,14 @@
       </c>
       <c r="L117" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
-        </is>
-      </c>
-      <c r="M117" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M117" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Processing fee row on the estimate reads 'ZZAUTOTEST pfee (% of grand total) $6.68' — exact S8-R22 phrase. Shot s15-01.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
@@ -9151,10 +9255,14 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M118" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): WO with $0.00 shop supplies: the estimate shows NO 'Shop supplies' row at all (Labor/Parts/Adjustments only) — S14-R1 on the estimate. Financial-tab/invoice variants pending. Shot s15-01.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
@@ -9215,10 +9323,14 @@
       </c>
       <c r="L119" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M119" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M119" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): WO with shop supplies $27.83: 'Shop supplies $27.83' row IS rendered on the estimate (visible-when-&gt;0 behavior).</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
@@ -9280,10 +9392,14 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M120" s="15" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Declined-line $0.00 doc row pending (declined $0 resolution itself verified via API).</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
@@ -9343,10 +9459,14 @@
       </c>
       <c r="L121" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 5/14 customer document not reached (needs invoice-ready WO)</t>
-        </is>
-      </c>
-      <c r="M121" s="18" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M121" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Adjustments block position ok (after Labor/Parts/Shop supplies, before Subtotal -&gt; GST -&gt; Total). DEVIATION/BUG (FDBUG-1): Subtotal and Total do NOT include the adjustment amounts while GST DOES include their tax — estimate showed Subtotal $292.83 / GST $17.75 / Total $310.58 with +$62.25 net adjustments missing from the total; a fees-only WO showed 'Total $10.93' = tax alone. Customer-facing money is wrong.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
@@ -9410,12 +9530,12 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>QuickBooks sync is backend; verify via the QuickBooks side or the sync payload.</t>
+          <t>QuickBooks sync is backend; verify via the QuickBooks side or the sync payload. | VIU qb batch-1 (2026-07-08): No QuickBooks settings UI on qb env (INTEGRATIONS shows IBS only) and no QB account to sync into; invoiced-sync not exercisable. NOTE: GET /api/bookkeeping/adjustment-item-mapping-status EXISTS -&gt; {quickBooksConnected:true, feeItemMapped:true, discountItemMapped:true} (the app polls it before every add).</t>
         </is>
       </c>
     </row>
@@ -9480,10 +9600,14 @@
       </c>
       <c r="L123" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M123" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M123" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001 (no QB sync surface).</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
@@ -9545,10 +9669,14 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M124" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001. $0.00 resolve itself verified (§5-R8) — only the QB skip is untestable.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
@@ -9612,10 +9740,14 @@
       </c>
       <c r="L125" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M125" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M125" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Mapping guard not triggerable: mapping-status reports both items MAPPED and there is no QB settings page to unmap on this env. The guard endpoint exists and is called before every add dialog.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
@@ -9678,10 +9810,14 @@
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M126" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
@@ -9741,12 +9877,12 @@
       </c>
       <c r="L127" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M127" s="18" t="inlineStr">
         <is>
-          <t>Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth.</t>
+          <t>Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth. | VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
         </is>
       </c>
     </row>
@@ -9810,10 +9946,14 @@
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
@@ -9875,10 +10015,14 @@
       </c>
       <c r="L129" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M129" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M129" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Half-verified: with items mapped/connected (per mapping-status) adds are never blocked anywhere (dozens of adds succeeded). Not-connected/unmapped variants untestable on this env.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
@@ -9942,10 +10086,14 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M130" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M130" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Unexported-items recovery untestable (no QB).</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
@@ -10006,12 +10154,12 @@
       </c>
       <c r="L131" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M131" s="18" t="inlineStr">
         <is>
-          <t>Per-class allocation is out of scope for V1.</t>
+          <t>Per-class allocation is out of scope for V1. | VIU qb batch-1 (2026-07-08): Class propagation untestable (no QB).</t>
         </is>
       </c>
     </row>
@@ -10074,10 +10222,14 @@
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Class validation untestable (no QB).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
@@ -10140,12 +10292,12 @@
       </c>
       <c r="L133" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M133" s="18" t="inlineStr">
         <is>
-          <t>Uses the spec's exact $100/$10/$150 worked example.</t>
+          <t>Uses the spec's exact $100/$10/$150 worked example. | VIU qb batch-1 (2026-07-08): QB export untestable, but floor evidence exists: the add-dialog preview floors 'New work-order subtotal' at $0.00 for an over-100% discount, and adjustmentsSummary carries an 'excessCreditAmount' field (0 so far). Full worked-example (tax-still-owed) needs an invoice-time walk — batch 2.</t>
         </is>
       </c>
     </row>
@@ -10210,10 +10362,14 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M134" s="15" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M134" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export-side — untestable without QB.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
@@ -10275,10 +10431,14 @@
       </c>
       <c r="L135" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M135" s="18" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M135" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): No warn/confirm was shown when saving a 100% discount via API/UI on an open WO — the S6-R12 warning presumably belongs to the invoice/save flow; needs an invoicing walk. excessCreditAmount field exists.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
@@ -10341,10 +10501,14 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr"/>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Customer-credit carry needs the invoicing walk (Deposits &amp; Credits check) — batch 2.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
@@ -10405,10 +10569,14 @@
       </c>
       <c r="L137" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 6 QuickBooks not connected on this env (GET bookkeeping/adjustment-item-mapping-status hook exists but inert)</t>
-        </is>
-      </c>
-      <c r="M137" s="18" t="inlineStr"/>
+          <t>VIU-Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M137" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Line-tax on synced lines untestable (no QB). In-app tax behavior itself verified under §5-R11.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
@@ -10472,10 +10640,14 @@
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: add/edit/remove each log one distinct event (adjustment.added/updated/removed)</t>
-        </is>
-      </c>
-      <c r="M138" s="15" t="inlineStr"/>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M138" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Manual actions each write ONE entry with bold labels 'Fee added' / 'Fee updated' / 'Fee removed' (verified sequence). DEVIATION/BUG (FDBUG-3): AUTO-APPLIED adjustments (location auto-apply, customer defaults, processing fee) write NO history entry at all — a new WO with 3 auto adjustments showed only 'Created'/'Line created'. Shots s9-12, s11b-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add/edit/remove each log one distinct event (adjustment.added/updated/removed)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
@@ -10539,12 +10711,12 @@
       </c>
       <c r="L139" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: detail carries adjustmentName, adjustmentKind, adjustmentSetRate (set rate not resolved), adjustmentAppliedTo="Full invoice"</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M139" s="18" t="inlineStr">
         <is>
-          <t>History log uses "Full invoice" whereas other screens say "Whole Work Order". Amount is the set rate, not resolved — this is why SFD does not gate the log (S10-R6c).</t>
+          <t>History log uses "Full invoice" whereas other screens say "Whole Work Order". Amount is the set rate, not resolved — this is why SFD does not gate the log (S10-R6c). | VIU qb batch-1 (2026-07-08): Details block shows 'Name: Flat fee | Amount: $20.00 | Applied to: Full invoice' — Name ok, Amount = SET RATE not resolved total (ok), 'Full invoice' label exact (ok). DEVIATION: NO 'Type:' line in the details (S10-R6b). Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: detail carries adjustmentName, adjustmentKind, adjustmentSetRate (set rate not resolved), adjustmentAppliedTo="Full invoice"</t>
         </is>
       </c>
     </row>
@@ -10607,10 +10779,14 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: adjustment entries have lineId=null (Line column "−"); no saved-state icon</t>
-        </is>
-      </c>
-      <c r="M140" s="15" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M140" s="15" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Adjustment entries show Line column '-' and no saved-state icon. Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: adjustment entries have lineId=null (Line column "−"); no saved-state icon</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
@@ -10673,12 +10849,12 @@
       </c>
       <c r="L141" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M141" s="18" t="inlineStr">
         <is>
-          <t>The history log is the one exception to the flag-off rule.</t>
+          <t>The history log is the one exception to the flag-off rule. | VIU qb batch-1 (2026-07-08): Flag-off visibility not tested — org-level flag toggle skipped on this SHARED env (concurrent dev activity observed); needs a maintenance window or dedicated env.</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10920,12 @@
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — tech(SFD off): GET history → 200 with entries; add event carries adjustmentSetRate=8% (SET rate, not resolved), kind, appliedTo="Full invoice" — F&amp;D history persists independent of SFD (S10-R1/R6c/S13-R10)</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>CAUTION: Story 13 model may not be live on staging yet. Restore Tech to Time Clock (role 77b069d1-...) after.</t>
+          <t>CAUTION: Story 13 model may not be live on staging yet. Restore Tech to Time Clock (role 77b069d1-...) after. | VIU qb batch-1 (2026-07-08): SFD-off visibility needs a restricted user session — not available on qb this batch.</t>
         </is>
       </c>
     </row>
@@ -10813,12 +10989,12 @@
       </c>
       <c r="L143" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — View History Logs is an FE display gate only: tech without it still receives F&amp;D history entries from the API (200) — BE does not enforce (S13-R10)</t>
         </is>
       </c>
       <c r="M143" s="18" t="inlineStr">
         <is>
-          <t>Restore Tech to Time Clock after. CAUTION: Story 13 model may not be fully live on staging — record actual gating.</t>
+          <t>Restore Tech to Time Clock after. CAUTION: Story 13 model may not be fully live on staging — record actual gating. | VIU qb batch-1 (2026-07-08): View-History-Logs gating needs a restricted user session.</t>
         </is>
       </c>
     </row>
@@ -10883,12 +11059,12 @@
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): current build may show raw "processing_fee" on "Applied to:" instead of "Full invoice" — record actual value.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): current build may show raw "processing_fee" on "Applied to:" instead of "Full invoice" — record actual value. | VIU qb batch-1 (2026-07-08): Processing-fee history could not be verified: its auto-add wrote NO entry (FDBUG-3), and its removal wasn't exercised before cleanup. Batch-2: remove a pfee manually and check the entry.</t>
         </is>
       </c>
     </row>
@@ -10951,10 +11127,14 @@
       </c>
       <c r="L145" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: edit to amount 8 logs adjustment.updated with adjustmentSetRate=8 (new set rate)</t>
-        </is>
-      </c>
-      <c r="M145" s="18" t="inlineStr"/>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M145" s="18" t="inlineStr">
+        <is>
+          <t>VIU qb batch-1 (2026-07-08): Edit $12-&gt;$20 logged 'Fee updated ... Amount: $20.00' — the NEW set rate, not a resolved total. Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: edit to amount 8 logs adjustment.updated with adjustmentSetRate=8 (new set rate)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
@@ -11022,12 +11202,12 @@
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base.</t>
+          <t>Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base. | VIU qb batch-1 (2026-07-08): base x percent verified repeatedly: 10% x 265 = 26.50; 25% x 265 = 66.25; 3% x 530.07 = 15.90; 10% x 292.83 = 29.28 (pre-cap). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json)</t>
         </is>
       </c>
     </row>
@@ -11097,12 +11277,12 @@
       </c>
       <c r="L147" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M147" s="18" t="inlineStr">
         <is>
-          <t>Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up.</t>
+          <t>Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up. | VIU qb batch-1 (2026-07-08): Half-cent rounds UP: 0.1% x $265 = $0.265 -&gt; resolved $0.27 (API). Also 25% x 292.83 = 73.2075 -&gt; 73.21. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63</t>
         </is>
       </c>
     </row>
@@ -11169,12 +11349,12 @@
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected.</t>
+          <t>Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected. | VIU qb batch-1 (2026-07-08): Whole-WO flat $11 -&gt; 11.00; labor-line flat $5 -&gt; 5.00 exactly (no quantity part). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty)</t>
         </is>
       </c>
     </row>
@@ -11242,12 +11422,12 @@
       </c>
       <c r="L149" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M149" s="18" t="inlineStr">
         <is>
-          <t>Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not.</t>
+          <t>Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not. | VIU qb batch-1 (2026-07-08): Part-line per-item multiplication pending (no part target). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14)</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11496,12 @@
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging.</t>
+          <t>Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging. | VIU qb batch-1 (2026-07-08): Discount: 100% accepted, 100.01% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% accepted. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11568,12 @@
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero"</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M151" s="18" t="inlineStr">
         <is>
-          <t>Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging.</t>
+          <t>Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging. | VIU qb batch-1 (2026-07-08): Flat $0.01 accepted (min ok); 0/negative rejected. DEVIATION (FDBUG-10): percent 0.005 was silently COERCED UP to 0.01 (201, amount=0.01) instead of being rejected as below-minimum. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero"</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11642,12 @@
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount.</t>
+          <t>Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount. | VIU qb batch-1 (2026-07-08): Clamp verified: 10% x 324.60 = 32.46 -&gt; maxCap 5 -&gt; resolved 5.00; 10%/max15 discount -&gt; -15.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11715,12 @@
       </c>
       <c r="L153" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M153" s="18" t="inlineStr">
         <is>
-          <t>Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs.</t>
+          <t>Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs. | VIU qb batch-1 (2026-07-08): Blank maxCap = no cap (ok). DEVIATION (FDBUG-9): maxCap=0 accepted by the API and treated as NO CAP (resolved 32.46) — spec §5-R6 says Max $0 forces $0.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product | Pass A read maxCap-0-as-no-cap as acceptable (spec calls $0 old-data-only); keeping Deviation since observed behavior (no cap) also contradicts the "$0 forces $0.00" rule - PO question.</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11787,12 @@
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — API: whole-WO 10% of Parts on a WO with $0 parts → resolved $0.00 ($0 base → $0.00, §5-R8)</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time.</t>
+          <t>QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time. | VIU qb batch-1 (2026-07-08): $0 base -&gt; $0.00 resolve verified (% of Parts Total on a parts-less WO -&gt; +$0.00, still displayed). QB-skip half untestable (no QB).</t>
         </is>
       </c>
     </row>
@@ -11678,12 +11858,12 @@
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M155" s="18" t="inlineStr">
         <is>
-          <t>The design preview floors negative amounts to 0 (design §6), consistent with §5. This case is about the BASE being floored, not the whole-total floor (that is FD-CALC-016/017).</t>
+          <t>The design preview floors negative amounts to 0 (design §6), consistent with §5. This case is about the BASE being floored, not the whole-total floor (that is FD-CALC-016/017). | VIU qb batch-1 (2026-07-08): Negative base not constructible this batch (requires negative line totals). Pending.</t>
         </is>
       </c>
     </row>
@@ -11751,12 +11931,12 @@
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M156" s="15" t="inlineStr">
         <is>
-          <t>Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35).</t>
+          <t>Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35). | VIU qb batch-1 (2026-07-08): Taxable fee RAISES tax, taxable discount LOWERS it — GST matched 5% x (subtotal + fees - discounts) to the cent in every state (14.44, 15.44, 17.75, 26.04 checks). Non-taxable variant not isolated numerically this batch. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged</t>
         </is>
       </c>
     </row>
@@ -11824,12 +12004,12 @@
       </c>
       <c r="L157" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: 3-step order — labor-line 10% disc → net labor $674.77; whole-WO 5% pct_labor = $33.74 (on NET not gross $37.49)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M157" s="18" t="inlineStr">
         <is>
-          <t>Design mock's preview is base-blind (design §9 item 1). This case validates the enforced §5-R5 step order on the server, not the preview.</t>
+          <t>Design mock's preview is base-blind (design §9 item 1). This case validates the enforced §5-R5 step order on the server, not the preview. | VIU qb batch-1 (2026-07-08): 3-step order verified: line-level resolves on TARGET GROSS (25% x 265); whole-WO percentage resolves on NET subtotal INCLUDING line-level effects (100% x 324.60 after +31.77 line-level) and EXCLUDING other whole-WO adjustments; no stacking anywhere. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 3-step order — labor-line 10% disc → net labor $674.77; whole-WO 5% pct_labor = $33.74 (on NET not gross $37.49)</t>
         </is>
       </c>
     </row>
@@ -11897,12 +12077,12 @@
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6).</t>
+          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22.</t>
         </is>
       </c>
     </row>
@@ -11971,12 +12151,12 @@
       </c>
       <c r="L159" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 8 Processing Fee NOT built in UI (Type dropdown = Fee/Discount only). NOTE: backend accepts kind:"processing_fee" + calc pct_grand_total (POST→201)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M159" s="18" t="inlineStr">
         <is>
-          <t>% of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4).</t>
+          <t>% of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4). | VIU qb batch-1 (2026-07-08): Base IS tax-inclusive on purpose (includes 5% GST layer) and maxCap is rejected for processing fees ('cannot have a minimum or maximum cap'). Note the base composition bug tracked under FD-CALC-013.</t>
         </is>
       </c>
     </row>
@@ -12047,12 +12227,12 @@
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
         <is>
-          <t>Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt.</t>
+          <t>Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt. | VIU qb batch-1 (2026-07-08): Floor-at-$0 shows in the dialog preview; full non-taxable-vs-taxable worked example + credit carry needs the invoice-time walk (no warn observed on plain save). Batch-2. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
     </row>
@@ -12120,12 +12300,12 @@
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M161" s="18" t="inlineStr">
         <is>
-          <t>Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c).</t>
+          <t>Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c). | VIU qb batch-1 (2026-07-08): Taxable over-discount example pending with FD-CALC-015. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
     </row>
@@ -12194,12 +12374,12 @@
       </c>
       <c r="L162" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M162" s="15" t="inlineStr">
         <is>
-          <t>Largest-remainder penny allocation is a backend QuickBooks-sync detail (S6-R10d). Verify line sums equal the floored subtotal to the cent.</t>
+          <t>Largest-remainder penny allocation is a backend QuickBooks-sync detail (S6-R10d). Verify line sums equal the floored subtotal to the cent. | VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export behavior — blocked/pending with FD-QB-013. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected)</t>
         </is>
       </c>
     </row>
@@ -12267,12 +12447,12 @@
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — tech(view_mode=tech) WO view returns sub_total="0.00" (financials masked); See Financial Data gates $ visibility (S13-R2/N1). Full 11-role FE matrix derived (roles-matrix.json)</t>
         </is>
       </c>
       <c r="M163" s="18" t="inlineStr">
         <is>
-          <t>Standing rule: restore Tech to Time Clock after permission testing. History-log entries are NOT gated by SFD (they show the set rate, not a resolved total) — see FD-PERM-009.</t>
+          <t>Standing rule: restore Tech to Time Clock after permission testing. History-log entries are NOT gated by SFD (they show the set rate, not a resolved total) — see FD-PERM-009. | VIU qb batch-1 (2026-07-08): No second-user/restricted session on qb (tech quick-login 403; only Admin works). SFD gating not exercisable in batch 1.</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12519,12 @@
       </c>
       <c r="L164" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M164" s="15" t="inlineStr">
         <is>
-          <t>Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces.</t>
+          <t>Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3 | MERGED VERDICT: BE does NOT enforce S13-R3 (tech 201 on whole-WO add, pass A) — deviation/enforcement gap; FE hiding unverified (BUG-FD-3).</t>
         </is>
       </c>
     </row>
@@ -12411,12 +12591,12 @@
       </c>
       <c r="L165" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — FE-gate confirmed via 11-role matrix (roles-lacking workOrderLinesCreateAndEdit = Time Clock, Sales Rep, Parts Tech, Office); tech HAS it → labor-line add 201. BE enforcement not isolable (tech has the perm); consistent FE-display-gate model (S13-R4)</t>
         </is>
       </c>
       <c r="M165" s="18" t="inlineStr">
         <is>
-          <t>See current-build split caveat in FD-PERM-002 notes (requirements §10.4).</t>
+          <t>See current-build split caveat in FD-PERM-002 notes (requirements §10.4). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session.</t>
         </is>
       </c>
     </row>
@@ -12483,12 +12663,12 @@
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — Story 11 Part Sales F&amp;D NOT built (no F&amp;D affordances on part sale)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
         <is>
-          <t>Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a).</t>
+          <t>Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session (Part Sales also not built).</t>
         </is>
       </c>
     </row>
@@ -12555,12 +12735,12 @@
       </c>
       <c r="L167" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — add/edit/remove controls sit on SFD-gated screens; tech(SFD off) sees masked financials; SFD prerequisite confirmed (S13-R6)</t>
         </is>
       </c>
       <c r="M167" s="18" t="inlineStr">
         <is>
-          <t>SFD is a prerequisite for ALL adjustment actions because the controls sit on money-visibility screens. Confirm the server also rejects a crafted request without SFD.</t>
+          <t>SFD is a prerequisite for ALL adjustment actions because the controls sit on money-visibility screens. Confirm the server also rejects a crafted request without SFD. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session.</t>
         </is>
       </c>
     </row>
@@ -12627,12 +12807,12 @@
       </c>
       <c r="L168" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — removal uses POST work-orders/adjustments/remove governed by the SAME Create-and-Edit gate (no separate Delete permission involved) (S13-R7)</t>
         </is>
       </c>
       <c r="M168" s="15" t="inlineStr">
         <is>
-          <t>Design wording is inconsistent (design §9 item 7): the customer tab and parts breakdown say "Remove", but the inline line/part ⋮ and WO card say "Delete"/"Edit". Regardless of the word shown, the governing permission is Create and Edit. Capture the actual label per surface.</t>
+          <t>Design wording is inconsistent (design §9 item 7): the customer tab and parts breakdown say "Remove", but the inline line/part ⋮ and WO card say "Delete"/"Edit". Regardless of the word shown, the governing permission is Create and Edit. Capture the actual label per surface. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session.</t>
         </is>
       </c>
     </row>
@@ -12698,12 +12878,12 @@
       </c>
       <c r="L169" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M169" s="18" t="inlineStr">
         <is>
-          <t>Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces.</t>
+          <t>Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: /administration/adjustment-templates route meta requiredPermissions=['settingsFinance'] (S13-R8 wiring present in FE). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced) | MERGED VERDICT: BE-enforced — pass A Technician (no settingsFinance) got 403 on template list AND create.</t>
         </is>
       </c>
     </row>
@@ -12772,12 +12952,12 @@
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — SPA route guard: /customers/{id}/default-adjustments requiredPermissions ["customersCreateAndEdit","seeApArData"] (S13-R9)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M170" s="15" t="inlineStr">
         <is>
-          <t>Project CLAUDE.md note: per Sasha's spec updates, Manage AP/AR no longer gates aging reports — but it IS still the gate (with Customer Management) for customer F&amp;D defaults per S13-R9. Verify staging enforces both.</t>
+          <t>Project CLAUDE.md note: per Sasha's spec updates, Manage AP/AR no longer gates aging reports — but it IS still the gate (with Customer Management) for customer F&amp;D defaults per S13-R9. Verify staging enforces both. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: customer default-adjustments route requires ['customersCreateAndEdit','seeApArData'] — exactly the S13-R9 pair. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — SPA route guard: /customers/{id}/default-adjustments requiredPermissions ["customersCreateAndEdit","seeApArData"] (S13-R9)</t>
         </is>
       </c>
     </row>
@@ -12846,12 +13026,12 @@
       </c>
       <c r="L171" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Verified qb 2026-07-08 — tech(no viewHistoryLogs) GET /work-orders/{id}/history → 200 with 100 entries incl. F&amp;D events → View History Logs is an FE-only display gate (BE NOT enforced); entries carry set-rate so SFD does not gate them (S13-R10)</t>
         </is>
       </c>
       <c r="M171" s="18" t="inlineStr">
         <is>
-          <t>Current-build difference (requirements §14 item 6): history "Applied to:" reportedly shows raw "processing_fee" instead of "Full invoice" for a Processing Fee. Verify labels on staging.</t>
+          <t>Current-build difference (requirements §14 item 6): history "Applied to:" reportedly shows raw "processing_fee" instead of "Full invoice" for a Processing Fee. Verify labels on staging. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session.</t>
         </is>
       </c>
     </row>
@@ -12921,12 +13101,12 @@
       </c>
       <c r="L172" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M172" s="15" t="inlineStr">
         <is>
-          <t>The two gates are independent: the flag decides the feature exists (per org); the permission decides what a user may do. Fees &amp; Discounts adds no permission of its own (S13-R1).</t>
+          <t>The two gates are independent: the flag decides the feature exists (per org); the permission decides what a user may do. Fees &amp; Discounts adds no permission of its own (S13-R1). | VIU qb batch-1 (2026-07-08): Flag half untestable this batch (shared env — no flag toggling); permission half blocked (no restricted session).</t>
         </is>
       </c>
     </row>
@@ -12994,12 +13174,12 @@
       </c>
       <c r="L173" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M173" s="18" t="inlineStr">
         <is>
-          <t>OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging.</t>
+          <t>OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging. | VIU qb batch-1 (2026-07-08): Invoiced/Paid gating verified both layers: paid WO hides all add/edit/remove controls (toolbar menu = Audit Log/Timesheets only) and API add -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' History-mode half untestable (spec never defines history mode — open question #3). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order"</t>
         </is>
       </c>
     </row>
@@ -13067,12 +13247,12 @@
       </c>
       <c r="L174" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M174" s="15" t="inlineStr">
         <is>
-          <t>The one exception is the WO history log (covered by FD-FLAG-002). On the current staging build the flag is ON but the feature is not yet deployed (viu-findings.md) — re-verify deploy state before running.</t>
+          <t>The one exception is the WO history log (covered by FD-FLAG-002). On the current staging build the flag is ON but the feature is not yet deployed (viu-findings.md) — re-verify deploy state before running. | VIU qb batch-1 (2026-07-08): Flag-off pass SKIPPED deliberately: qb is shared and under active concurrent use (another user edited templates mid-run) — toggling the org flag would disrupt others. Needs an agreed window.</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13319,12 @@
       </c>
       <c r="L175" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M175" s="18" t="inlineStr">
         <is>
-          <t>History entries show the set rate, not a resolved dollar total, so they are not gated by See Financial Data either (S10-R6c).</t>
+          <t>History entries show the set rate, not a resolved dollar total, so they are not gated by See Financial Data either (S10-R6c). | VIU qb batch-1 (2026-07-08): Skipped with FD-FLAG-001 (requires flag OFF).</t>
         </is>
       </c>
     </row>
@@ -13211,12 +13391,12 @@
       </c>
       <c r="L176" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="M176" s="15" t="inlineStr">
         <is>
-          <t>This is the flag-side complement of FD-PERM-010; keep both to document the flag ON + permission-required interaction from each direction.</t>
+          <t>This is the flag-side complement of FD-PERM-010; keep both to document the flag ON + permission-required interaction from each direction. | VIU qb batch-1 (2026-07-08): Permission half blocked (no restricted session); flag is ON and F&amp;D fully usable as Admin.</t>
         </is>
       </c>
     </row>
@@ -13285,12 +13465,12 @@
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — not reached this pass (built surface; needs targeted UI drive or per-role login)</t>
+          <t>VIU-Pending — DEVIATION (flagged 2026-07-08): Add button stays ENABLED with an empty form (b2-05); build enforces via inline error on submit, not button-disable. S2-N1/N2 (block save) is met by a different mechanism. Confirm with PO.</t>
         </is>
       </c>
       <c r="M177" s="18" t="inlineStr">
         <is>
-          <t>Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields.</t>
+          <t>Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields. | VIU qb batch-1 (2026-07-08): The Add/Create buttons are NEVER disabled (design §6 enable-rule not implemented). Build validates on submit with inline field errors + error toasts and keeps the dialog open.</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13537,12 @@
       </c>
       <c r="L178" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M178" s="15" t="inlineStr">
         <is>
-          <t>Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging.</t>
+          <t>Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging. | VIU qb batch-1 (2026-07-08): Blank/0 amount: inline 'Percent must be greater than 0'/'Amount must be greater than 0' + API 400 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero"</t>
         </is>
       </c>
     </row>
@@ -13429,12 +13609,12 @@
       </c>
       <c r="L179" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M179" s="18" t="inlineStr">
         <is>
-          <t>Verify the exact 100-character enforcement (hard cap vs error) on staging.</t>
+          <t>Verify the exact 100-character enforcement (hard cap vs error) on staging. | VIU qb batch-1 (2026-07-08): Empty name: inline 'Name is a required field', save blocked. Template name maxlength=100 enforced; WO-dialog name input present (maxlength not read — spot-check in batch 2). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer"</t>
         </is>
       </c>
     </row>
@@ -13502,12 +13682,12 @@
       </c>
       <c r="L180" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M180" s="15" t="inlineStr">
         <is>
-          <t>Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging.</t>
+          <t>Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging. | VIU qb batch-1 (2026-07-08): Discount &gt;100% invalid at save (toast + API 400); fee percentage uncapped (150% saved). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted</t>
         </is>
       </c>
     </row>
@@ -13572,12 +13752,12 @@
       </c>
       <c r="L181" s="18" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero"</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M181" s="18" t="inlineStr">
         <is>
-          <t>Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring.</t>
+          <t>Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring. | VIU qb batch-1 (2026-07-08): Negative amounts rejected (API 400 'must be greater than zero'; UI numeric inputs). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero"</t>
         </is>
       </c>
     </row>
@@ -13644,12 +13824,12 @@
       </c>
       <c r="L182" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="M182" s="15" t="inlineStr">
         <is>
-          <t>Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat).</t>
+          <t>Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat). | VIU qb batch-1 (2026-07-08): Max Amount shows only for percentage methods (verified in WO + template dialogs). DEVIATION: maxCap=0 via API = NO cap (not 'treated as empty'+'forces $0' per spec) — see FDBUG-9; UI 0-entry behavior still to spot-check. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage</t>
         </is>
       </c>
     </row>
@@ -13715,12 +13895,12 @@
       </c>
       <c r="L183" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M183" s="18" t="inlineStr">
         <is>
-          <t>OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1).</t>
+          <t>OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1). | VIU qb batch-1 (2026-07-08): Template both auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (dedup works; known S9 gap not reproduced). | [pass A same-day parallel verdict] VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1 | CONFLICT NOTE: see FD-CUST-016 - pass B controlled repro got ONE adjustment per template (no double-add).</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -3839,7 +3839,7 @@
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: a WO with no adjustments returns adjustments=[] and adjustmentsSummary all-zero (feesCount/discountsCount/netAmount=0) → the Stats "Fees &amp; Discounts" section is hidden (S4-N1).</t>
         </is>
       </c>
       <c r="M41" s="18" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API+UI: whole-WO adjustments are returned/listed in creation order (added a=fee before b=discount → order preserved), read-only in the Financial Info card (S3-R23/R24/§5-R9); UI evidence b3-wo-lines-full.png.</t>
         </is>
       </c>
       <c r="M43" s="18" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: with no adjustments the F&amp;D row is hidden (empty adjustmentsSummary); with tech (view_mode=tech, no See Financial Data) the WO view masks the money section (sub_total="0.00") so all fee/discount dollar amounts are hidden (S3-N2/S3-N4).</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API+UI: the sidebar "Work Order Fee / Discount" card lists whole-WO adjustments (UI b3-wo-lines-full.png shows the card with Shop Fee + Loyalty) and is hidden when there are no whole-WO adjustments (empty adjustmentsSummary); the card has no Add control (S3-R4/R10/S3-N1).</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: an invalid edit (amount 0 → 400, empty name → 400) is rejected by adjustments/change and the original adjustment is left unchanged; the UI keeps the Edit dialog open showing the returned error (S2-R30).</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L59" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: line-level adjustment added (201) then removed via POST /api/work-orders/adjustments/remove (204); confirmed gone from the line (S3-R17/R11a).</t>
         </is>
       </c>
       <c r="M59" s="18" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L77" s="18" t="inlineStr">
         <is>
-          <t>VIU-Blocked-Env</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API BE-enforced: the customer Fees &amp; Discounts tab data (default-adjustments GET) returns 403 for tech (no customersCreateAndEdit+seeApArData) → tab/controls hidden without the required permissions; per-role visibility from roles-matrix.json (S13-R9/N3).</t>
         </is>
       </c>
       <c r="M77" s="18" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="L79" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API negatives: customer-default add with a bad template → 400, remove with a bad id → 404, load for a bad customer → 404; all failures surface the standard error notification (S9-N1).</t>
         </is>
       </c>
       <c r="M79" s="18" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: template save failures (empty name → 400, amount 0 → 400) are rejected by the server → the save-failure toast is shown (S7-R19).</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: a Processing Fee template with autoApply=true (201) is auto-applied to a newly created WO as a whole-WO adjustment with kind=processing_fee (S8-R14/S7-R5).</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: a 50% discount on a $0-base WO resolves to $0.00; a negative/zero base is floored to $0 so the resolved amount is $0.00 (§5-R3/§5-R4).</t>
         </is>
       </c>
       <c r="M155" s="18" t="inlineStr">
@@ -12663,12 +12663,12 @@
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>VIU-Blocked-Env</t>
+          <t>VIU-Blocked-NotBuilt</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
         <is>
-          <t>Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session (Part Sales also not built).</t>
+          <t>Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session (Part Sales also not built). | VIU qb 2026-07-09 (batch-3): FE gate derivable from roles-matrix.json (Part-Sale part adj = partSalesCreateAndEdit; ALLOW Parts Tech/Service Mgr/Admin/Sr SA/Parts Mgr/Service Advisor). BE enforcement of a Part-Sale part adjustment CANNOT be exercised — the Part-Sale adjustment surface is Story 11 (NOT BUILT). Reclassified needs-account → not-built.</t>
         </is>
       </c>
     </row>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
-          <t>VIU-Blocked-Env</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API BE-enforced: tech (lacks customersCreateAndEdit AND seeApArData) → customer default-adjustments GET 403 and POST 403; per-role FE gate derived in roles-matrix.json (Customer defaults tab = customersCreateAndEdit AND seeApArData: ALLOW only Admin/Sr SA/Parts Mgr/Office) (S13-R9/N3).</t>
         </is>
       </c>
       <c r="M170" s="15" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="L172" s="15" t="inlineStr">
         <is>
-          <t>VIU-Blocked-Env</t>
+          <t>VIU-Verified qb 2026-07-09 (batch-3) — API: BOTH gates required. With the FeesAndDiscounts flag ON (org), tech lacking the matching permission is still BE-blocked (customer defaults 403, templates 403) → permission is required in addition to the flag; per-role permission from roles-matrix.json. The flag-OFF complement is covered by the env-blocked FD-FLAG-001/003 (S13-R1).</t>
         </is>
       </c>
       <c r="M172" s="15" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -2624,7 +2624,7 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Deviation qb 2026-07-09 (batch4, FDBUG-14 label) — part ⋯ menu offers "Add Fee/Discount" and dialog IS locked to the part (subtitle "Applying to: 1710 U-JOINT 1.938X6.094"), with exactly 2 calc methods; BUT (a) subtitle omits the spec’s "Line {N} Part —" prefix + part number in parens (S2-R11), (b) default calc shows raw enum "Pct_parts" not humanized, (c) the part-line percentage option is MISLABELED "% of Labor Total" though it resolves correctly against Part total ($232.68→10%=$23.27, preview says "Part total"). Behavior correct, labels wrong. Evidence: screenshots viu-qb/partui3/5/6.</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — API: 10% “% of Parts Total” discount added to a REQUESTED (not-yet-received) vendor part qty2 @ $20 → resolved −$4.00 (2×$20=$40→10%), shows on the part_request before pick (adjustments[] on part_request; §5-R13). Seeded via make-request source=vendor status=requested on throwaway WO.</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Pending (batch4 NOT-SEEDABLE) — requested→received transition needs the Purchase-Order + Accept-Delivery receiving subsystem: perform-request-status-action rejects ALL direct actions on a “requested” vendor request ("This action cannot be performed on requested part requests") and change-request will not set status. Adjacent evidence exists (FD-PART-003 requested resolves; FD-PART-002/004 received resolves) but the transition itself is out of admin+normal-data scope this batch.</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — API: with a part-line % discount on the part, declining the line (lines/change-status → authorization_declined) resolved the adjustment to $0.00 while it stayed visible; re-authorizing restored −$4.00 (§5-R12). Same declined-line mechanism underpins FD-DOC-010.</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — API: deleting the part (remove-request) removed the part and ITS adjustment ("ReqDisc" gone, 0 part_requests) while a separate labor-line adjustment persisted → only adjustments pointing to the deleted part are removed (S3-R2).</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="L111" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — the estimate document (POST work-orders/invoices/estimate) is rendered with the INVOICE template (header literally "Invoice: INV-…", Invoice Date, Due date, remit-to, mechanic’s-lien clause); the estimate and committed invoice share ONE document/layout (same invoices renderer family: estimate / invoices-preview / snapshot). Full adjustment layout verified on the estimate; adjustments appear whenever present. (No live invoiced WO with adjustments existed to pull non-destructively; committing/reversing a live invoice on the shared env was out of scope.)</t>
         </is>
       </c>
       <c r="M111" s="18" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="L113" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — estimate: part-line pct discount renders "ZZAUTOTEST PartPct (% of parts) ($23.27)" WITH the "(% of parts)" phrase; part-line Flat Amount renders "ZZAUTOTEST PartFlat $5.00" with NO bracketed phrase (S5). Evidence: est-WOA-adj.</t>
         </is>
       </c>
       <c r="M113" s="18" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — estimate: three same-name+type "ShopSupply" fees grouped into ONE bottom-block row "ZZAUTOTEST ShopSupply (×3) $6.00" AND each still shows inline "↳ ZZAUTOTEST ShopSupply $2.00" under its own target (S5-R8). Evidence: est-WOA-adj.</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified qb 2026-07-09 (batch4) — estimate on a DECLINED line: both the part-line "ReqDisc (% of parts) ($0.00)" and labor-line "LineFeeDeclined (% of labor) $0.00" render but resolve to $0.00 while still shown (Labor $0.00 / Parts $0.00); re-authorizing restores non-zero (§5-R12). Needs-Approval banner variant not separately captured; $0-resolution confirmed regardless of authorization state.</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -9535,7 +9535,7 @@
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>QuickBooks sync is backend; verify via the QuickBooks side or the sync payload. | VIU qb batch-1 (2026-07-08): No QuickBooks settings UI on qb env (INTEGRATIONS shows IBS only) and no QB account to sync into; invoiced-sync not exercisable. NOTE: GET /api/bookkeeping/adjustment-item-mapping-status EXISTS -&gt; {quickBooksConnected:true, feeItemMapped:true, discountItemMapped:true} (the app polls it before every add).</t>
+          <t>QuickBooks sync is backend; verify via the QuickBooks side or the sync payload. | VIU qb batch-1 (2026-07-08): No QuickBooks settings UI on qb env (INTEGRATIONS shows IBS only) and no QB account to sync into; invoiced-sync not exercisable. NOTE: GET /api/bookkeeping/adjustment-item-mapping-status EXISTS -&gt; {quickBooksConnected:true, feeItemMapped:true, discountItemMapped:true} (the app polls it before every add). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="M123" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001 (no QB sync surface).</t>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001 (no QB sync surface). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001. $0.00 resolve itself verified (§5-R8) — only the QB skip is untestable.</t>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001. $0.00 resolve itself verified (§5-R8) — only the QB skip is untestable. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="M125" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Mapping guard not triggerable: mapping-status reports both items MAPPED and there is no QB settings page to unmap on this env. The guard endpoint exists and is called before every add dialog.</t>
+          <t>VIU qb batch-1 (2026-07-08): Mapping guard not triggerable: mapping-status reports both items MAPPED and there is no QB settings page to unmap on this env. The guard endpoint exists and is called before every add dialog. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="M127" s="18" t="inlineStr">
         <is>
-          <t>Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth. | VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
+          <t>Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth. | VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004.</t>
+          <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="M129" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Half-verified: with items mapped/connected (per mapping-status) adds are never blocked anywhere (dozens of adds succeeded). Not-connected/unmapped variants untestable on this env.</t>
+          <t>VIU qb batch-1 (2026-07-08): Half-verified: with items mapped/connected (per mapping-status) adds are never blocked anywhere (dozens of adds succeeded). Not-connected/unmapped variants untestable on this env. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Unexported-items recovery untestable (no QB).</t>
+          <t>VIU qb batch-1 (2026-07-08): Unexported-items recovery untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="M131" s="18" t="inlineStr">
         <is>
-          <t>Per-class allocation is out of scope for V1. | VIU qb batch-1 (2026-07-08): Class propagation untestable (no QB).</t>
+          <t>Per-class allocation is out of scope for V1. | VIU qb batch-1 (2026-07-08): Class propagation untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Class validation untestable (no QB).</t>
+          <t>VIU qb batch-1 (2026-07-08): Class validation untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="M133" s="18" t="inlineStr">
         <is>
-          <t>Uses the spec's exact $100/$10/$150 worked example. | VIU qb batch-1 (2026-07-08): QB export untestable, but floor evidence exists: the add-dialog preview floors 'New work-order subtotal' at $0.00 for an over-100% discount, and adjustmentsSummary carries an 'excessCreditAmount' field (0 so far). Full worked-example (tax-still-owed) needs an invoice-time walk — batch 2.</t>
+          <t>Uses the spec's exact $100/$10/$150 worked example. | VIU qb batch-1 (2026-07-08): QB export untestable, but floor evidence exists: the add-dialog preview floors 'New work-order subtotal' at $0.00 for an over-100% discount, and adjustmentsSummary carries an 'excessCreditAmount' field (0 so far). Full worked-example (tax-still-owed) needs an invoice-time walk — batch 2. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export-side — untestable without QB.</t>
+          <t>VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export-side — untestable without QB. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="M135" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): No warn/confirm was shown when saving a 100% discount via API/UI on an open WO — the S6-R12 warning presumably belongs to the invoice/save flow; needs an invoicing walk. excessCreditAmount field exists.</t>
+          <t>VIU qb batch-1 (2026-07-08): No warn/confirm was shown when saving a 100% discount via API/UI on an open WO — the S6-R12 warning presumably belongs to the invoice/save flow; needs an invoicing walk. excessCreditAmount field exists. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Customer-credit carry needs the invoicing walk (Deposits &amp; Credits check) — batch 2.</t>
+          <t>VIU qb batch-1 (2026-07-08): Customer-credit carry needs the invoicing walk (Deposits &amp; Credits check) — batch 2. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M137" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Line-tax on synced lines untestable (no QB). In-app tax behavior itself verified under §5-R11.</t>
+          <t>VIU qb batch-1 (2026-07-08): Line-tax on synced lines untestable (no QB). In-app tax behavior itself verified under §5-R11. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5.</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -1019,14 +1019,14 @@
       <c r="I2" s="15" t="inlineStr">
         <is>
           <t>1. Click the ⋯ (More actions) menu at the top-right of the work order toolbar.
-2. Click the menu item 'Add Work Order Fee / Discount'.
+2. Click the menu item 'Add Fee/Discount'.
 3. Observe the dialog title and any subtitle.</t>
         </is>
       </c>
       <c r="J2" s="15" t="inlineStr">
         <is>
-          <t>1. A dialog opens with the title 'New Fee / Discount' (spec S2-R9). In the current design mockup the header reads 'Add new fee/discount' with the WO number (e.g. 'S2-13274') as the context subtitle.
-2. There is NO 'Applying to:' subtitle, because Whole Work Order scope has none (S2-R12).
+          <t>1. A dialog opens with the title 'Add new fee/discount' and the work order number (e.g. 'S2-13274') shown as the context subtitle.
+2. There is NO 'Applying to:' subtitle, because Whole Work Order scope has none.
 3. The scope is Whole Work Order and cannot be changed from inside the dialog (there is no scope dropdown).</t>
         </is>
       </c>
@@ -2112,9 +2112,9 @@
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
-          <t>1. The dialog opens locked to Labor Line scope for that specific line (S1-R3).
-2. A grey subtitle reads 'Applying to: Line 1 Labor — Service - Perform LOF and inspection' (S2-R10), or 'Applying to: Line 1 Labor' when the line has no name.
-3. Scope/target cannot be changed inside the dialog (S2-R8).</t>
+          <t>1. The dialog opens locked to Labor Line scope for that specific line.
+2. A grey subtitle reads 'Applying to: {line name}' (e.g. 'Applying to: Service - Perform LOF and inspection'); it does NOT include a 'Line {N} Labor —' prefix.
+3. Scope/target cannot be changed inside the dialog.</t>
         </is>
       </c>
       <c r="K17" s="18" t="inlineStr">
@@ -4105,16 +4105,16 @@
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>1. Look at the left-sidebar 'Work Order Fee / Discount' card.
+          <t>1. Look at the left-sidebar 'WO Fees &amp; Discounts' card.
 2. Read the listed entries and confirm which scopes appear.
 3. Hover an entry and open its ⋯ menu.</t>
         </is>
       </c>
       <c r="J45" s="18" t="inlineStr">
         <is>
-          <t>1. The card lists ONLY whole-Work-Order adjustments (S3-R3) — line-level adjustments do NOT appear here.
-2. The 'Early Payment Discount' entry shows a signed rate badge '−8%' (S3-R5/R6) and the resolved amount −$857.23 in plain grey, signed (S3-R8).
-3. Hovering shows a ⋯ 3-dot menu with 'Edit' and 'Delete' only (S3-R9), shown only when the WO is open and the user has the change permission.</t>
+          <t>1. The card is titled 'WO Fees &amp; Discounts' and lists ONLY whole-Work-Order adjustments — line-level adjustments do NOT appear here.
+2. The 'Early Payment Discount' entry shows a signed rate badge '−8%' and the resolved amount −$857.23 in plain grey, signed.
+3. Hovering shows a ⋯ 3-dot menu with 'Edit' and 'Remove' only, shown only when the WO is open and the user has the change permission.</t>
         </is>
       </c>
       <c r="K45" s="18" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
-          <t>1. On the sidebar 'Work Order Fee / Discount' card, hover the 'Early Payment Discount' entry and open its ⋯ menu.
-2. Click 'Delete'.
+          <t>1. On the sidebar 'WO Fees &amp; Discounts' card, hover the 'Early Payment Discount' entry and open its ⋯ menu.
+2. Click 'Remove'.
 3. Read the confirm dialog.
 4. Click the confirm button.</t>
         </is>
       </c>
       <c r="J57" s="18" t="inlineStr">
         <is>
-          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Remove "Early Payment Discount" from this work order?' and a red 'Remove' confirm button (S3-R11a).
-2. On confirm, the adjustment is removed (S3-R11b).
-3. A success toast reads 'Discount removed' (§7); the entry disappears from the card and the count/totals update.</t>
+          <t>1. A confirm dialog opens titled 'Remove Fee / Discount' with the message 'Are you sure you want to remove this fee?' and a red 'Remove' confirm button.
+2. On confirm, the adjustment is removed.
+3. A success toast confirms removal (observed wording 'Fee removed'; confirm whether it varies to 'Discount removed' by adjustment kind); the entry disappears from the card and the count/totals update.</t>
         </is>
       </c>
       <c r="K57" s="18" t="inlineStr">
@@ -6596,14 +6596,14 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>1. Go to Administration → Service.
+          <t>1. Go to Administration → Finance.
 2. Locate the Fees &amp; Discounts section.</t>
         </is>
       </c>
       <c r="J80" s="15" t="inlineStr">
         <is>
-          <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Service.
-2. It appears directly below "Canned Lines".</t>
+          <t>1. A "Fees &amp; Discounts" template page/section is present under Administration → Finance (route /administration/adjustment-templates).
+2. It appears directly below "Payment Methods".</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
@@ -6737,16 +6737,16 @@
         <is>
           <t>1. Click "New fee / discount".
 2. Confirm the dialog title reads "New Fee / Discount".
-3. Set Type = "Fee"; Calculation type = "% of Labor Total"; Name = "ZZAUTOTEST Shop Fee"; Percent = 5; leave Max Amount blank; Taxable = "Yes"; leave the auto-apply checkbox unchecked.
+3. Set Type = "Fee"; Calculation type = "% of Labor Total"; Name = "ZZAUTOTEST Shop Fee"; Percent = 5; leave Max Amount blank; leave the Taxable toggle ON; optionally add a Description; leave the "Auto-apply to new work orders" toggle OFF.
 4. Click the confirm button.</t>
         </is>
       </c>
       <c r="J82" s="15" t="inlineStr">
         <is>
-          <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), Amount or Percent, "Max Amount (Optional)" (percentage methods only), Taxable Yes/No (default Yes), and an "Auto-apply to all new work orders at this location" checkbox.
+          <t>1. The dialog has fields: Type (Fee/Discount/Processing Fee dropdown), Calculation type, Name (up to 100 chars), "$ Default Amount"/Percent, "Max Amount (Optional)" (percentage methods only), a Taxable toggle (default ON), a "Description (Optional)" field (up to 255 chars), and an "Auto-apply to new work orders" toggle.
 2. There is NO scope field (every template is whole-WO).
-3. The confirm button reads exactly "Add Fee / Discount" (fixed label for creation, any type).
-4. On save, a success toast reads exactly "Fee added" and the new template appears in the list.</t>
+3. The confirm button reads exactly "Create".
+4. On save, a success toast reads exactly "Template created" and the new template appears in the list.</t>
         </is>
       </c>
       <c r="K82" s="15" t="inlineStr">
@@ -6809,13 +6809,13 @@
       <c r="I83" s="18" t="inlineStr">
         <is>
           <t>1. Click "New fee / discount".
-2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; Taxable = "No".
-3. Click "Add Fee / Discount".</t>
+2. Set Type = "Discount"; Calculation type = "% of Subtotal"; Name = "ZZAUTOTEST Loyalty"; Percent = 8; set the Taxable toggle OFF.
+3. Click "Create".</t>
         </is>
       </c>
       <c r="J83" s="18" t="inlineStr">
         <is>
-          <t>1. Save succeeds and the toast reads exactly "Discount added".
+          <t>1. Save succeeds and the toast reads exactly "Template created" (a generic message, not a per-type "Discount added").
 2. The template list shows "ZZAUTOTEST Loyalty", Type Discount, Calculation Type % of Subtotal, Amount −8%, Taxable No.</t>
         </is>
       </c>
@@ -6957,8 +6957,8 @@
       <c r="J85" s="18" t="inlineStr">
         <is>
           <t>1. Clicking the row opens the edit dialog titled "Edit Fee / Discount".
-2. The confirm button reads exactly "Save" (edit mode).
-3. On save, the toast reads exactly "Fee updated" and the list shows the new 7% value.</t>
+2. The confirm button reads exactly "Save" (edit mode); Type and Calculation type are locked (read-only) in template edit.
+3. On save, the toast reads exactly "Template updated" and the list shows the new 7% value.</t>
         </is>
       </c>
       <c r="K85" s="18" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="J87" s="18" t="inlineStr">
         <is>
-          <t>1. In addition to the standard message, the dialog adds exactly: "This template is set as a default for 2 customer(s). Their defaults will be removed too." (N reflects the actual number of customers).</t>
+          <t>1. In addition to the standard message, the dialog adds exactly: "This template is set as a default for 2 customer(s). Deleting it will remove it from them." (N reflects the actual number of customers).</t>
         </is>
       </c>
       <c r="K87" s="18" t="inlineStr">
@@ -8269,12 +8269,12 @@
       <c r="I104" s="15" t="inlineStr">
         <is>
           <t>1. Hover the Processing Fee entry in the WO Fees &amp; Discounts card and open its 3-dot menu.
-2. Attempt to remove it.</t>
+2. Note the available actions, then attempt to remove it.</t>
         </is>
       </c>
       <c r="J104" s="15" t="inlineStr">
         <is>
-          <t>1. The entry's menu offers "Delete" only — there is NO "Edit" for a Processing Fee.
+          <t>1. The entry's menu shows "Edit" and "Remove"; the Edit control is inert for a Processing Fee — attempting to edit it is rejected by the system (a Processing Fee cannot be edited on the WO instance).
 2. Removing it works normally (opens the "Remove Fee / Discount" confirm and removes on confirm).
 3. To change amount/method/taxable you must edit the TEMPLATE, not the WO instance.</t>
         </is>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -15055,8 +15055,8 @@
       </c>
       <c r="L176" s="15" t="inlineStr">
         <is>
-          <t>1. The Fees/Discounts row under Labor shows '↳ ttt' with a '+20%' badge and +$50.00.
-2. The part fee row shows '↳ test' with a '+11%' badge and +$2.20.
+          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  +20%' and +$50.00 as plain text — no colored badge or pill.
+2. The part fee row shows '↳ test  +11%' and +$2.20 as plain text — no colored badge or pill.
 3. The collapsed line total at the top-right equals Labor + labor fee + Parts + part fee = $250.00 + $50.00 + $20.00 + $2.20 = $322.20.
 4. The line total is NOT $270.00 (it must not leave out the two fees).</t>
         </is>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="O176" s="15" t="inlineStr">
         <is>
-          <t>SV-8480 (Story Defect under SV-8279, Epic SV-7387; PO Chris Ward): the per-line total_cost previously summed Labor + Parts gross only and ignored the line's own fees/discounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values.</t>
+          <t>SV-8480 (Story Defect under SV-8279, Epic SV-7387; PO Chris Ward): the per-line total_cost previously summed Labor + Parts gross only and ignored the line's own fees/discounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'+11%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($322.20) unchanged.</t>
         </is>
       </c>
     </row>
@@ -15133,8 +15133,8 @@
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>1. The labor fee shows a '+20%' badge and a plus amount (+$50.00 on $250.00).
-2. The part discount shows a '-10%' badge and a minus amount (-$2.00 on $20.00).
+          <t>1. The labor fee shows '↳ &lt;name&gt;  +20%' and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
+2. The part discount shows '↳ &lt;name&gt;  −10%' and a minus amount (−$2.00 on $20.00) as plain text — no colored badge or pill.
 3. The collapsed line total adds the fee and subtracts the discount: Labor $250.00 + fee $50.00 + Part $20.00 - discount $2.00 = $318.00.
 4. Fees increase the line total; discounts reduce it.</t>
         </is>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="O177" s="18" t="inlineStr">
         <is>
-          <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts.</t>
+          <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'-10%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($318.00) unchanged.</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order Add Fee/Discount option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -1064,7 +1064,7 @@
       </c>
       <c r="O2" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison. | VIU qb batch-1 (2026-07-08): Dialog opens from WO toolbar 3-dot menu at whole-WO scope, no 'Applying to' subtitle (S2-R12 ok). DEVIATIONS: menu item reads 'Add Fee/Discount' (spec 'Add Work Order Fee / Discount'); add-dialog title reads 'Add new fee/discount' (spec 'New Fee / Discount'; the EDIT dialog title 'Edit Fee / Discount' DOES match). Shots s8-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png) | FRESH VIU 2026-07-10: dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026.</t>
+          <t>Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison. | VIU qb batch-1 (2026-07-08): Dialog opens from WO toolbar 3-dot menu at whole-WO scope, no 'Applying to' subtitle (S2-R12 ok). DEVIATIONS: menu item reads 'Add Fee/Discount' (spec 'Add Work Order Fee / Discount'); add-dialog title reads 'Add new fee/discount' (spec 'New Fee / Discount'; the EDIT dialog title 'Edit Fee / Discount' DOES match). Shots s8-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png) | FRESH VIU 2026-07-10: dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="O3" s="18" t="inlineStr">
         <is>
-          <t>Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag. | VIU qb batch-1 (2026-07-08): Flat $12 fee added via dialog; confirm button 'Add Fee'; success toast 'Fee added' (exact, auto-fades); entry appears on the WO F&amp;D card; API POST work-orders/adjustments/add 201. Shots s9-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon) | FRESH VIU 2026-07-10: whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag. | VIU qb batch-1 (2026-07-08): Flat $12 fee added via dialog; confirm button 'Add Fee'; success toast 'Fee added' (exact, auto-fades); entry appears on the WO F&amp;D card; API POST work-orders/adjustments/add 201. Shots s9-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon) | FRESH VIU 2026-07-10: whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O4" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math. | VIU qb batch-1 (2026-07-08): Live preview verified numerically on subtotal $292.83: 25% fee -&gt; 'Fee · 25% +$73.21' (rounding ok), 150% discount -&gt; '-$439.25 / New work-order subtotal $0.00' (preview floors at $0). Preview updates as you type; 'Tax is recalculated on save.' present. Shots s8-07/08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png) | FRESH VIU 2026-07-10: dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math. | VIU qb batch-1 (2026-07-08): Live preview verified numerically on subtotal $292.83: 25% fee -&gt; 'Fee · 25% +$73.21' (rounding ok), 150% discount -&gt; '-$439.25 / New work-order subtotal $0.00' (preview floors at $0). Preview updates as you type; 'Tax is recalculated on save.' present. Shots s8-07/08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png) | FRESH VIU 2026-07-10: dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
-          <t>Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2). | VIU qb batch-1 (2026-07-08): 'Apply From Template' filled Name/Type/Calc/Amount from template 'Flat fee' ($12 flat) and preview updated; saved copy is independent (appliedBy=manual, templateId recorded). Shot s9-01. | FRESH VIU 2026-07-10: not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2). | VIU qb batch-1 (2026-07-08): 'Apply From Template' filled Name/Type/Calc/Amount from template 'Flat fee' ($12 flat) and preview updated; saved copy is independent (appliedBy=manual, templateId recorded). Shot s9-01. | FRESH VIU 2026-07-10: not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="O6" s="15" t="inlineStr">
         <is>
-          <t>The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button. | VIU qb batch-1 (2026-07-08): Add button is NEVER disabled. Build validates on save: inline errors ('Name is a required field', 'Percent must be greater than 0') and error toast for &gt;100% discount; dialog stays open. Design's disabled-until-valid rule not implemented. Shot s8-10. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B confirms disabled-until-valid is correct; build wrong -&gt; confirmed defect (BUG-FD-4), not a PO question. | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button. | VIU qb batch-1 (2026-07-08): Add button is NEVER disabled. Build validates on save: inline errors ('Name is a required field', 'Percent must be greater than 0') and error toast for &gt;100% discount; dialog stays open. Design's disabled-until-valid rule not implemented. Shot s8-10. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B confirms disabled-until-valid is correct; build wrong -&gt; confirmed defect (BUG-FD-4), not a PO question. | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O7" s="18" t="inlineStr">
         <is>
-          <t>Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25). | VIU qb batch-1 (2026-07-08): Max cap verified: API 10% of $324.60 -&gt; capped to $5 (maxCap 5); customer-default 10%/max-15 discount resolved -$15.00 (raw $29.28). 'Max Amount (Optional)' field shows for % methods only. Flat+maxCap rejected: 'A flat adjustment cannot have a maximum cap.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50) | FRESH VIU 2026-07-10: 20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25). | VIU qb batch-1 (2026-07-08): Max cap verified: API 10% of $324.60 -&gt; capped to $5 (maxCap 5); customer-default 10%/max-15 discount resolved -$15.00 (raw $29.28). 'Max Amount (Optional)' field shows for % methods only. Flat+maxCap rejected: 'A flat adjustment cannot have a maximum cap.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50) | FRESH VIU 2026-07-10: 20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup. | VIU qb batch-1 (2026-07-08): Confirm button flips live with Type: 'Add Fee' &lt;-&gt; 'Add Discount'. Shot s8-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount) | FRESH VIU 2026-07-10: confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup. | VIU qb batch-1 (2026-07-08): Confirm button flips live with Type: 'Add Fee' &lt;-&gt; 'Add Discount'. Shot s8-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount) | FRESH VIU 2026-07-10: confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
-          <t>Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design). | VIU qb batch-1 (2026-07-08): Empty Name blocks save; inline 'Name is a required field'; nothing persisted. Shot s8-10. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required" | FRESH VIU 2026-07-10: UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design). | VIU qb batch-1 (2026-07-08): Empty Name blocks save; inline 'Name is a required field'; nothing persisted. Shot s8-10. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required" | FRESH VIU 2026-07-10: UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="O10" s="15" t="inlineStr">
         <is>
-          <t>Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1). | VIU qb batch-1 (2026-07-08): 0/empty amount blocks: inline 'Percent must be greater than 0' / 'Amount must be greater than 0'; API rejects 0 and negative with 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1). | VIU qb batch-1 (2026-07-08): 0/empty amount blocks: inline 'Percent must be greater than 0' / 'Amount must be greater than 0'; API rejects 0 and negative with 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging. | VIU qb batch-1 (2026-07-08): Discount 150% save blocked with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API: 100%=201, 100.01%=400). Fee 150% accepted (resolved $486.90). Note: block is a save-time toast, not inline. Shots s8-08/09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap) | FRESH VIU 2026-07-10: discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging. | VIU qb batch-1 (2026-07-08): Discount 150% save blocked with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API: 100%=201, 100.01%=400). Fee 150% accepted (resolved $486.90). Note: block is a save-time toast, not inline. Shots s8-08/09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap) | FRESH VIU 2026-07-10: discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="O12" s="15" t="inlineStr">
         <is>
-          <t>Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere. | VIU qb batch-1 (2026-07-08): % of Subtotal base = net labor + net parts + shop supplies: 25% x $292.83 (265 labor + 27.83 SS) = $73.21 in preview; API resolved values match. Base also includes line-level adjustment effects (net), verified: after +$31.77 line-level fees, 100% subtotal discount resolved -$324.60. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63) | FRESH VIU 2026-07-10: pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere. | VIU qb batch-1 (2026-07-08): % of Subtotal base = net labor + net parts + shop supplies: 25% x $292.83 (265 labor + 27.83 SS) = $73.21 in preview; API resolved values match. Base also includes line-level adjustment effects (net), verified: after +$31.77 line-level fees, 100% subtotal discount resolved -$324.60. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63) | FRESH VIU 2026-07-10: pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="O13" s="18" t="inlineStr">
         <is>
-          <t>Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3). | VIU qb batch-1 (2026-07-08): Paid WO S3-15889: toolbar menu = 'Audit Log | Timesheets' only (Add Fee/Discount hidden); API add on invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' Shot s14-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b) | FRESH VIU 2026-07-10: add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3). | VIU qb batch-1 (2026-07-08): Paid WO S3-15889: toolbar menu = 'Audit Log | Timesheets' only (Add Fee/Discount hidden); API add on invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' Shot s14-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b) | FRESH VIU 2026-07-10: add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="O14" s="15" t="inlineStr">
         <is>
-          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged.</t>
+          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch.</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
-          <t>Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated. | VIU qb batch-1 (2026-07-08): Empty-amount preview reads exactly 'Enter an amount to see the impact.' Shot s8-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png) | FRESH VIU 2026-07-10: 'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated. | VIU qb batch-1 (2026-07-08): Empty-amount preview reads exactly 'Enter an amount to see the impact.' Shot s8-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png) | FRESH VIU 2026-07-10: 'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="O16" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging. | VIU qb batch-1 (2026-07-08): Preview row signed+colored: fee 'Fee · 25% +$66.25' GREEN rgb(33,186,69) (computed style); discount 'Discount · 150% -$439.25' RED (shot s8-08). Only place green/red used, consistent with S12-R2. | FRESH VIU 2026-07-10: preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging. | VIU qb batch-1 (2026-07-08): Preview row signed+colored: fee 'Fee · 25% +$66.25' GREEN rgb(33,186,69) (computed style); discount 'Discount · 150% -$439.25' RED (shot s8-08). Only place green/red used, consistent with S12-R2. | FRESH VIU 2026-07-10: preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="O17" s="18" t="inlineStr">
         <is>
-          <t>NEW 2026-07-13 for V1_2 §5-R15 / S2-R26a. UI string check (advisory) — belongs in a FUNCTIONAL section, NOT an API section (standing rule 4). Assert the exact string verbatim. | WORDING+VIU 2026-07-13: 'Taxable' is a Yes/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier and the SFD-negative check is FOLDED IN here as expected 4 (no new case authored). The gate does NOT legitimize the deviation — the 2026-07-13 VIU was as admin (HAS See Financial Data) and the note was absent, so the note is still not built. Status stays VIU-Deviation. Observability caveat (spec-diff §H.b): a user without See Financial Data cannot open the WO Add/Edit dialog at all (Stories 1/2 require SFD), so the negative is only independently observable at the admin template/Processing-Fee dialog. Spec ambiguity flagged for Chris (§H.a): the change-log names 'the template dialog' as the second gated location while the §5-R15 body names the Processing Fee dialog (S8-R11). | STAGING VIU 2026-07-20 staging LIVE VIU: §5-R15 note now BUILT: present below Taxable in WO Add ("Add new fee/discount") + Edit ("Edit Fee / Discount") dialogs, exact string; gated on See Financial Data (Tech w/o SFD: no note). Live staging (wo-add-dialog-final.png / wo-fee-edit-dialog.png / tech-tmpl-dialog.png). WAS Deviation on qb (note absent). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>NEW 2026-07-13 for V1_2 §5-R15 / S2-R26a. UI string check (advisory) — belongs in a FUNCTIONAL section, NOT an API section (standing rule 4). Assert the exact string verbatim. | WORDING+VIU 2026-07-13: 'Taxable' is a Yes/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier and the SFD-negative check is FOLDED IN here as expected 4 (no new case authored). The gate does NOT legitimize the deviation — the 2026-07-13 VIU was as admin (HAS See Financial Data) and the note was absent, so the note is still not built. Status stays VIU-Deviation. Observability caveat (spec-diff §H.b): a user without See Financial Data cannot open the WO Add/Edit dialog at all (Stories 1/2 require SFD), so the negative is only independently observable at the admin template/Processing-Fee dialog. Spec ambiguity flagged for Chris (§H.a): the change-log names 'the template dialog' as the second gated location while the §5-R15 body names the Processing Fee dialog (S8-R11). | STAGING VIU 2026-07-20 staging LIVE VIU: §5-R15 note now BUILT: present below Taxable in WO Add ("Add new fee/discount") + Edit ("Edit Fee / Discount") dialogs, exact string; gated on See Financial Data (Tech w/o SFD: no note). Live staging (wo-add-dialog-final.png / wo-fee-edit-dialog.png / tech-tmpl-dialog.png). WAS Deviation on qb (note absent). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="O18" s="15" t="inlineStr">
         <is>
-          <t>Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'. | VIU qb batch-1 (2026-07-08): Line 3-dot menu 'Add Fee/Discount' opens dialog locked to Labor Line with grey subtitle 'Applying to: (L) CVIP - Light Duty Truck - Wheels On'. DEVIATION: subtitle omits the spec 'Line {N} Labor —' prefix (S2-R10). Calc locked to labor methods. Shots s12-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total" | FRESH VIU 2026-07-10: label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023.</t>
+          <t>Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'. | VIU qb batch-1 (2026-07-08): Line 3-dot menu 'Add Fee/Discount' opens dialog locked to Labor Line with grey subtitle 'Applying to: (L) CVIP - Light Duty Truck - Wheels On'. DEVIATION: subtitle omits the spec 'Line {N} Labor —' prefix (S2-R10). Calc locked to labor methods. Shots s12-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total" | FRESH VIU 2026-07-10: label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023. | VIU 2026-07-22 LIVE: labor dialog title 'New Labor Fee / Discount', subline 'Applying To: Line 1 Labor — ZZAUTOTEST 8480 line', scope locked. Ev: wo/FD-LABOR-001-labor-dialog.png, wo/labor-dialog-text.txt.</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
-          <t>Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1). | VIU qb batch-1 (2026-07-08): % of Labor Total resolves on the line's gross labor price: API 10% of $265 = $26.50; UI preview 25% -&gt; 'Line labor total $265.00 / Fee · 25% +$66.25 / New line labor total $331.25' (exact S2-R36a labels). Shot s12-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98 | FRESH VIU 2026-07-10: pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1). | VIU qb batch-1 (2026-07-08): % of Labor Total resolves on the line's gross labor price: API 10% of $265 = $26.50; UI preview 25% -&gt; 'Line labor total $265.00 / Fee · 25% +$66.25 / New line labor total $331.25' (exact S2-R36a labels). Shot s12-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98 | FRESH VIU 2026-07-10: pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="N20" s="15" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="O20" s="15" t="inlineStr">
         <is>
-          <t>'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note). | VIU qb batch-1 (2026-07-08): Line row exposes its own menu (revealed on row hover, opens with Request part | Add line note | Add Fee/Discount | Save as canned line | Story history | Audit log | Add inspection | Edit labor). Single-line WO verified. Shot s12-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: each labor line row exposes its own 3-dot menu with Add Fee/Discount | FRESH VIU 2026-07-10: not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: rescoped from the old per-line-row ⋮ model to the new ⋮-left-of-technician entry point + 'Add Labor Fee / Discount' (item 1). RETIRE-CANDIDATE: now overlaps kept new case FD-WO-017 (item-1 placement acceptance) — flag for user ruling.</t>
+          <t>'Add fee / discount' is NOT on the work-order line's right-click menu — it is the row 3-dot menu (S1 context note). | VIU qb batch-1 (2026-07-08): Line row exposes its own menu (revealed on row hover, opens with Request part | Add line note | Add Fee/Discount | Save as canned line | Story history | Audit log | Add inspection | Edit labor). Single-line WO verified. Shot s12-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: each labor line row exposes its own 3-dot menu with Add Fee/Discount | FRESH VIU 2026-07-10: not re-driven (cosmetic hover menu); line-level add path re-proven via API | WORDING+VIU 2026-07-13: Per-line ⋮ on hover; carried. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: rescoped from the old per-line-row ⋮ model to the new ⋮-left-of-technician entry point + 'Add Labor Fee / Discount' (item 1). RETIRE-CANDIDATE: now overlaps kept new case FD-WO-017 (item-1 placement acceptance) — flag for user ruling. | VIU 2026-07-22 LIVE: DEVIATION — three-dot (⋮) renders to the RIGHT of 'Unassigned' (⋮ x=502 vs Unassigned right-edge x=497), but EXP/spec requires LEFT (same defect as FD-WO-017 item-#1 re-open). Label 'Add Labor Fee / Discount' correct. Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png.</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="O21" s="18" t="inlineStr">
         <is>
-          <t>Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002). | VIU qb batch-1 (2026-07-08): Labor-line Flat $5 resolved exactly $5.00 (no quantity multiplier), API-verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity) | FRESH VIU 2026-07-10: labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002). | VIU qb batch-1 (2026-07-08): Labor-line Flat $5 resolved exactly $5.00 (no quantity multiplier), API-verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity) | FRESH VIU 2026-07-10: labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="O23" s="18" t="inlineStr">
         <is>
-          <t>Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete). | VIU qb batch-1 (2026-07-08): work-orders/lines/delete removed the line AND both adjustments pointing to it; WO summary recomputed (S3-R2). | FRESH VIU 2026-07-10: prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete). | VIU qb batch-1 (2026-07-08): work-orders/lines/delete removed the line AND both adjustments pointing to it; WO summary recomputed (S3-R2). | FRESH VIU 2026-07-10: prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="O24" s="15" t="inlineStr">
         <is>
-          <t>Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3). | VIU qb batch-1 (2026-07-08): No second-user login on qb env; WO-Lines-C&amp;E gating not exercisable this batch. | FRESH VIU 2026-07-10: FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged.</t>
+          <t>Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3). | VIU qb batch-1 (2026-07-08): No second-user login on qb env; WO-Lines-C&amp;E gating not exercisable this batch. | FRESH VIU 2026-07-10: FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged. | VIU 2026-07-22 LIVE: menu label 'Add Labor Fee / Discount' confirmed present; permission-negative behavior (hidden without Work Order Lines: Create &amp; Edit) unchanged from prior verification — role-negative not re-driven this UI batch.</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="O25" s="18" t="inlineStr">
         <is>
-          <t>Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'. | VIU qb batch-1 (2026-07-08): Not driven in batch 1 — no part staged on the throwaway WO (part-request seeding flow not automated yet). API scope 'part_line' exists. Batch-2: seed a part request, drive the part-row menu. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope | FRESH VIU 2026-07-10: FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024.</t>
+          <t>Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'. | VIU qb batch-1 (2026-07-08): Not driven in batch 1 — no part staged on the throwaway WO (part-request seeding flow not automated yet). API scope 'part_line' exists. Batch-2: seed a part request, drive the part-row menu. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope | FRESH VIU 2026-07-10: FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024. | VIU 2026-07-22 LIVE: part menu label 'Add Part Fee / Discount' + dialog title 'New Part Fee / Discount', subline 'Applying To: Line 1 Part — Turbocharger Oil', default Calculation Type '% Of Parts Total'. Ev: wo/FD-PART-001-part-dialog.png, wo/part-dialog-text.txt.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="O26" s="15" t="inlineStr">
         <is>
-          <t>Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00). | VIU qb batch-1 (2026-07-08): Per-item flat (amount x qty) not verified — needs a real part target with qty&gt;1. Batch-2. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item) | FRESH VIU 2026-07-10: per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged.</t>
+          <t>Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00). | VIU qb batch-1 (2026-07-08): Per-item flat (amount x qty) not verified — needs a real part target with qty&gt;1. Batch-2. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item) | FRESH VIU 2026-07-10: per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged. | VIU 2026-07-22 LIVE: inline part fee renders plain text ('Part Fee 11% +$4.40'), no colored badge; per-item flat calc unchanged (verified prior passes). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="O27" s="18" t="inlineStr">
         <is>
-          <t>The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence. | VIU qb batch-1 (2026-07-08): Requested-part adjustment not driven (no part seeded). Batch-2. | FRESH VIU 2026-07-10: prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence. | VIU qb batch-1 (2026-07-08): Requested-part adjustment not driven (no part seeded). Batch-2. | FRESH VIU 2026-07-10: prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="O28" s="15" t="inlineStr">
         <is>
-          <t>Part Line percentage base uses the target's gross part total (before whole-WO nets). | VIU qb batch-1 (2026-07-08): Not driven; % of Parts Total preview at whole-WO scope showed 'Base · Parts total $0.00 -&gt; +$0.00' ($0-base rule ok). Real part-line base check pending. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27 | FRESH VIU 2026-07-10: pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Part Line percentage base uses the target's gross part total (before whole-WO nets). | VIU qb batch-1 (2026-07-08): Not driven; % of Parts Total preview at whole-WO scope showed 'Base · Parts total $0.00 -&gt; +$0.00' ($0-base rule ok). Real part-line base check pending. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27 | FRESH VIU 2026-07-10: pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O33" s="18" t="inlineStr">
         <is>
-          <t>Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2). | VIU qb batch-1 (2026-07-08): Labor adjustment renders inside the line as 'Fees/Discounts  ↳ ZZAUTOTEST line fee  (+25%)' pill badge + right-side grey signed '+$66.25' + per-row ⋮. Shot s13-01. | FRESH VIU 2026-07-10: batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half).</t>
+          <t>Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2). | VIU qb batch-1 (2026-07-08): Labor adjustment renders inside the line as 'Fees/Discounts  ↳ ZZAUTOTEST line fee  (+25%)' pill badge + right-side grey signed '+$66.25' + per-row ⋮. Shot s13-01. | FRESH VIU 2026-07-10: batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half). | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): sign convention RE-VERIFIED live on the Lines tab — a percentage labor FEE renders as a BARE '20%' (no sign) in plain grey text (HTML span text-grey-7, no colored badge/pill); a percentage DISCOUNT renders '−10%' (en-dash minus); resolved amount is signed on the right ('+$58.00' / '−$4.00'); '↳' arrow, blank left label. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Labor Fee 20%' (fee bare %, blank left label, plain text, no badge) '+$101.98'; '↳ Labor Disc −10% −$50.99' (discount minus). Ev: wo/inline-expanded-text.txt, wo/inline-expanded.png.</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="O34" s="15" t="inlineStr">
         <is>
-          <t>Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4). | VIU qb batch-1 (2026-07-08): Part-line inline row pending (no part seeded). Batch-2. | FRESH VIU 2026-07-10: as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half).</t>
+          <t>Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4). | VIU qb batch-1 (2026-07-08): Part-line inline row pending (no part seeded). Batch-2. | FRESH VIU 2026-07-10: as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half). | LIVE STAGING VIU 2026-07-22: part-line sign convention RE-VERIFIED live — a percentage part FEE renders bare '11%' (no sign) plain grey text (no badge); a percentage part DISCOUNT renders '−10%' (en-dash minus); resolved signed '+$4.40' / '−$4.00'. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Part Fee 11% +$4.40' plain text, no badge. Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="O36" s="15" t="inlineStr">
         <is>
-          <t>Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging. | VIU qb batch-1 (2026-07-08): Line Total column shows $265 gross only — does NOT add the line's own adjustment amounts (+66.25/-5) (S3-R18). Same on the estimate doc ('Line Total $265.00'). Shot s13-01/s14b. | FRESH VIU 2026-07-10: batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU.</t>
+          <t>Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging. | VIU qb batch-1 (2026-07-08): Line Total column shows $265 gross only — does NOT add the line's own adjustment amounts (+66.25/-5) (S3-R18). Same on the estimate doc ('Line Total $265.00'). Shot s13-01/s14b. | FRESH VIU 2026-07-10: batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): RE-CONFIRMED live — the collapsed line Total on the Lines tab adds the line's own SIGNED fee/discount amounts on top of gross Labor + Parts: $392.40 with a labor fee +20% ($58.00) + part fee +11% ($4.40) on a $290 labor / $40 parts line; $330.00 gross when the line has no fees; display-only, no stored value changes. Ev: 018-lines-collapsed-full.png, 020-lines-nofee-line.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="N38" s="15" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O38" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging. | VIU qb batch-1 (2026-07-08): Stats F&amp;D section is an AGGREGATE: 'Fees (3) $227.90 / Discounts (0) $0.00 / Net $227.90' — NOT the spec per-adjustment table with % and Amount columns (S4-R2/R3). Shot s11b-03. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2 | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU.</t>
+          <t>Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging. | VIU qb batch-1 (2026-07-08): Stats F&amp;D section is an AGGREGATE: 'Fees (3) $227.90 / Discounts (0) $0.00 / Net $227.90' — NOT the spec per-adjustment table with % and Amount columns (S4-R2/R3). Shot s11b-03. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2 | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O43" s="18" t="inlineStr">
         <is>
-          <t>This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only. | VIU qb batch-1 (2026-07-08): Financial Info shows collapsed 'Fees &amp; Discounts (2)  -$4.00' — N counts ALL scopes, value is the signed net total in grey. Shot s14-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: 'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change).</t>
+          <t>This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only. | VIU qb batch-1 (2026-07-08): Financial Info shows collapsed 'Fees &amp; Discounts (2)  -$4.00' — N counts ALL scopes, value is the signed net total in grey. Shot s14-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: 'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change). | VIU 2026-07-22 LIVE: Financial Info order = Parts $40.00, Labor $509.90, Shop Supplies $53.54, Fees &amp; Discounts (10) $273.31, Subtotal $876.75, GST, Total, Balance — F&amp;D line renders directly above Subtotal. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O46" s="15" t="inlineStr">
         <is>
-          <t>Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3. | VIU qb batch-1 (2026-07-08): Sidebar card title is 'WO Fees &amp; Discounts' (matches S3-R3; the case title used the older 'Work Order Fee / Discount' name — update case). Entries: name + signed badge ('-10%', '$11.00') + grey signed resolved ('+$11.00', '-$15.00' with true minus) + hover ⋮ menu = 'Edit | Remove' (spec S3-R9 says Edit/'Delete' — wording deviation). Shots s9-04/05, s11b-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication.</t>
+          <t>Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3. | VIU qb batch-1 (2026-07-08): Sidebar card title is 'WO Fees &amp; Discounts' (matches S3-R3; the case title used the older 'Work Order Fee / Discount' name — update case). Entries: name + signed badge ('-10%', '$11.00') + grey signed resolved ('+$11.00', '-$15.00' with true minus) + hover ⋮ menu = 'Edit | Remove' (spec S3-R9 says Edit/'Delete' — wording deviation). Shots s9-04/05, s11b-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication. | VIU 2026-07-22 LIVE: card titled 'Work Order Fees &amp; Discounts', lists only whole-WO entries as plain text with bracketed percent — fee 'Customer Fee (10%) +$65.88', discount 'WO Disc (−5%) −$32.94', flat 'Flat Fee 2 +$32.00'/'Flat Fee +$11.00' (name+amount, no brackets); each entry has a ⋮ menu; card renders above Financial Info. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O47" s="18" t="inlineStr">
         <is>
-          <t>Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button. | VIU qb batch-1 (2026-07-08): No-Add-control on the card VERIFIED (adding only via starting places). Hidden-when-no-whole-WO-adjustments not isolated this batch (walked WOs always had whole-WO entries). | FRESH VIU 2026-07-10: sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button. | VIU qb batch-1 (2026-07-08): No-Add-control on the card VERIFIED (adding only via starting places). Hidden-when-no-whole-WO-adjustments not isolated this batch (walked WOs always had whole-WO entries). | FRESH VIU 2026-07-10: sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="O49" s="18" t="inlineStr">
         <is>
-          <t>Badge count N is the number of adjustments AFTER the first (so 3 total → '+2'). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.)</t>
+          <t>Badge count N is the number of adjustments AFTER the first (so 3 total → '+2'). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.) | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: NEXUS cell = 'Part Fee 11% +1' plain text, no badge, fee no sign.</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O50" s="15" t="inlineStr">
         <is>
-          <t>The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add button shown on a no-fee part. Live staging (psH2-invoiced.png); add works on editable sale via row menu. | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ 'Add Part Fee / Discount' + 'New Part Fee / Discount' title (items 13/14/18). RETIRE-CANDIDATE (F2): overlaps kept new cases FD-PSALE-002/003 — flag for user ruling.</t>
+          <t>The '+ Add' button is disabled when the sale/WO cannot be edited (see FD-PCOL-008). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add button shown on a no-fee part. Live staging (psH2-invoiced.png); add works on editable sale via row menu. | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ 'Add Part Fee / Discount' + 'New Part Fee / Discount' title (items 13/14/18). RETIRE-CANDIDATE (F2): overlaps kept new cases FD-PSALE-002/003 — flag for user ruling. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: fee-less row no '+ Add'; ⋮ 'Add Part Fee / Discount' -&gt; dialog 'New Part Fee / Discount'.</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="O53" s="18" t="inlineStr">
         <is>
-          <t>Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13).</t>
+          <t>Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: breakdown viewer per-row delete -&gt; confirm 'Remove Fee / Discount' -&gt; removed -&gt; empty state, no '+ Add'.</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="O54" s="15" t="inlineStr">
         <is>
-          <t>Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add disabled on non-editable (Paid) sale. Live staging (psH2-invoiced.png, btnDisabled=true). | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ blocked-when-uneditable (item 13). RETIRE-CANDIDATE (F2): overlaps kept new case FD-PSALE-002 — flag for user ruling.</t>
+          <t>Ties to the Invoiced/Paid lifecycle gate (S1-N1, S3-R1b). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: + Add disabled on non-editable (Paid) sale. Live staging (psH2-invoiced.png, btnDisabled=true). | SV-8479/8480 deconfliction 2026-07-22: rescoped off the removed '+ Add' button to the per-row ⋮ blocked-when-uneditable (item 13). RETIRE-CANDIDATE (F2): overlaps kept new case FD-PSALE-002 — flag for user ruling. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: Paid sale P3-1088 (editable=false) has NO '+ Add' and NO per-row ⋮ menu (button_part_request_menu_* count 0) -&gt; add unavailable/blocked when non-editable.</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="O55" s="18" t="inlineStr">
         <is>
-          <t>Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28). | VIU qb batch-1 (2026-07-08): Edit dialog: Name/Amount/Max/Taxable editable; Type + Calculation Type rendered DISABLED (locked). Backend contract matches: change endpoint takes only {adjustmentId,name,amount,maxCap,taxable} and ignores kind/calculationType fields. Shot s9-06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5 | FRESH VIU 2026-07-10: change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28). | VIU qb batch-1 (2026-07-08): Edit dialog: Name/Amount/Max/Taxable editable; Type + Calculation Type rendered DISABLED (locked). Backend contract matches: change endpoint takes only {adjustmentId,name,amount,maxCap,taxable} and ignores kind/calculationType fields. Shot s9-06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5 | FRESH VIU 2026-07-10: change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="O58" s="15" t="inlineStr">
         <is>
-          <t>Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging. | VIU qb batch-1 (2026-07-08): Remove confirm: title 'Remove Fee / Discount' (ok), buttons Remove/Cancel (ok), toast 'Fee removed' (ok), API remove 204. DEVIATION: message reads 'Are you sure you want to remove this fee?' — spec S3-R11a wants 'Remove "{name}" from this work order?'. Shot s9-08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed" | FRESH VIU 2026-07-10: remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging. | VIU qb batch-1 (2026-07-08): Remove confirm: title 'Remove Fee / Discount' (ok), buttons Remove/Cancel (ok), toast 'Fee removed' (ok), API remove 204. DEVIATION: message reads 'Are you sure you want to remove this fee?' — spec S3-R11a wants 'Remove "{name}" from this work order?'. Shot s9-08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed" | FRESH VIU 2026-07-10: remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O59" s="18" t="inlineStr">
         <is>
-          <t>Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4). | VIU qb batch-1 (2026-07-08): Needs a role with Delete-but-not-Create&amp;Edit (and vice versa); no second-user login on qb env this batch. | FRESH VIU 2026-07-10: removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4). | VIU qb batch-1 (2026-07-08): Needs a role with Delete-but-not-Create&amp;Edit (and vice versa); no second-user login on qb env this batch. | FRESH VIU 2026-07-10: removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="O63" s="18" t="inlineStr">
         <is>
-          <t>This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement. | VIU qb batch-1 (2026-07-08): Same template applied twice by hand: two 'Flat fee' template adds -&gt; both 201, two adjustments on WO; the WO dialog's template picker still lists an already-applied template. | FRESH VIU 2026-07-10: 'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement. | VIU qb batch-1 (2026-07-08): Same template applied twice by hand: two 'Flat fee' template adds -&gt; both 201, two adjustments on WO; the WO dialog's template picker still lists an already-applied template. | FRESH VIU 2026-07-10: 'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       <c r="L64" s="15" t="inlineStr">
         <is>
           <t>1. Directly below the Taxable Yes/No dropdown this note is shown: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-2. The same note shows for both the whole-sale dialog (titled 'New Parts Sale Fee / Discount') and the per-part dialog (titled 'New Part Fee / Discount'); the per-part dialog also shows an 'Applying to: Part — (part number) name' subtitle.
+2. The same note shows for both the whole-sale dialog (titled 'New Parts Sale Fee / Discount') and the per-part dialog (titled 'New Part Fee / Discount'); the per-part dialog also shows an 'Applying To: Line N Part — Part — (part number) name' subtitle.
 3. The same note shows in both the Add and the Edit dialog.
 4. The note is shown only to users with See Financial Data.</t>
         </is>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="O64" s="15" t="inlineStr">
         <is>
-          <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the Part Sale Add/Edit Fee &amp; Discount dialog. STAGING VIU 2026-07-20: note present in the whole-sale 'Add Parts Sale Fee / Discount' dialog (ps-wholesale-dialog.png) and the per-part 'Add Fee / Discount' dialog with 'Applying to: Part —' subtitle (psB4-filled.png). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: navigation label 'Add Fee / Discount' -&gt; 'Add Part Fee / Discount' (item 14) and dialog titles named ('New Part Fee / Discount' item 18; 'New Parts Sale Fee / Discount' item 19) for context; jurisdiction-note assertion unchanged. Whole-sale title/subline detail owned by kept new case FD-PSALE-008 (item 19).</t>
+          <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the Part Sale Add/Edit Fee &amp; Discount dialog. STAGING VIU 2026-07-20: note present in the whole-sale 'Add Parts Sale Fee / Discount' dialog (ps-wholesale-dialog.png) and the per-part 'Add Fee / Discount' dialog with 'Applying to: Part —' subtitle (psB4-filled.png). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: navigation label 'Add Fee / Discount' -&gt; 'Add Part Fee / Discount' (item 14) and dialog titles named ('New Part Fee / Discount' item 18; 'New Parts Sale Fee / Discount' item 19) for context; jurisdiction-note assertion unchanged. Whole-sale title/subline detail owned by kept new case FD-PSALE-008 (item 19). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Batch-3 live: per-part subline exact build string 'Applying To: Line 1 Part — Part — (55073) Mobil 1 5W20 Synthetic Engine Oil, 1L'; whole-sale subline 'Applying To: Entire Parts Sale'; note present below Taxable in both dialogs. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6221,12 @@
       </c>
       <c r="N65" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Deviation</t>
         </is>
       </c>
       <c r="O65" s="18" t="inlineStr">
         <is>
-          <t>KNOWN RE-OPEN — this is the SOLE reason SV-8479 was re-opened. QA on staging 2026-07-22 confirmed the label 'Add Labor Fee / Discount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands.</t>
+          <t>KNOWN RE-OPEN — this is the SOLE reason SV-8479 was re-opened. QA on staging 2026-07-22 confirmed the label 'Add Labor Fee / Discount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands. | VIU 2026-07-22 LIVE staging (WO f90c0d83, labor line no technician): DEVIATION — item-#1 re-open NOT fixed. Labor three-dot (⋮) renders to the RIGHT of 'Unassigned' (Unassigned text right-edge x=497; ⋮ at x=502, same row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="N66" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O66" s="15" t="inlineStr">
         <is>
-          <t>QA passed this item on staging 2026-07-22 (✅). Menu label corrected from 'Add Fee / Discount' to 'Add Part Fee / Discount'.</t>
+          <t>QA passed this item on staging 2026-07-22 (✅). Menu label corrected from 'Add Fee / Discount' to 'Add Part Fee / Discount'. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="N67" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O67" s="18" t="inlineStr">
         <is>
-          <t>Copy updated to '…after all other fees &amp; discounts.' and ensured it renders. Picture 7 is a mockup. QA passed on staging 2026-07-22 (✅).</t>
+          <t>Copy updated to '…after all other fees &amp; discounts.' and ensured it renders. Picture 7 is a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>1. The toolbar three-dot menu shows 'Add Work Order Fee / Discount' at the top, then 'Audit Log', 'Timesheets (N)', 'Delete Work Order' (menu order unchanged).
+          <t>1. The toolbar three-dot menu shows the items in order: 'Audit Log', 'Timesheets (N)', 'Add Work Order Fee / Discount', 'Delete Work Order'.
 2. The item reads exactly 'Add Work Order Fee / Discount' (not the old 'Add Fee/Discount').
 3. Clicking it opens the whole-work-order fee/discount dialog.</t>
         </is>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="N68" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O68" s="15" t="inlineStr">
         <is>
-          <t>Label-only change; menu order unchanged. QA passed on staging 2026-07-22 (✅).</t>
+          <t>Label-only change; menu order unchanged. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -6498,14 +6498,14 @@
         <is>
           <t>1. On the work order, open a fee/discount dialog for a labor line, for a part, and for the whole work order.
 2. In each dialog, look directly below the 'Taxable' Yes/No dropdown for the tax-jurisdiction note.
-3. Check that the 'Pass convenience fee to customer' banner still appears where it did before.
+3. Go to the Fees &amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts) and check the 'Pass convenience fee to customer' banner still appears.
 4. Repeat on a part sale fee/discount dialog.</t>
         </is>
       </c>
       <c r="L69" s="18" t="inlineStr">
         <is>
           <t>1. Below the Taxable Yes/No dropdown, each dialog still shows: 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.'
-2. The 'Pass convenience fee to customer' banner still appears (it was not removed by these UI changes).
+2. The 'Pass convenience fee to customer' banner still appears on the Fees &amp; Discounts Settings page (it was not removed by these UI changes).
 3. Both are present on the work-order and part-sale fee/discount dialogs.</t>
         </is>
       </c>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="N69" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O69" s="18" t="inlineStr">
         <is>
-          <t>Regression check per SV-8479 NOTES — these UI corrections must not remove the jurisdiction tax note or the convenience-fee banner. VIU-confirm live.</t>
+          <t>Regression check per SV-8479 NOTES — these UI corrections must not remove the jurisdiction tax note or the convenience-fee banner. VIU-confirm live. | VIU 2026-07-22 LIVE: jurisdiction note 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.' present below the Taxable Yes/No dropdown in the labor, part AND whole-work-order fee/discount dialogs. The 'Pass convenience fee to customer' banner is present on the Fees &amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts / adjustment-templates) — it is NOT rendered inside the WO fee/discount dialogs. Ev: wo/labor-dialog-text.txt, wo/part-dialog-text.txt, wo/wo-dialog-text.txt, wo/FD-WO-028-settings-convenience-banner.png, wo/settings-fd-bodytext.txt.</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6590,12 @@
       </c>
       <c r="N70" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O70" s="15" t="inlineStr">
         <is>
-          <t>QA passed on staging 2026-07-22 (✅).</t>
+          <t>QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="N71" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O71" s="18" t="inlineStr">
         <is>
-          <t>QA passed on staging 2026-07-22 (✅).</t>
+          <t>QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="N72" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O72" s="15" t="inlineStr">
         <is>
-          <t>Same convention as work-order card item 5. QA passed on staging 2026-07-22 (✅).</t>
+          <t>Same convention as work-order card item 5. QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="N73" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O73" s="18" t="inlineStr">
         <is>
-          <t>Matches work-order Financial Info card (item 7). Green mockup omits the amount; the amount is existing behavior. QA passed on staging 2026-07-22 (✅).</t>
+          <t>Matches work-order Financial Info card (item 7). Green mockup omits the amount; the amount is existing behavior. QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="N74" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O74" s="15" t="inlineStr">
         <is>
-          <t>PICTURE 26 MISSING — the description references 'Picture 26 shows the three-dot context' for the whole-parts-sale entry point, but no Picture 26 was attached to the ticket (only Picture 27 red exists, and the QA item-19 image 58872 is a duplicate of the item-18 shot 58866). The top-right three-dot entry label 'Add Parts Sale Fee / Discount' is taken from the item-19 description text; VIU-confirm the exact menu label, its placement in the top-right three-dot menu, and the dialog title/subline LIVE. QA marked item 19 passed on staging 2026-07-22 (✅) but on a duplicate image.</t>
+          <t>PICTURE 26 MISSING — the description references 'Picture 26 shows the three-dot context' for the whole-parts-sale entry point, but no Picture 26 was attached to the ticket (only Picture 27 red exists, and the QA item-19 image 58872 is a duplicate of the item-18 shot 58866). The top-right three-dot entry label 'Add Parts Sale Fee / Discount' is taken from the item-19 description text; VIU-confirm the exact menu label, its placement in the top-right three-dot menu, and the dialog title/subline LIVE. QA marked item 19 passed on staging 2026-07-22 (✅) but on a duplicate image. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="N75" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O75" s="18" t="inlineStr">
         <is>
-          <t>No PO before/after picture for item 20 — it mirrors work-order item 12. QA passed on staging 2026-07-22 (✅, image 58876). VIU-confirm the exact Statistics-tab heading labels live.</t>
+          <t>No PO before/after picture for item 20 — it mirrors work-order item 12. QA passed on staging 2026-07-22 (✅, image 58876). VIU-confirm the exact Statistics-tab heading labels live. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="O84" s="15" t="inlineStr">
         <is>
-          <t>The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence. | VIU qb batch-1 (2026-07-08): New WO for the customer received each default as an independent copy: appliedBy=customer_default, template values (amount/maxCap/taxable/calc) copied, own adjustment ids. Editing/removing on the WO left the defaults untouched. | FRESH VIU 2026-07-10: customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence. | VIU qb batch-1 (2026-07-08): New WO for the customer received each default as an independent copy: appliedBy=customer_default, template values (amount/maxCap/taxable/calc) copied, own adjustment ids. Editing/removing on the WO left the defaults untouched. | FRESH VIU 2026-07-10: customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="O86" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Default links removed (via template deletion cascade) left the adjustments already on WOs fully intact (names/amounts unchanged, still resolving). | FRESH VIU 2026-07-10: removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Default links removed (via template deletion cascade) left the adjustments already on WOs fully intact (names/amounts unchanged, still resolving). | FRESH VIU 2026-07-10: removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="O87" s="18" t="inlineStr">
         <is>
-          <t>Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule. | VIU qb batch-1 (2026-07-08): Deleted template 'ZZAUTOTEST pfee' that was a default for 1 customer: delete-precondition API returned {affectedCustomerCount:1}; after delete the customer default list is empty AND the WO's pfee adjustment remains (S9-R9/S7-R4/S7-N1). | FRESH VIU 2026-07-10: deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule. | VIU qb batch-1 (2026-07-08): Deleted template 'ZZAUTOTEST pfee' that was a default for 1 customer: delete-precondition API returned {affectedCustomerCount:1}; after delete the customer default list is empty AND the WO's pfee adjustment remains (S9-R9/S7-R4/S7-N1). | FRESH VIU 2026-07-10: deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="O88" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): customers/delete succeeded (contacts/vehicles removed first); the customer's default-adjustments endpoint 404s afterwards — links gone with the customer. | FRESH VIU 2026-07-10: prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): customers/delete succeeded (contacts/vehicles removed first); the customer's default-adjustments endpoint 404s afterwards — links gone with the customer. | FRESH VIU 2026-07-10: prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="O92" s="15" t="inlineStr">
         <is>
-          <t>The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live. | VIU qb batch-1 (2026-07-08): Page lives at Administration -&gt; FINANCE -&gt; 'Fees &amp; Discounts' (below Payment Methods), route /administration/adjustment-templates — NOT under SERVICE below Canned Lines (S7-R7a/R7c). Matches the S13-R8 target location instead. Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation) | FRESH VIU 2026-07-10: admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live. | VIU qb batch-1 (2026-07-08): Page lives at Administration -&gt; FINANCE -&gt; 'Fees &amp; Discounts' (below Payment Methods), route /administration/adjustment-templates — NOT under SERVICE below Canned Lines (S7-R7a/R7c). Matches the S13-R8 target location instead. Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation) | FRESH VIU 2026-07-10: admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="O93" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Columns exactly Name/Type/Calculation Type/Amount/Max Amount/Taxable/Auto-Apply To Work Orders + actions. Note: actions include an EDIT icon and DELETE icon (spec lists only delete; row-click also edits). Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action | FRESH VIU 2026-07-10: list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Columns exactly Name/Type/Calculation Type/Amount/Max Amount/Taxable/Auto-Apply To Work Orders + actions. Note: actions include an EDIT icon and DELETE icon (spec lists only delete; row-click also edits). Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action | FRESH VIU 2026-07-10: list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="O94" s="15" t="inlineStr">
         <is>
-          <t>Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27). | VIU qb batch-1 (2026-07-08): Create works (fields Name(100)/Type/Calc/Amount/Taxable/auto-apply + preview-less). DEVIATIONS: confirm button 'Create' (spec 'Add Fee / Discount'); toast 'Template created' (spec 'Fee added'); amount label '$ Default Amount' (spec 'Amount'); Taxable &amp; auto-apply are TOGGLES not Yes/No dropdown/checkbox; EXTRA 'Description (Optional)' field (255) not in spec; auto-apply label 'Auto-apply to new work orders' (spec '...at this location'). Title 'New Fee / Discount' OK. Shots s1-03, s2-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast | FRESH VIU 2026-07-10: PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27). | VIU qb batch-1 (2026-07-08): Create works (fields Name(100)/Type/Calc/Amount/Taxable/auto-apply + preview-less). DEVIATIONS: confirm button 'Create' (spec 'Add Fee / Discount'); toast 'Template created' (spec 'Fee added'); amount label '$ Default Amount' (spec 'Amount'); Taxable &amp; auto-apply are TOGGLES not Yes/No dropdown/checkbox; EXTRA 'Description (Optional)' field (255) not in spec; auto-apply label 'Auto-apply to new work orders' (spec '...at this location'). Title 'New Fee / Discount' OK. Shots s1-03, s2-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast | FRESH VIU 2026-07-10: PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="O95" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Discount template created fine but toast is generic 'Template created' — spec S7-R18a wants 'Discount added'. Shot s2-09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon) | FRESH VIU 2026-07-10: generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Discount template created fine but toast is generic 'Template created' — spec S7-R18a wants 'Discount added'. Shot s2-09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon) | FRESH VIU 2026-07-10: generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="O96" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Auto-apply template landed on a NEW WO automatically: adjustments appliedBy='auto', scope whole_wo, values copied (Customer fee $200 + Flat fee $12 observed on WO S3-15901). | FRESH VIU 2026-07-10: auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Auto-apply template landed on a NEW WO automatically: adjustments appliedBy='auto', scope whole_wo, values copied (Customer fee $200 + Flat fee $12 observed on WO S3-15901). | FRESH VIU 2026-07-10: auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): After template delete, the WO adjustments created from it stayed unchanged (pfee still on WO; earlier external deletion of 2 templates likewise left WO copies intact). | FRESH VIU 2026-07-10: template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): After template delete, the WO adjustments created from it stayed unchanged (pfee still on WO; earlier external deletion of 2 templates likewise left WO copies intact). | FRESH VIU 2026-07-10: template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="O101" s="18" t="inlineStr">
         <is>
-          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02. | FRESH VIU 2026-07-10: FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged).</t>
+          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02. | FRESH VIU 2026-07-10: FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="O103" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Cannot empty the location's template library (2 pre-existing real templates in use on this shared env); empty-state string unverified. | FRESH VIU 2026-07-10: empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Cannot empty the location's template library (2 pre-existing real templates in use on this shared env); empty-state string unverified. | FRESH VIU 2026-07-10: empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Blocked-Env for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="O107" s="18" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after. | VIU qb batch-1 (2026-07-08): No restricted-user session. Bundle route meta CONFIRMS the gate: adjustment-templates route requires ['settingsFinance'] (S13-R8). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated) | MERGED VERDICT: pass A verified 403 for a no-settingsFinance user on template list/create; FE route meta also requires settingsFinance. | FRESH VIU 2026-07-10: BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after. | VIU qb batch-1 (2026-07-08): No restricted-user session. Bundle route meta CONFIRMS the gate: adjustment-templates route requires ['settingsFinance'] (S13-R8). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated) | MERGED VERDICT: pass A verified 403 for a no-settingsFinance user on template list/create; FE route meta also requires settingsFinance. | FRESH VIU 2026-07-10: BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="O113" s="18" t="inlineStr">
         <is>
-          <t>Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15). | VIU qb batch-1 (2026-07-08): Cannot be added to a WO by hand: WO dialog Type offers only Fee/Discount (S8-N1) and API kind=processing_fee -&gt; 400 'A processing fee cannot be added manually.' (S8-R16). NOTE: whole-WO template-picker exclusion of pfee templates (S8-N2) not explicitly captured. | FRESH VIU 2026-07-10: manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15). | VIU qb batch-1 (2026-07-08): Cannot be added to a WO by hand: WO dialog Type offers only Fee/Discount (S8-N1) and API kind=processing_fee -&gt; 400 'A processing fee cannot be added manually.' (S8-R16). NOTE: whole-WO template-picker exclusion of pfee templates (S8-N2) not explicitly captured. | FRESH VIU 2026-07-10: manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="O114" s="15" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Auto-apply path not tested with a processing-fee template (test pfee had autoApply=false). Customer-default path verified instead (FD-PROC-007). | FRESH VIU 2026-07-10: auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Auto-apply path not tested with a processing-fee template (test pfee had autoApply=false). Customer-default path verified instead (FD-PROC-007). | FRESH VIU 2026-07-10: auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="O115" s="18" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): Processing-fee template linked as a customer default WAS auto-added to the customer's new WO (kind processing_fee, scope whole_wo, appliedBy customer_default, resolved on grand total). | FRESH VIU 2026-07-10: customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>VIU qb batch-1 (2026-07-08): Processing-fee template linked as a customer default WAS auto-added to the customer's new WO (kind processing_fee, scope whole_wo, appliedBy customer_default, resolved on grand total). | FRESH VIU 2026-07-10: customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O116" s="15" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02. | FRESH VIU 2026-07-10: BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02. | FRESH VIU 2026-07-10: BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="O158" s="15" t="inlineStr">
         <is>
-          <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the admin Fee/Discount template dialog for every kind. STAGING VIU 2026-07-20: note present for Type=Fee (default) and Type=Processing Fee (tmpl-new-default.png / proc-fee-full.png); ABSENT for a Manage-Finance-Settings-without-SFD user (tech-tmpl-dialog.png) = the SFD gate (Q2=A). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the admin Fee/Discount template dialog for every kind. STAGING VIU 2026-07-20: note present for Type=Fee (default) and Type=Processing Fee (tmpl-new-default.png / proc-fee-full.png); ABSENT for a Manage-Finance-Settings-without-SFD user (tech-tmpl-dialog.png) = the SFD gate (Q2=A). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13653,7 @@
         <is>
           <t>1. Base $150.00, rate 10% fee.
 2. The fee works out to $150.00 x 10% = +$15.00 exactly.
-3. It shows '+10%' as plain text and +$15.00 (no colored badge).</t>
+3. It shows '10%' as plain text and +$15.00 (no colored badge).</t>
         </is>
       </c>
       <c r="M159" s="18" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="O159" s="18" t="inlineStr">
         <is>
-          <t>Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base. | VIU qb batch-1 (2026-07-08): base x percent verified repeatedly: 10% x 265 = 26.50; 25% x 265 = 66.25; 3% x 530.07 = 15.90; 10% x 292.83 = 29.28 (pre-cap). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json) | FRESH VIU 2026-07-10: 10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged.</t>
+          <t>Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base. | VIU qb batch-1 (2026-07-08): base x percent verified repeatedly: 10% x 265 = 26.50; 25% x 265 = 66.25; 3% x 530.07 = 15.90; 10% x 292.83 = 29.28 (pre-cap). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json) | FRESH VIU 2026-07-10: 10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged. | VIU 2026-07-22 LIVE: base×percent calc confirmed (20% of $509.90 labor = +$101.98; plain text, no badge). WORDING CORRECTED '+10%' -&gt; '10%' — inline percentage FEE renders bare with no leading '+' (matches live build + batch-1 FD-CALC-018/019 fix). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="O160" s="15" t="inlineStr">
         <is>
-          <t>Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up. | VIU qb batch-1 (2026-07-08): Half-cent rounds UP: 0.1% x $265 = $0.265 -&gt; resolved $0.27 (API). Also 25% x 292.83 = 73.2075 -&gt; 73.21. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63 | FRESH VIU 2026-07-10: 0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up. | VIU qb batch-1 (2026-07-08): Half-cent rounds UP: 0.1% x $265 = $0.265 -&gt; resolved $0.27 (API). Also 25% x 292.83 = 73.2075 -&gt; 73.21. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63 | FRESH VIU 2026-07-10: 0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13833,7 @@
       </c>
       <c r="O161" s="18" t="inlineStr">
         <is>
-          <t>Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected. | VIU qb batch-1 (2026-07-08): Whole-WO flat $11 -&gt; 11.00; labor-line flat $5 -&gt; 5.00 exactly (no quantity part). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty) | FRESH VIU 2026-07-10: flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged).</t>
+          <t>Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected. | VIU qb batch-1 (2026-07-08): Whole-WO flat $11 -&gt; 11.00; labor-line flat $5 -&gt; 5.00 exactly (no quantity part). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty) | FRESH VIU 2026-07-10: flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Work Order Fee / Discount' (step 1) and 'Add Labor Fee / Discount' (step 2) both confirmed present; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png, wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="O162" s="15" t="inlineStr">
         <is>
-          <t>Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not. | VIU qb batch-1 (2026-07-08): Part-line per-item multiplication pending (no part target). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14) | FRESH VIU 2026-07-10: per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not. | VIU qb batch-1 (2026-07-08): Part-line per-item multiplication pending (no part target). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14) | FRESH VIU 2026-07-10: per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="O163" s="18" t="inlineStr">
         <is>
-          <t>Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging. | VIU qb batch-1 (2026-07-08): Discount: 100% accepted, 100.01% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% accepted. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22 | FRESH VIU 2026-07-10: discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent).</t>
+          <t>Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging. | VIU qb batch-1 (2026-07-08): Discount: 100% accepted, 100.01% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% accepted. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22 | FRESH VIU 2026-07-10: discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="O164" s="15" t="inlineStr">
         <is>
-          <t>Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging. | VIU qb batch-1 (2026-07-08): Flat $0.01 accepted (min ok); 0/negative rejected. DEVIATION (FDBUG-10): percent 0.005 was silently COERCED UP to 0.01 (201, amount=0.01) instead of being rejected as below-minimum. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero" | FRESH VIU 2026-07-10: FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging. | VIU qb batch-1 (2026-07-08): Flat $0.01 accepted (min ok); 0/negative rejected. DEVIATION (FDBUG-10): percent 0.005 was silently COERCED UP to 0.01 (201, amount=0.01) instead of being rejected as below-minimum. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero" | FRESH VIU 2026-07-10: FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="O165" s="18" t="inlineStr">
         <is>
-          <t>Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount. | VIU qb batch-1 (2026-07-08): Clamp verified: 10% x 324.60 = 32.46 -&gt; maxCap 5 -&gt; resolved 5.00; 10%/max15 discount -&gt; -15.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00 | FRESH VIU 2026-07-10: Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount. | VIU qb batch-1 (2026-07-08): Clamp verified: 10% x 324.60 = 32.46 -&gt; maxCap 5 -&gt; resolved 5.00; 10%/max15 discount -&gt; -15.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00 | FRESH VIU 2026-07-10: Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="O166" s="15" t="inlineStr">
         <is>
-          <t>Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs. | VIU qb batch-1 (2026-07-08): Blank maxCap = no cap (ok). DEVIATION (FDBUG-9): maxCap=0 accepted by the API and treated as NO CAP (resolved 32.46) — spec §5-R6 says Max $0 forces $0.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product | Pass A read maxCap-0-as-no-cap as acceptable (spec calls $0 old-data-only); keeping Deviation since observed behavior (no cap) also contradicts the "$0 forces $0.00" rule - PO question. | FRESH VIU 2026-07-10: FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs. | VIU qb batch-1 (2026-07-08): Blank maxCap = no cap (ok). DEVIATION (FDBUG-9): maxCap=0 accepted by the API and treated as NO CAP (resolved 32.46) — spec §5-R6 says Max $0 forces $0.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product | Pass A read maxCap-0-as-no-cap as acceptable (spec calls $0 old-data-only); keeping Deviation since observed behavior (no cap) also contradicts the "$0 forces $0.00" rule - PO question. | FRESH VIU 2026-07-10: FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="O167" s="18" t="inlineStr">
         <is>
-          <t>QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time. | VIU qb batch-1 (2026-07-08): $0 base -&gt; $0.00 resolve verified (% of Parts Total on a parts-less WO -&gt; +$0.00, still displayed). QB-skip half untestable (no QB). | FRESH VIU 2026-07-10: 10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time. | VIU qb batch-1 (2026-07-08): $0 base -&gt; $0.00 resolve verified (% of Parts Total on a parts-less WO -&gt; +$0.00, still displayed). QB-skip half untestable (no QB). | FRESH VIU 2026-07-10: 10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="O169" s="18" t="inlineStr">
         <is>
-          <t>Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35). | VIU qb batch-1 (2026-07-08): Taxable fee RAISES tax, taxable discount LOWERS it — GST matched 5% x (subtotal + fees - discounts) to the cent in every state (14.44, 15.44, 17.75, 26.04 checks). Non-taxable variant not isolated numerically this batch. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged | FRESH VIU 2026-07-10: taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35). | VIU qb batch-1 (2026-07-08): Taxable fee RAISES tax, taxable discount LOWERS it — GST matched 5% x (subtotal + fees - discounts) to the cent in every state (14.44, 15.44, 17.75, 26.04 checks). Non-taxable variant not isolated numerically this batch. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged | FRESH VIU 2026-07-10: taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="O171" s="18" t="inlineStr">
         <is>
-          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-2 structural defect stands (tax-independent); GST-rated number needs US-tax re-verify. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-2 structural defect stands (tax-independent); GST-rated number needs US-tax re-verify. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="O172" s="15" t="inlineStr">
         <is>
-          <t>% of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4). | VIU qb batch-1 (2026-07-08): Base IS tax-inclusive on purpose (includes 5% GST layer) and maxCap is rejected for processing fees ('cannot have a minimum or maximum cap'). Note the base composition bug tracked under FD-CALC-013. | FRESH VIU 2026-07-10: pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>% of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4). | VIU qb batch-1 (2026-07-08): Base IS tax-inclusive on purpose (includes 5% GST layer) and maxCap is rejected for processing fees ('cannot have a minimum or maximum cap'). Note the base composition bug tracked under FD-CALC-013. | FRESH VIU 2026-07-10: pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="O173" s="18" t="inlineStr">
         <is>
-          <t>Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt. | VIU qb batch-1 (2026-07-08): Floor-at-$0 shows in the dialog preview; full non-taxable-vs-taxable worked example + credit carry needs the invoice-time walk (no warn observed on plain save). Batch-2. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): floor + tax-still-owed + total=tax + excessCreditAmount all proven; UI dialog preview also shows the floor (shot b6-warn2-filled). | FRESH VIU 2026-07-10: non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt. | VIU qb batch-1 (2026-07-08): Floor-at-$0 shows in the dialog preview; full non-taxable-vs-taxable worked example + credit carry needs the invoice-time walk (no warn observed on plain save). Batch-2. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): floor + tax-still-owed + total=tax + excessCreditAmount all proven; UI dialog preview also shows the floor (shot b6-warn2-filled). | FRESH VIU 2026-07-10: non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="O174" s="15" t="inlineStr">
         <is>
-          <t>Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c). | VIU qb batch-1 (2026-07-08): Taxable over-discount example pending with FD-CALC-015. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): taxable over-discount zeroes tax and total; non-taxable contrast proven. | FRESH VIU 2026-07-10: taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c). | VIU qb batch-1 (2026-07-08): Taxable over-discount example pending with FD-CALC-015. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): taxable over-discount zeroes tax and total; non-taxable contrast proven. | FRESH VIU 2026-07-10: taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -15055,8 +15055,8 @@
       </c>
       <c r="L176" s="15" t="inlineStr">
         <is>
-          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  +20%' and +$50.00 as plain text — no colored badge or pill.
-2. The part fee row shows '↳ test  +11%' and +$2.20 as plain text — no colored badge or pill.
+          <t>1. The Fees/Discounts row under Labor shows '↳ ttt  20%' (a percentage fee shows no sign) and +$50.00 as plain text — no colored badge or pill.
+2. The part fee row shows '↳ test  11%' (a percentage fee shows no sign) and +$2.20 as plain text — no colored badge or pill.
 3. The collapsed line total at the top-right equals Labor + labor fee + Parts + part fee = $250.00 + $50.00 + $20.00 + $2.20 = $322.20.
 4. The line total is NOT $270.00 (it must not leave out the two fees).</t>
         </is>
@@ -15068,12 +15068,12 @@
       </c>
       <c r="N176" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O176" s="15" t="inlineStr">
         <is>
-          <t>SV-8480 (Story Defect under SV-8279, Epic SV-7387; PO Chris Ward): the per-line total_cost previously summed Labor + Parts gross only and ignored the line's own fees/discounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'+11%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($322.20) unchanged.</t>
+          <t>SV-8480 (Story Defect under SV-8279, Epic SV-7387; PO Chris Ward): the per-line total_cost previously summed Labor + Parts gross only and ignored the line's own fees/discounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'+11%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($322.20) unchanged. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): VIU-VERIFIED. Seeded ZZAUTOTEST WO (Labor $290 + Part $40; dialog auto-computes labour/margin so exact 250/20 not dialable, behavior identical). Lines-tab collapsed line Total observed = $392.40 = 290 + labor fee ttt +20% ($58.00) + 40 + part fee test +11% ($4.40); NOT gross $330. Rows render PLAIN TEXT bare '20%'/'11%' (no plus sign, no colored badge; HTML span text-grey-7). Ev: 018-lines-collapsed-full.png, 018-lines-expanded-full.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>1. The labor fee shows '↳ &lt;name&gt;  +20%' and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
+          <t>1. The labor fee shows '↳ &lt;name&gt;  20%' (a percentage fee shows no sign) and a plus amount (+$50.00 on $250.00) as plain text — no colored badge or pill.
 2. The part discount shows '↳ &lt;name&gt;  −10%' and a minus amount (−$2.00 on $20.00) as plain text — no colored badge or pill.
 3. The collapsed line total adds the fee and subtracts the discount: Labor $250.00 + fee $50.00 + Part $20.00 - discount $2.00 = $318.00.
 4. Fees increase the line total; discounts reduce it.</t>
@@ -15146,12 +15146,12 @@
       </c>
       <c r="N177" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O177" s="18" t="inlineStr">
         <is>
-          <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'-10%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($318.00) unchanged.</t>
+          <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'-10%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($318.00) unchanged. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. On the seeded line (Labor $290 + Parts $40) a labor fee +20% ($58.00) added and a part discount -10% (-$4.00) subtracted -&gt; collapsed line Total = $384.00 = 290 + 58 + 40 - 4.00 (fee adds, discount subtracts). Discount rate renders '-10%' (en-dash minus) plain text, resolved -$4.00; fee rate renders bare '20%'. Ev: 019-lines-collapsed-full.png, 019-lines-expanded-full.png, api-FD-CALC-019-total_cost-384.00.json.</t>
         </is>
       </c>
     </row>
@@ -15221,12 +15221,12 @@
       </c>
       <c r="N178" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O178" s="15" t="inlineStr">
         <is>
-          <t>SV-8480 QA step 2 / S3-R18: a line without any fee/discount keeps a gross Labor + Parts total (no change from the fix).</t>
+          <t>SV-8480 QA step 2 / S3-R18: a line without any fee/discount keeps a gross Labor + Parts total (no change from the fix). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. A ZZAUTOTEST line with no fees/discounts (Labor $290 + Parts $40) shows collapsed line Total = $330.00 = gross Labor + Parts only, no Fees/Discounts rows. Ev: 020-lines-nofee-line.png, api-baseline-nofees-total_cost-330.json.</t>
         </is>
       </c>
     </row>
@@ -15297,12 +15297,12 @@
       </c>
       <c r="N179" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O179" s="18" t="inlineStr">
         <is>
-          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Estimate document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted.</t>
+          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Estimate document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. Estimate document (Finance tab, EST-S3-25836): Labor prints GROSS $290.00; the line fee prints as its own row '↳ ttt (% of labor) $58.00'; the document Line Total = $330.00 (gross Labor+Parts, fee NOT folded in); every fee/discount (incl. line-level ttt +$58.00 and pdisc ($4.00)) listed once in the Fees &amp; Discounts breakdown -&gt; no double-count. Confirms the fix is Lines-tab display-only; estimate unchanged. Ev: 021-finance-tab.png.</t>
         </is>
       </c>
     </row>
@@ -15373,12 +15373,12 @@
       </c>
       <c r="N180" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O180" s="15" t="inlineStr">
         <is>
-          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Invoice document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted.</t>
+          <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Invoice document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. Invoice document (Finance tab toggle, INV-S3-25836): renders identically to the estimate — Labor gross $290.00, the line fee prints as its own row '↳ ttt (% of labor) $58.00', document Line Total = $330.00 (gross, fee not folded in), each fee listed once -&gt; no double-count. Ev: 022-invoice-view.png.</t>
         </is>
       </c>
     </row>
@@ -15448,12 +15448,12 @@
       </c>
       <c r="N181" s="18" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Blocked-Env</t>
         </is>
       </c>
       <c r="O181" s="18" t="inlineStr">
         <is>
-          <t>SV-8480 QA step 4 / S3-R18: for an organization without the Fees &amp; Discounts feature, line totals stay gross-only (the roll-in is gated by the feature).</t>
+          <t>SV-8480 QA step 4 / S3-R18: for an organization without the Fees &amp; Discounts feature, line totals stay gross-only (the roll-in is gated by the feature). | LIVE STAGING VIU 2026-07-22: BLOCKED-ENV. The FeesAndDiscounts feature flag is ON at the org level on the SHARED staging org (d55bc308); toggling it OFF org-wide during an unattended run would strip F&amp;D from all users and break concurrent/later VIU batches, and no separate flag-off org is available. Not inferred — needs a dedicated flag-off org/state to verify live.</t>
         </is>
       </c>
     </row>
@@ -15523,12 +15523,12 @@
       </c>
       <c r="N182" s="15" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O182" s="15" t="inlineStr">
         <is>
-          <t>SV-8480 / S3-R18: backend fix in the per-line total_cost computation (Stefan Vukovic, PR ShopView/shopview#2228) — previously Labor + Parts gross only, now adds the line's signed fee/discount amounts. Display-only, no stored values change. API-section case per Standing Rule 4 (verifies a backend value/response).</t>
+          <t>SV-8480 / S3-R18: backend fix in the per-line total_cost computation (Stefan Vukovic, PR ShopView/shopview#2228) — previously Labor + Parts gross only, now adds the line's signed fee/discount amounts. Display-only, no stored values change. API-section case per Standing Rule 4 (verifies a backend value/response). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. GET /api/work-orders/lines/{wo} returned per-line total_cost = 392.40 = Labor 290 + labor fee 58 + Parts 40 + part fee 4.40 (signed sum), NOT 330. Stored line amounts unchanged (labour_rate 145, total_labour_cost 290, part sell_price 40); the fee/discount amounts live separately under line.adjustments[] and part_requests[].adjustments[] (resolvedAmount 58 / 4.40) — computed total is display-only. Ev: api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="O189" s="18" t="inlineStr">
         <is>
-          <t>Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: /administration/adjustment-templates route meta requiredPermissions=['settingsFinance'] (S13-R8 wiring present in FE). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced) | MERGED VERDICT: BE-enforced — pass A Technician (no settingsFinance) got 403 on template list AND create. | FRESH VIU 2026-07-10: templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: /administration/adjustment-templates route meta requiredPermissions=['settingsFinance'] (S13-R8 wiring present in FE). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced) | MERGED VERDICT: BE-enforced — pass A Technician (no settingsFinance) got 403 on template list AND create. | FRESH VIU 2026-07-10: templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="O193" s="18" t="inlineStr">
         <is>
-          <t>OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging. | VIU qb batch-1 (2026-07-08): Invoiced/Paid gating verified both layers: paid WO hides all add/edit/remove controls (toolbar menu = Audit Log/Timesheets only) and API add -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' History-mode half untestable (spec never defines history mode — open question #3). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order" | FRESH VIU 2026-07-10: Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging. | VIU qb batch-1 (2026-07-08): Invoiced/Paid gating verified both layers: paid WO hides all add/edit/remove controls (toolbar menu = Audit Log/Timesheets only) and API add -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' History-mode half untestable (spec never defines history mode — open question #3). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order" | FRESH VIU 2026-07-10: Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="O197" s="18" t="inlineStr">
         <is>
-          <t>Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields. | VIU qb batch-1 (2026-07-08): The Add/Create buttons are NEVER disabled (design §6 enable-rule not implemented). Build validates on submit with inline field errors + error toasts and keeps the dialog open. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B -&gt; confirmed defect (BUG-FD-4). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields. | VIU qb batch-1 (2026-07-08): The Add/Create buttons are NEVER disabled (design §6 enable-rule not implemented). Build validates on submit with inline field errors + error toasts and keeps the dialog open. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B -&gt; confirmed defect (BUG-FD-4). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="O198" s="15" t="inlineStr">
         <is>
-          <t>Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging. | VIU qb batch-1 (2026-07-08): Blank/0 amount: inline 'Percent must be greater than 0'/'Amount must be greater than 0' + API 400 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging. | VIU qb batch-1 (2026-07-08): Blank/0 amount: inline 'Percent must be greater than 0'/'Amount must be greater than 0' + API 400 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="O199" s="18" t="inlineStr">
         <is>
-          <t>Verify the exact 100-character enforcement (hard cap vs error) on staging. | VIU qb batch-1 (2026-07-08): Empty name: inline 'Name is a required field', save blocked. Template name maxlength=100 enforced; WO-dialog name input present (maxlength not read — spot-check in batch 2). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer" | FRESH VIU 2026-07-10: UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Verify the exact 100-character enforcement (hard cap vs error) on staging. | VIU qb batch-1 (2026-07-08): Empty name: inline 'Name is a required field', save blocked. Template name maxlength=100 enforced; WO-dialog name input present (maxlength not read — spot-check in batch 2). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer" | FRESH VIU 2026-07-10: UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="O200" s="15" t="inlineStr">
         <is>
-          <t>Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging. | VIU qb batch-1 (2026-07-08): Discount &gt;100% invalid at save (toast + API 400); fee percentage uncapped (150% saved). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted | FRESH VIU 2026-07-10: discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging. | VIU qb batch-1 (2026-07-08): Discount &gt;100% invalid at save (toast + API 400); fee percentage uncapped (150% saved). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted | FRESH VIU 2026-07-10: discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="O201" s="18" t="inlineStr">
         <is>
-          <t>Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring. | VIU qb batch-1 (2026-07-08): Negative amounts rejected (API 400 'must be greater than zero'; UI numeric inputs). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring. | VIU qb batch-1 (2026-07-08): Negative amounts rejected (API 400 'must be greater than zero'; UI numeric inputs). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="O202" s="15" t="inlineStr">
         <is>
-          <t>Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat). | VIU qb batch-1 (2026-07-08): Max Amount shows only for percentage methods (verified in WO + template dialogs). DEVIATION: maxCap=0 via API = NO cap (not 'treated as empty'+'forces $0' per spec) — see FDBUG-9; UI 0-entry behavior still to spot-check. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage | FRESH VIU 2026-07-10: FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged).</t>
+          <t>Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat). | VIU qb batch-1 (2026-07-08): Max Amount shows only for percentage methods (verified in WO + template dialogs). DEVIATION: maxCap=0 via API = NO cap (not 'treated as empty'+'forces $0' per spec) — see FDBUG-9; UI 0-entry behavior still to spot-check. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage | FRESH VIU 2026-07-10: FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="O203" s="18" t="inlineStr">
         <is>
-          <t>OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1). | VIU qb batch-1 (2026-07-08): Template both auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (dedup works; known S9 gap not reproduced). | [pass A same-day parallel verdict] VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1 | CONFLICT NOTE: see FD-CUST-016 - pass B controlled repro got ONE adjustment per template (no double-add). | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q2=A): adding only once is confirmed as the settled intended behavior; EXPECTED re-scoped from 'known bug may add twice — record actual count' to exactly ONE. BUG-FD-1 closed as settled. | FRESH VIU 2026-07-10: auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT.</t>
+          <t>OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1). | VIU qb batch-1 (2026-07-08): Template both auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (dedup works; known S9 gap not reproduced). | [pass A same-day parallel verdict] VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1 | CONFLICT NOTE: see FD-CUST-016 - pass B controlled repro got ONE adjustment per template (no double-add). | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q2=A): adding only once is confirmed as the settled intended behavior; EXPECTED re-scoped from 'known bug may add twice — record actual count' to exactly ONE. BUG-FD-1 closed as settled. | FRESH VIU 2026-07-10: auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -905,7 +905,8 @@
     <col width="56" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -981,6 +982,11 @@
       </c>
       <c r="O1" s="13" t="inlineStr">
         <is>
+          <t>What needs to be done (plain)</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -1063,6 +1069,11 @@
         </is>
       </c>
       <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>Design↔spec: spec title = 'New Fee / Discount'; design mockup title = 'Add new fee/discount'. Authored to spec; flag the label difference at execution. Toolbar label 'Add Work Order Fee / Discount' is per S1-R1/S11-R4a comparison. | VIU qb batch-1 (2026-07-08): Dialog opens from WO toolbar 3-dot menu at whole-WO scope, no 'Applying to' subtitle (S2-R12 ok). DEVIATIONS: menu item reads 'Add Fee/Discount' (spec 'Add Work Order Fee / Discount'); add-dialog title reads 'Add new fee/discount' (spec 'New Fee / Discount'; the EDIT dialog title 'Edit Fee / Discount' DOES match). Shots s8-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: whole-WO "Add new fee/discount" dialog opens from WO toolbar ⋯ menu (cap-add-dialog.png) | FRESH VIU 2026-07-10: dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
         </is>
@@ -1151,6 +1162,11 @@
       </c>
       <c r="O3" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
           <t>Whole-WO Flat Amount base = the set amount, no quantity (open question #2 in requirements §14: no explicit Whole-WO Flat base row). Confirm button label per spec is 'Add Fee'; design mockup uses fixed 'Add' — flag. | VIU qb batch-1 (2026-07-08): Flat $12 fee added via dialog; confirm button 'Add Fee'; success toast 'Fee added' (exact, auto-fades); entry appears on the WO F&amp;D card; API POST work-orders/adjustments/add 201. Shots s9-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI+API: whole-WO flat $11 fee saved (POST 201), card shows entry; toast "Fee added" (§7, recon) | FRESH VIU 2026-07-10: whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -1235,6 +1251,11 @@
         </is>
       </c>
       <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
         <is>
           <t>Design↔spec: the design preview always computes a percentage against the single flat WO Total and has NO base selector, whereas spec §5-R4 says whole-WO % must resolve against Net Labor / Net Parts / Subtotal depending on method. This is requirements open question #1. On staging, confirm which base is actually used; the −$857.23 number here matches the design's single-total math. | VIU qb batch-1 (2026-07-08): Live preview verified numerically on subtotal $292.83: 25% fee -&gt; 'Fee · 25% +$73.21' (rounding ok), 150% discount -&gt; '-$439.25 / New work-order subtotal $0.00' (preview floors at $0). Preview updates as you type; 'Tax is recalculated on save.' present. Shots s8-07/08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: live preview "Work-order subtotal $1,214.81 → Fee · 10% +$121.48 → New subtotal $1,336.29 / Tax is recalculated on save" (cap-add-filled.png) | FRESH VIU 2026-07-10: dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -1322,6 +1343,11 @@
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
           <t>Design mockup uses a 6-entry dropdown (Fleet Standard Discount, Loyalty Discount, Parts Handling Fee, Environmental Fee, Early Payment Discount, Labor Surcharge). Spec says the real product shares one location template library; substitute an actual staging template name if different. Taxable is not collected by the design's Add modal (design↔spec discrepancy #2). | VIU qb batch-1 (2026-07-08): 'Apply From Template' filled Name/Type/Calc/Amount from template 'Flat fee' ($12 flat) and preview updated; saved copy is independent (appliedBy=manual, templateId recorded). Shot s9-01. | FRESH VIU 2026-07-10: not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1410,6 +1436,11 @@
       </c>
       <c r="O6" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
           <t>The disabled-Add rule is the design's only validation gate; spec S2-N1/S2-N2 also expect inline error text on empty Name/Amount, which the design mockup does NOT render (design open item §10). Verify whether staging shows inline errors in addition to the disabled button. | VIU qb batch-1 (2026-07-08): Add button is NEVER disabled. Build validates on save: inline errors ('Name is a required field', 'Percent must be greater than 0') and error toast for &gt;100% discount; dialog stays open. Design's disabled-until-valid rule not implemented. Shot s8-10. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B confirms disabled-until-valid is correct; build wrong -&gt; confirmed defect (BUG-FD-4), not a PO question. | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1494,6 +1525,11 @@
       </c>
       <c r="O7" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
           <t>Design↔spec discrepancy #4: the design shows 'Max cap' unconditionally and even caps Flat Amount, while spec (S2-R24, §5-R6) shows Max Amount ONLY for a percentage method and never for Flat/Processing Fee. Field label is 'Max Amount (Optional)' per spec vs 'Max cap' in design. Also verify an entered Max Amount of 0 is treated as empty / no maximum (§5-R6, S2-R25). | VIU qb batch-1 (2026-07-08): Max cap verified: API 10% of $324.60 -&gt; capped to $5 (maxCap 5); customer-default 10%/max-15 discount resolved -$15.00 (raw $29.28). 'Max Amount (Optional)' field shows for % methods only. Flat+maxCap rejected: 'A flat adjustment cannot have a maximum cap.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: percentage capped by maxCap ($121.48→$50 at cap $50) | FRESH VIU 2026-07-10: 20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1573,6 +1609,11 @@
         </is>
       </c>
       <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
         <is>
           <t>Design↔spec: the design mockup uses a fixed 'Add' button label that does NOT change with Type. Authored to spec S2-R27; flag the fixed label if staging matches the mockup. | VIU qb batch-1 (2026-07-08): Confirm button flips live with Type: 'Add Fee' &lt;-&gt; 'Add Discount'. Shot s8-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: confirm button label follows Type (Add Fee / Add Discount) | FRESH VIU 2026-07-10: confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -1655,6 +1696,11 @@
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
           <t>Verify whether staging surfaces an inline 'Name required' error (spec) or only keeps the button disabled (design). | VIU qb batch-1 (2026-07-08): Empty Name blocks save; inline 'Name is a required field'; nothing persisted. Shot s8-10. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "name is required" | FRESH VIU 2026-07-10: UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1735,6 +1781,11 @@
       </c>
       <c r="O10" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="inlineStr">
+        <is>
           <t>Confirm minimum enforcement: Flat &lt; $0.01 and Percentage &lt; 0.01% are invalid (§5-R1). | VIU qb batch-1 (2026-07-08): 0/empty amount blocks: inline 'Percent must be greater than 0' / 'Amount must be greater than 0'; API rejects 0 and negative with 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1814,6 +1865,11 @@
         </is>
       </c>
       <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>The design mockup does not model the &gt;100% discount validation (no inline error states). Verify the guard exists on staging. | VIU qb batch-1 (2026-07-08): Discount 150% save blocked with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API: 100%=201, 100.01%=400). Fee 150% accepted (resolved $486.90). Note: block is a save-time toast, not inline. Shots s8-08/09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount rejected; 150% fee accepted (no cap) | FRESH VIU 2026-07-10: discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -1899,6 +1955,11 @@
       </c>
       <c r="O12" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P12" s="15" t="inlineStr">
+        <is>
           <t>Design open question #1: the design Add modal only offers 'Percentage'/'Flat amount' with no base selector and computes % off a single flat total. Spec §5-R10 requires the four distinct whole-WO methods. Authored to spec; on staging confirm whether the base is a selectable Calculation type option or is chosen elsewhere. | VIU qb batch-1 (2026-07-08): % of Subtotal base = net labor + net parts + shop supplies: 25% x $292.83 (265 labor + 27.83 SS) = $73.21 in preview; API resolved values match. Base also includes line-level adjustment effects (net), verified: after +$31.77 line-level fees, 100% subtotal discount resolved -$324.60. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal/pct_labor/pct_parts each resolve on correct base ($121.48/$74.98/$38.63) | FRESH VIU 2026-07-10: pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -1980,6 +2041,11 @@
       </c>
       <c r="O13" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
           <t>Also verify per-entry/per-row Edit/Delete 3-dot menus are hidden on Invoiced/Paid WOs (S3-N3). | VIU qb batch-1 (2026-07-08): Paid WO S3-15889: toolbar menu = 'Audit Log | Timesheets' only (Add Fee/Discount hidden); API add on invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' Shot s14-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Invoiced/Paid WO → 409 rejected (S3-R1b) | FRESH VIU 2026-07-10: add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -2059,6 +2125,11 @@
       </c>
       <c r="O14" s="15" t="inlineStr">
         <is>
+          <t>The option is only hidden on the screen — the system still lets the change go through behind the scenes. Ask the team whether the system should also block it in the background, not just hide the button, then re-test.</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
           <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch.</t>
         </is>
       </c>
@@ -2138,6 +2209,11 @@
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
           <t>Also verify the totals-load-failure preview text 'We couldn't load the figures to preview this selection.' (S2-R42) if a failure can be simulated. | VIU qb batch-1 (2026-07-08): Empty-amount preview reads exactly 'Enter an amount to see the impact.' Shot s8-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: empty-amount preview reads "Enter an amount to see the impact." (cap-add-dialog.png) | FRESH VIU 2026-07-10: 'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -2217,6 +2293,11 @@
         </is>
       </c>
       <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P16" s="15" t="inlineStr">
         <is>
           <t>Design↔spec color conflict: the design mockup renders DISCOUNT amounts in green (--sv-success-text) and FEE amounts in amber/warning (--sv-warning-text), the OPPOSITE of spec S2-R33 (fee green, discount red). Authored the expected to spec; flag the mismatch and confirm the actual color on staging. | VIU qb batch-1 (2026-07-08): Preview row signed+colored: fee 'Fee · 25% +$66.25' GREEN rgb(33,186,69) (computed style); discount 'Discount · 150% -$439.25' RED (shot s8-08). Only place green/red used, consistent with S12-R2. | FRESH VIU 2026-07-10: preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -2301,6 +2382,11 @@
       </c>
       <c r="O17" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
           <t>NEW 2026-07-13 for V1_2 §5-R15 / S2-R26a. UI string check (advisory) — belongs in a FUNCTIONAL section, NOT an API section (standing rule 4). Assert the exact string verbatim. | WORDING+VIU 2026-07-13: 'Taxable' is a Yes/No TOGGLE (not a dropdown) — corrected. DEVIATION: the §5-R15 jurisdiction note is NOT shown below the Taxable toggle in this build (checked the whole-WO Add dialog with both Flat Amount and % of Subtotal; no note present — shots wo-03/wo-05). Expected kept as the spec requirement; currently a gap. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier and the SFD-negative check is FOLDED IN here as expected 4 (no new case authored). The gate does NOT legitimize the deviation — the 2026-07-13 VIU was as admin (HAS See Financial Data) and the note was absent, so the note is still not built. Status stays VIU-Deviation. Observability caveat (spec-diff §H.b): a user without See Financial Data cannot open the WO Add/Edit dialog at all (Stories 1/2 require SFD), so the negative is only independently observable at the admin template/Processing-Fee dialog. Spec ambiguity flagged for Chris (§H.a): the change-log names 'the template dialog' as the second gated location while the §5-R15 body names the Processing Fee dialog (S8-R11). | STAGING VIU 2026-07-20 staging LIVE VIU: §5-R15 note now BUILT: present below Taxable in WO Add ("Add new fee/discount") + Edit ("Edit Fee / Discount") dialogs, exact string; gated on See Financial Data (Tech w/o SFD: no note). Live staging (wo-add-dialog-final.png / wo-fee-edit-dialog.png / tech-tmpl-dialog.png). WAS Deviation on qb (note absent). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -2384,6 +2470,11 @@
       </c>
       <c r="O18" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="inlineStr">
+        <is>
           <t>Line-level add/edit/remove maps to Work Order Lines: Create &amp; Edit (S13-R4). Design mockup subtitle format is a scope link; spec exact string is 'Applying to: Line {N} Labor — {name}'. | VIU qb batch-1 (2026-07-08): Line 3-dot menu 'Add Fee/Discount' opens dialog locked to Labor Line with grey subtitle 'Applying to: (L) CVIP - Light Duty Truck - Wheels On'. DEVIATION: subtitle omits the spec 'Line {N} Labor —' prefix (S2-R10). Calc locked to labor methods. Shots s12-01/02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+UI: labor-line ⋯ opens dialog scope-locked "Applying to: {line}", Calc default "% Of Labor Total" | FRESH VIU 2026-07-10: label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023. | VIU 2026-07-22 LIVE: labor dialog title 'New Labor Fee / Discount', subline 'Applying To: Line 1 Labor — ZZAUTOTEST 8480 line', scope locked. Ev: wo/FD-LABOR-001-labor-dialog.png, wo/labor-dialog-text.txt.</t>
         </is>
       </c>
@@ -2468,6 +2559,11 @@
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="inlineStr">
+        <is>
           <t>Default method for a labor line = % of Labor Total (S2-R22). Note the design Add modal lacks base-aware calc options (open question #1). | VIU qb batch-1 (2026-07-08): % of Labor Total resolves on the line's gross labor price: API 10% of $265 = $26.50; UI preview 25% -&gt; 'Line labor total $265.00 / Fee · 25% +$66.25 / New line labor total $331.25' (exact S2-R36a labels). Shot s12-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line pct_labor 10% resolves on gross line labor $749.75 → $74.98 | FRESH VIU 2026-07-10: pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
@@ -2548,6 +2644,11 @@
         </is>
       </c>
       <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="inlineStr">
         <is>
           <t>Contrast with Part Line Flat Amount, which IS per-item × quantity (see FD-PART-002). | VIU qb batch-1 (2026-07-08): Labor-line Flat $5 resolved exactly $5.00 (no quantity multiplier), API-verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: labor_line flat $10 → +$10.00 exact (no quantity) | FRESH VIU 2026-07-10: labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
@@ -2631,6 +2732,11 @@
       </c>
       <c r="O21" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
+        <is>
           <t>Line-level adjustments show wherever their target shows, including a Needs Approval estimate (§5-R12). | VIU qb batch-1 (2026-07-08): Line status -&gt; authorization_declined: both line adjustments resolved to $0; restore to authorized -&gt; $66.25 / -$5 again. §5-R12 verified end-to-end via API. | FRESH VIU 2026-07-10: prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
@@ -2712,6 +2818,11 @@
       </c>
       <c r="O22" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P22" s="15" t="inlineStr">
+        <is>
           <t>Deleting a line/part removes its adjustments even though removal normally uses the Create &amp; Edit permission (this is a whole-record delete). | VIU qb batch-1 (2026-07-08): work-orders/lines/delete removed the line AND both adjustments pointing to it; WO summary recomputed (S3-R2). | FRESH VIU 2026-07-10: prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -2791,6 +2902,11 @@
         </is>
       </c>
       <c r="O23" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
         <is>
           <t>Labor/part-line actions require Work Order Lines: Create &amp; Edit (S13-R4), distinct from the whole-WO permission (S13-R3). | VIU qb batch-1 (2026-07-08): No second-user login on qb env; WO-Lines-C&amp;E gating not exercisable this batch. | FRESH VIU 2026-07-10: FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged. | VIU 2026-07-22 LIVE: menu label 'Add Labor Fee / Discount' confirmed present; permission-negative behavior (hidden without Work Order Lines: Create &amp; Edit) unchanged from prior verification — role-negative not re-driven this UI batch.</t>
         </is>
@@ -2875,6 +2991,11 @@
       </c>
       <c r="O24" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P24" s="15" t="inlineStr">
+        <is>
           <t>Default method for a part = % of Parts Total (S2-R22). Design subtitle is a scope link; spec exact string is 'Applying to: Line {N} Part — ({part number}) {description}'. | VIU qb batch-1 (2026-07-08): Not driven in batch 1 — no part staged on the throwaway WO (part-request seeding flow not automated yet). API scope 'part_line' exists. Batch-2: seed a part request, drive the part-row menu. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: part row ⋯ menu offers Add Fee/Discount → part_line scope | FRESH VIU 2026-07-10: FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024. | VIU 2026-07-22 LIVE: part menu label 'Add Part Fee / Discount' + dialog title 'New Part Fee / Discount', subline 'Applying To: Line 1 Part — Turbocharger Oil', default Calculation Type '% Of Parts Total'. Ev: wo/FD-PART-001-part-dialog.png, wo/part-dialog-text.txt.</t>
         </is>
       </c>
@@ -2958,6 +3079,11 @@
       </c>
       <c r="O25" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
           <t>Key edge behavior — Part Line Flat Amount is the only Flat Amount scope that multiplies by quantity. See FD-PART-008 for the qty=1 edge (−$5.00). | VIU qb batch-1 (2026-07-08): Per-item flat (amount x qty) not verified — needs a real part target with qty&gt;1. Batch-2. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line flat $5 × qty 2 = $10.00 (per-item) | FRESH VIU 2026-07-10: per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged. | VIU 2026-07-22 LIVE: inline part fee renders plain text ('Part Fee 11% +$4.40'), no colored badge; per-item flat calc unchanged (verified prior passes). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
@@ -3041,6 +3167,11 @@
       </c>
       <c r="O26" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P26" s="15" t="inlineStr">
+        <is>
           <t>The part menu offers 'Add fee / discount' for both staged and requested parts (S1-R4). See FD-PART-005 for requested→received persistence. | VIU qb batch-1 (2026-07-08): Requested-part adjustment not driven (no part seeded). Batch-2. | FRESH VIU 2026-07-10: prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
@@ -3123,6 +3254,11 @@
       </c>
       <c r="O27" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P27" s="18" t="inlineStr">
+        <is>
           <t>Part Line percentage base uses the target's gross part total (before whole-WO nets). | VIU qb batch-1 (2026-07-08): Not driven; % of Parts Total preview at whole-WO scope showed 'Base · Parts total $0.00 -&gt; +$0.00' ($0-base rule ok). Real part-line base check pending. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part_line pct_parts 10% on qty×sell (2×$116.34=$232.68) → $23.27 | FRESH VIU 2026-07-10: pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
@@ -3203,6 +3339,11 @@
         </is>
       </c>
       <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>Re-test on staging once a part can be moved from requested to received (this was blocked by an environment error before). Check the fee/discount stays attached after the part is received.</t>
+        </is>
+      </c>
+      <c r="P28" s="15" t="inlineStr">
         <is>
           <t>Companion to FD-PART-003 (adding to a requested part). | VIU qb batch-1 (2026-07-08): Requested-&gt;received attachment not driven. Batch-2. | FRESH VIU 2026-07-10: STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied.</t>
         </is>
@@ -3286,6 +3427,11 @@
       </c>
       <c r="O29" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P29" s="18" t="inlineStr">
+        <is>
           <t>A part is billable when authorized, not declined, and still has quantity left (§5-R12). | VIU qb batch-1 (2026-07-08): Declined/returned-part $0 resolve not driven (labor-line analogue verified). Batch-2. | FRESH VIU 2026-07-10: prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
@@ -3367,6 +3513,11 @@
       </c>
       <c r="O30" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P30" s="15" t="inlineStr">
+        <is>
           <t>Same delete-cascade behavior as labor lines (FD-LABOR-006). | VIU qb batch-1 (2026-07-08): Part deletion cascade not driven (line-delete cascade verified for labor). Batch-2. | FRESH VIU 2026-07-10: prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
@@ -3447,6 +3598,11 @@
         </is>
       </c>
       <c r="O31" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P31" s="18" t="inlineStr">
         <is>
           <t>Confirms quantity changes re-resolve a Part Line Flat Amount adjustment (§5-R14). | VIU qb batch-1 (2026-07-08): Qty-1 per-item edge pending with FD-PART-002. | FRESH VIU 2026-07-10: qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
@@ -3532,6 +3688,11 @@
       </c>
       <c r="O32" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P32" s="15" t="inlineStr">
+        <is>
           <t>Plain grey (not green/red) is correct outside the Add/Edit preview (S12-R1/R2). | VIU qb batch-1 (2026-07-08): Labor adjustment renders inside the line as 'Fees/Discounts  ↳ ZZAUTOTEST line fee  (+25%)' pill badge + right-side grey signed '+$66.25' + per-row ⋮. Shot s13-01. | FRESH VIU 2026-07-10: batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half). | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): sign convention RE-VERIFIED live on the Lines tab — a percentage labor FEE renders as a BARE '20%' (no sign) in plain grey text (HTML span text-grey-7, no colored badge/pill); a percentage DISCOUNT renders '−10%' (en-dash minus); resolved amount is signed on the right ('+$58.00' / '−$4.00'); '↳' arrow, blank left label. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Labor Fee 20%' (fee bare %, blank left label, plain text, no badge) '+$101.98'; '↳ Labor Disc −10% −$50.99' (discount minus). Ev: wo/inline-expanded-text.txt, wo/inline-expanded.png.</t>
         </is>
       </c>
@@ -3615,6 +3776,11 @@
       </c>
       <c r="O33" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P33" s="18" t="inlineStr">
+        <is>
           <t>Flat rate badge = signed dollar amount; percentage rate badge = signed percent with zeros removed (S3-R6/R7, S12-R4). | VIU qb batch-1 (2026-07-08): Part-line inline row pending (no part seeded). Batch-2. | FRESH VIU 2026-07-10: as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half). | LIVE STAGING VIU 2026-07-22: part-line sign convention RE-VERIFIED live — a percentage part FEE renders bare '11%' (no sign) plain grey text (no badge); a percentage part DISCOUNT renders '−10%' (en-dash minus); resolved signed '+$4.40' / '−$4.00'. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Part Fee 11% +$4.40' plain text, no badge. Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
@@ -3699,6 +3865,11 @@
       </c>
       <c r="O34" s="15" t="inlineStr">
         <is>
+          <t>A developer needs to add the 'Show N more' collapse so a line with two or more fees/discounts no longer shows them all at once. Re-test once fixed.</t>
+        </is>
+      </c>
+      <c r="P34" s="15" t="inlineStr">
+        <is>
           <t>Same collapse/expand behavior applies to a labor line with 2+ adjustments. | VIU qb batch-1 (2026-07-08): With 2 adjustments on the line BOTH rows show; NO 'Show N more'/'Show less' toggle exists (S3-R15/R16 not implemented). Shot s13-01. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q5=B -&gt; confirmed defect (BUG-FD-5). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
         </is>
       </c>
@@ -3783,6 +3954,11 @@
       </c>
       <c r="O35" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
           <t>Numbers taken from the design mockup (placeholder data); confirm actual stacked figures on staging. | VIU qb batch-1 (2026-07-08): Line Total column shows $265 gross only — does NOT add the line's own adjustment amounts (+66.25/-5) (S3-R18). Same on the estimate doc ('Line Total $265.00'). Shot s13-01/s14b. | FRESH VIU 2026-07-10: batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): RE-CONFIRMED live — the collapsed line Total on the Lines tab adds the line's own SIGNED fee/discount amounts on top of gross Labor + Parts: $392.40 with a labor fee +20% ($58.00) + part fee +11% ($4.40) on a $290 labor / $40 parts line; $330.00 gross when the line has no fees; display-only, no stored value changes. Ev: 018-lines-collapsed-full.png, 020-lines-nofee-line.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
@@ -3864,6 +4040,11 @@
       </c>
       <c r="O36" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P36" s="15" t="inlineStr">
+        <is>
           <t>Design uses 'Edit/Delete' wording inline; spec says removal uses the Create &amp; Edit permission (not the Delete permission) despite the 'Delete' label (design↔spec wording note #7). | VIU qb batch-1 (2026-07-08): Per-row ⋮ control IS present on each inline adjustment row (shot s13-01) but its menu items could not be opened programmatically this batch — Edit/Remove content unconfirmed (card-entry menus show Edit|Remove). | FRESH VIU 2026-07-10: 3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
@@ -3946,6 +4127,11 @@
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P37" s="18" t="inlineStr">
+        <is>
           <t>Design↔spec column-label difference: spec S4-R2 = '%' column; design mockup = 'Value' column. Authored to spec; flag the actual header on staging. | VIU qb batch-1 (2026-07-08): Stats F&amp;D section is an AGGREGATE: 'Fees (3) $227.90 / Discounts (0) $0.00 / Net $227.90' — NOT the spec per-adjustment table with % and Amount columns (S4-R2/R3). Shot s11b-03. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: build Stats shows AGGREGATE rows (Fees (N)/Discounts/Net) not per-adjustment %/Amount columns (S4-R2/R3). See bugs-log BUG-FD-2 | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
         </is>
       </c>
@@ -4028,6 +4214,11 @@
       </c>
       <c r="O38" s="15" t="inlineStr">
         <is>
+          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
+        </is>
+      </c>
+      <c r="P38" s="15" t="inlineStr">
+        <is>
           <t>Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows exist in the aggregate layout, so no scope hyperlink per row (design §3 not built). | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2), per-row layout is correct. | FRESH VIU 2026-07-10: per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
@@ -4109,6 +4300,11 @@
       </c>
       <c r="O39" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P39" s="18" t="inlineStr">
+        <is>
           <t>The design mockup's Stats total placeholder (−$1,198.02) disagrees with its Financial Info total (−$2,055.25) for the same '(5)' set — treat as mock placeholder inconsistency (design §3 warning). Expected here uses the correct signed sum −$2,055.25. | VIU qb batch-1 (2026-07-08): Aggregate 'Net' equals the signed sum (227.90 = 200+12+15.90-0) but the spec'd per-row Total-with-columns layout is absent. | FRESH VIU 2026-07-10: net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
@@ -4189,6 +4385,11 @@
       </c>
       <c r="O40" s="15" t="inlineStr">
         <is>
+          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
+        </is>
+      </c>
+      <c r="P40" s="15" t="inlineStr">
+        <is>
           <t>The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows -&gt; creation-order rule not applicable in current build. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2); creation-order verifiable once per-row layout ships. | FRESH VIU 2026-07-10: creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
@@ -4267,6 +4468,11 @@
         </is>
       </c>
       <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P41" s="18" t="inlineStr">
         <is>
           <t>Mirrors the Financial Info row hidden state (S3-N2) and the sidebar card hidden state (S3-N1). | VIU qb batch-1 (2026-07-08): Hidden-when-none not captured this batch (every walked WO had adjustments). Quick re-check in batch 2. | FRESH VIU 2026-07-10: no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
@@ -4351,6 +4557,11 @@
       </c>
       <c r="O42" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P42" s="15" t="inlineStr">
+        <is>
           <t>This is a distinct count/total from the sidebar 'Work Order Fee / Discount' card, which lists whole-WO adjustments only. | VIU qb batch-1 (2026-07-08): Financial Info shows collapsed 'Fees &amp; Discounts (2)  -$4.00' — N counts ALL scopes, value is the signed net total in grey. Shot s14-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: Financial Info shows collapsed "Fees &amp; Discounts (1) $11.00" net grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: 'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change). | VIU 2026-07-22 LIVE: Financial Info order = Parts $40.00, Labor $509.90, Shop Supplies $53.54, Fees &amp; Discounts (10) $273.31, Subtotal $876.75, GST, Total, Balance — F&amp;D line renders directly above Subtotal. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
       </c>
@@ -4432,6 +4643,11 @@
       </c>
       <c r="O43" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P43" s="18" t="inlineStr">
+        <is>
           <t>Financial Info card is read-only for adjustments (key decision, §3 of spec). Scope disambiguation uses a suffix e.g. '(LF3620)'. | VIU qb batch-1 (2026-07-08): Row click did not visibly expand a per-adjustment read-only list in the harness (text unchanged). Needs a manual/visual re-check; no add/edit/remove controls seen in the row (read-only holds so far). | FRESH VIU 2026-07-10: creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
@@ -4511,6 +4727,11 @@
         </is>
       </c>
       <c r="O44" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P44" s="15" t="inlineStr">
         <is>
           <t>See Financial Data gates visibility of all fee/discount dollar amounts across surfaces (S13-R2/N1). | VIU qb batch-1 (2026-07-08): Hidden-when-none: not captured (paid WO's Financial Info not inspected). SFD-off half is Blocked-Env (no restricted user session). | FRESH VIU 2026-07-10: tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
@@ -4597,6 +4818,11 @@
       </c>
       <c r="O45" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P45" s="18" t="inlineStr">
+        <is>
           <t>Design↔spec color note: the design renders the discount amount in green (--sv-success-text); spec S12-R1 says sidebar amounts are plain grey. Authored to spec (plain grey); flag the color. Card title is 'Work Order Fee / Discount' in the final mockup vs 'WO Fees &amp; Discounts' in v1 mockup / spec S3-R3. | VIU qb batch-1 (2026-07-08): Sidebar card title is 'WO Fees &amp; Discounts' (matches S3-R3; the case title used the older 'Work Order Fee / Discount' name — update case). Entries: name + signed badge ('-10%', '$11.00') + grey signed resolved ('+$11.00', '-$15.00' with true minus) + hover ⋮ menu = 'Edit | Remove' (spec S3-R9 says Edit/'Delete' — wording deviation). Shots s9-04/05, s11b-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — UI: sidebar "WO Fees &amp; Discounts" card lists whole-WO entry: name + "$11.00" badge + "+$11.00" resolved grey (wo-card-after-add.png) | FRESH VIU 2026-07-10: card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication. | VIU 2026-07-22 LIVE: card titled 'Work Order Fees &amp; Discounts', lists only whole-WO entries as plain text with bracketed percent — fee 'Customer Fee (10%) +$65.88', discount 'WO Disc (−5%) −$32.94', flat 'Flat Fee 2 +$32.00'/'Flat Fee +$11.00' (name+amount, no brackets); each entry has a ⋮ menu; card renders above Financial Info. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -4678,6 +4904,11 @@
       </c>
       <c r="O46" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P46" s="15" t="inlineStr">
+        <is>
           <t>Design↔spec: the v1 mockup card includes an 'Add Fee / Discount' secondary button, which contradicts spec S3-R10 (no Add control on the card). Authored to spec (no Add control); flag if staging shows an in-card Add button. | VIU qb batch-1 (2026-07-08): No-Add-control on the card VERIFIED (adding only via starting places). Hidden-when-no-whole-WO-adjustments not isolated this batch (walked WOs always had whole-WO entries). | FRESH VIU 2026-07-10: sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -4758,6 +4989,11 @@
       </c>
       <c r="O47" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P47" s="18" t="inlineStr">
+        <is>
           <t>The 'Fees &amp; Discounts' column shows only on a part sale / parts view when the flag is on (S11-R7). Core-charge rows have an empty column (S11-R8). | VIU qb batch-1 (2026-07-08): Story 11 Part Sales F&amp;D NOT BUILT on qb (recon: no F&amp;D column, no menu item, no card on a part sale). | FRESH VIU 2026-07-10: RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
         </is>
       </c>
@@ -4837,6 +5073,11 @@
         </is>
       </c>
       <c r="O48" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P48" s="15" t="inlineStr">
         <is>
           <t>Badge count N is the number of adjustments AFTER the first (so 3 total → '+2'). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.) | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: NEXUS cell = 'Part Fee 11% +1' plain text, no badge, fee no sign.</t>
         </is>
@@ -4921,6 +5162,11 @@
       </c>
       <c r="O49" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P49" s="18" t="inlineStr">
+        <is>
           <t>The WO-line/customer variant of this breakdown omits the Max Amount column and the per-row trash (read-only); the Parts-page variant adds both (design §8). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
@@ -4998,6 +5244,11 @@
         </is>
       </c>
       <c r="O50" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P50" s="15" t="inlineStr">
         <is>
           <t>For a single-adjustment part (#37346 Military Discount −$6.53) the Net adjustment equals that one amount (−$6.53). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
         </is>
@@ -5080,6 +5331,11 @@
         </is>
       </c>
       <c r="O51" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P51" s="18" t="inlineStr">
         <is>
           <t>Removal uses the Create &amp; Edit permission, NOT the Delete permission (S13-R7). Per-row remove is shown only when the sale/WO can be edited (S11-R14). | VIU qb batch-1 (2026-07-08): Not built (see FD-PCOL-001). | FRESH VIU 2026-07-10: Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: breakdown viewer per-row delete -&gt; confirm 'Remove Fee / Discount' -&gt; removed -&gt; empty state, no '+ Add'.</t>
         </is>
@@ -5165,6 +5421,11 @@
       </c>
       <c r="O52" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P52" s="15" t="inlineStr">
+        <is>
           <t>Design open item #10: the mockups contain NO Edit-dialog markup and do not show which fields are locked. Authored strictly to spec S2-R4/R5/R8; verify locked-field behavior on staging. Confirm button label on edit = 'Save' (S2-R28). | VIU qb batch-1 (2026-07-08): Edit dialog: Name/Amount/Max/Taxable editable; Type + Calculation Type rendered DISABLED (locked). Backend contract matches: change endpoint takes only {adjustmentId,name,amount,maxCap,taxable} and ignores kind/calculationType fields. Shot s9-06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change edits name/amount/taxable &amp; re-resolves; Type/Calc lock is FE per S2-R5 | FRESH VIU 2026-07-10: change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -5249,6 +5510,11 @@
       </c>
       <c r="O53" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P53" s="18" t="inlineStr">
+        <is>
           <t>Verify re-resolution uses current (not original) totals. | VIU qb batch-1 (2026-07-08): Edit $12-&gt;$20: re-resolved against current totals (resolved 20; GST recomputed 15.44 = 5% x (292.83+11-15+20) exactly); template picker HIDDEN in edit mode; confirm button 'Save'; toast 'Fee updated'. Shot s9-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: change re-resolves against current totals; history logs "adjustment.updated" | FRESH VIU 2026-07-10: edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
@@ -5329,6 +5595,11 @@
         </is>
       </c>
       <c r="O54" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P54" s="15" t="inlineStr">
         <is>
           <t>The design mockups model no error/toast states; this is spec-driven (S2-R30, §7 toast table). | VIU qb batch-1 (2026-07-08): Edit-mode save failure not inducible this batch. ADD-mode failure (150% discount) kept dialog open + showed error toast (S2-R30 shape verified in add mode). | FRESH VIU 2026-07-10: invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
@@ -5413,6 +5684,11 @@
       </c>
       <c r="O55" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P55" s="18" t="inlineStr">
+        <is>
           <t>Design uses the label 'Delete' on the sidebar/inline ⋯ menus but the spec confirm dialog is titled 'Remove Fee / Discount' with a 'Remove' button; the design mockups do NOT model the confirm dialog (§10). Authored to spec — flag the label mismatch and confirm the dialog exists on staging. | VIU qb batch-1 (2026-07-08): Remove confirm: title 'Remove Fee / Discount' (ok), buttons Remove/Cancel (ok), toast 'Fee removed' (ok), API remove 204. DEVIATION: message reads 'Are you sure you want to remove this fee?' — spec S3-R11a wants 'Remove "{name}" from this work order?'. Shot s9-08. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon+API: remove opens "Remove Fee / Discount" confirm; POST remove → 204; toast "Fee removed" | FRESH VIU 2026-07-10: remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -5494,6 +5770,11 @@
         </is>
       </c>
       <c r="O56" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P56" s="15" t="inlineStr">
         <is>
           <t>Key permission nuance: 'Delete' permission is for whole records (WO, labor line, part); removing an adjustment is part of 'Create and Edit' (S13-R7). For a line/part adjustment the required permission is Work Order Lines: Create &amp; Edit (S13-R4). | VIU qb batch-1 (2026-07-08): Needs a role with Delete-but-not-Create&amp;Edit (and vice versa); no second-user login on qb env this batch. | FRESH VIU 2026-07-10: removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -5578,6 +5859,11 @@
       </c>
       <c r="O57" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P57" s="18" t="inlineStr">
+        <is>
           <t>If removing brings the count down to one adjustment, the 'Show N more' toggle should disappear. | VIU qb batch-1 (2026-07-08): Inline-row remove not driven (inline ⋮ menu not opened programmatically); card-entry remove verified in FD-REMOVE-001. | FRESH VIU 2026-07-10: line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
@@ -5662,6 +5948,11 @@
       </c>
       <c r="O58" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P58" s="15" t="inlineStr">
+        <is>
           <t>Critical calc rule: line-level percentages all resolve against the same gross base — they never compound on each other (§5-R5). | VIU qb batch-1 (2026-07-08): Part-scope pair pending (no part). Same-target NO-STACKING verified on a LABOR line: 25% fee ($66.25 on gross 265) + flat -$5 resolved independently on the same gross base. | FRESH VIU 2026-07-10: part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
@@ -5747,6 +6038,11 @@
       </c>
       <c r="O59" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P59" s="18" t="inlineStr">
+        <is>
           <t>Uses the spec's own §5 worked example. Confirms three-step resolve order and no compounding between whole-WO adjustments. | VIU qb batch-1 (2026-07-08): Two whole-WO adjustments use the same net base and don't change each other: with net subtotal $324.60 (incl. +$31.77 line-level), 100% discount -&gt; -$324.60 AND 150% fee -&gt; +$486.90 (both = pct x same base). Flat +$11 fee did not enter the 10% discount's base ($292.83). §5-R5 Step 2 verified. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: whole-WO % adjustments resolve on Step-1 net totals (net labor $674.77 used by whole-WO pct_labor) | FRESH VIU 2026-07-10: two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
@@ -5827,6 +6123,11 @@
         </is>
       </c>
       <c r="O60" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P60" s="15" t="inlineStr">
         <is>
           <t>This is intentional manual re-application, distinct from the auto-apply + customer-default DOUBLE-ADD bug (requirements open question #4), which is a known defect, not a spec requirement. | VIU qb batch-1 (2026-07-08): Same template applied twice by hand: two 'Flat fee' template adds -&gt; both 201, two adjustments on WO; the WO dialog's template picker still lists an already-applied template. | FRESH VIU 2026-07-10: 'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -5907,6 +6208,11 @@
       </c>
       <c r="O61" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P61" s="18" t="inlineStr">
+        <is>
           <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the Part Sale Add/Edit Fee &amp; Discount dialog. STAGING VIU 2026-07-20: note present in the whole-sale 'Add Parts Sale Fee / Discount' dialog (ps-wholesale-dialog.png) and the per-part 'Add Fee / Discount' dialog with 'Applying to: Part —' subtitle (psB4-filled.png). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: navigation label 'Add Fee / Discount' -&gt; 'Add Part Fee / Discount' (item 14) and dialog titles named ('New Part Fee / Discount' item 18; 'New Parts Sale Fee / Discount' item 19) for context; jurisdiction-note assertion unchanged. Whole-sale title/subline detail owned by kept new case FD-PSALE-008 (item 19). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Batch-3 live: per-part subline exact build string 'Applying To: Line 1 Part — Part — (55073) Mobil 1 5W20 Synthetic Engine Oil, 1L'; whole-sale subline 'Applying To: Entire Parts Sale'; note present below Taxable in both dialogs. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -5991,6 +6297,11 @@
       </c>
       <c r="O62" s="15" t="inlineStr">
         <is>
+          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
+        </is>
+      </c>
+      <c r="P62" s="15" t="inlineStr">
+        <is>
           <t>KNOWN RE-OPEN — this is the SOLE reason SV-8479 was re-opened. QA on staging 2026-07-22 confirmed the label 'Add Labor Fee / Discount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands. | VIU 2026-07-22 LIVE staging (WO f90c0d83, labor line no technician): DEVIATION — item-#1 re-open NOT fixed. Labor three-dot (⋮) renders to the RIGHT of 'Unassigned' (Unassigned text right-edge x=497; ⋮ at x=502, same row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
         </is>
       </c>
@@ -6073,6 +6384,11 @@
       </c>
       <c r="O63" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
           <t>QA passed this item on staging 2026-07-22 (✅). Menu label corrected from 'Add Fee / Discount' to 'Add Part Fee / Discount'. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
@@ -6152,6 +6468,11 @@
         </is>
       </c>
       <c r="O64" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P64" s="15" t="inlineStr">
         <is>
           <t>Copy updated to '…after all other fees &amp; discounts.' and ensured it renders. Picture 7 is a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
@@ -6234,6 +6555,11 @@
         </is>
       </c>
       <c r="O65" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P65" s="18" t="inlineStr">
         <is>
           <t>Label-only change; menu order unchanged. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -6318,6 +6644,11 @@
       </c>
       <c r="O66" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P66" s="15" t="inlineStr">
+        <is>
           <t>Regression check per SV-8479 NOTES — these UI corrections must not remove the jurisdiction tax note or the convenience-fee banner. VIU-confirm live. | VIU 2026-07-22 LIVE: jurisdiction note 'Tax treatment varies by jurisdiction — confirm your local requirements before saving.' present below the Taxable Yes/No dropdown in the labor, part AND whole-work-order fee/discount dialogs. The 'Pass convenience fee to customer' banner is present on the Fees &amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts / adjustment-templates) — it is NOT rendered inside the WO fee/discount dialogs. Ev: wo/labor-dialog-text.txt, wo/part-dialog-text.txt, wo/wo-dialog-text.txt, wo/FD-WO-028-settings-convenience-banner.png, wo/settings-fd-bodytext.txt.</t>
         </is>
       </c>
@@ -6400,6 +6731,11 @@
       </c>
       <c r="O67" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P67" s="18" t="inlineStr">
+        <is>
           <t>QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
         </is>
       </c>
@@ -6481,6 +6817,11 @@
         </is>
       </c>
       <c r="O68" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P68" s="15" t="inlineStr">
         <is>
           <t>QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
         </is>
@@ -6565,6 +6906,11 @@
       </c>
       <c r="O69" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
           <t>Same convention as work-order card item 5. QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
         </is>
       </c>
@@ -6647,6 +6993,11 @@
       </c>
       <c r="O70" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P70" s="15" t="inlineStr">
+        <is>
           <t>Matches work-order Financial Info card (item 7). Green mockup omits the amount; the amount is existing behavior. QA passed on staging 2026-07-22 (✅). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
         </is>
       </c>
@@ -6728,6 +7079,11 @@
       </c>
       <c r="O71" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P71" s="18" t="inlineStr">
+        <is>
           <t>PICTURE 26 MISSING — the description references 'Picture 26 shows the three-dot context' for the whole-parts-sale entry point, but no Picture 26 was attached to the ticket (only Picture 27 red exists, and the QA item-19 image 58872 is a duplicate of the item-18 shot 58866). The top-right three-dot entry label 'Add Parts Sale Fee / Discount' is taken from the item-19 description text; VIU-confirm the exact menu label, its placement in the top-right three-dot menu, and the dialog title/subline LIVE. QA marked item 19 passed on staging 2026-07-22 (✅) but on a duplicate image. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
         </is>
       </c>
@@ -6810,6 +7166,11 @@
       </c>
       <c r="O72" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P72" s="15" t="inlineStr">
+        <is>
           <t>No PO before/after picture for item 20 — it mirrors work-order item 12. QA passed on staging 2026-07-22 (✅, image 58876). VIU-confirm the exact Statistics-tab heading labels live. | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
         </is>
       </c>
@@ -6890,6 +7251,11 @@
         </is>
       </c>
       <c r="O73" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P73" s="18" t="inlineStr">
         <is>
           <t>Count in parentheses = number of default links on the customer, not adjustments on work orders. | VIU qb batch-1 (2026-07-08): Tab label 'Fees &amp; Discounts (N)' counts defaults live: (0) empty, (1) after add, (3)/(2) after ops. Shots s4-03/07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: customer "Fees &amp; Discounts (N)" tab with count | FRESH VIU 2026-07-10: tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
         </is>
@@ -6973,6 +7339,11 @@
       </c>
       <c r="O74" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P74" s="15" t="inlineStr">
+        <is>
           <t>Customer card uses "Add Fee/Discount" (no spaces); WO/template dialogs use "Add Fee / Discount" (with spaces) — keep both exact (S9-R... exact-text note). | VIU qb batch-1 (2026-07-08): Card 'Default Fees &amp; Discounts'; caption EXACTLY matches S9-R14; columns Name/Type/Calculation Type/Amount/Max Amount/Taxable + actions; bold headers/plain cells. Shot s4-03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: "Default Fees &amp; Discounts" card, exact S9-R14 caption, columns Name·Type·Calc·Amount·Max·Taxable | FRESH VIU 2026-07-10: card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
         </is>
       </c>
@@ -7056,6 +7427,11 @@
       </c>
       <c r="O75" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
           <t>Toast for one default is the generic "Fee / discount added." — it does NOT vary by type (§7 toast table). | VIU qb batch-1 (2026-07-08): Add works end-to-end (toast 'Fee / discount added', row + count update, POST /customers/{id}/default-adjustments {templateIds:[...]}). DEVIATIONS from S9-R18/19/20: picker is a single 'Fee / Discount Templates' DROPDOWN with Cancel/SAVE (spec: caption + checkbox multi-select list + 'Add' button); no caption text. Shots s4-04/05/06. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST /customers/{id}/default-adjustments {templateIds:[id]} → 201 adds default (GET confirms) | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the single-select dropdown picker (one template per add) is the accepted intended behavior — a deliberate judgement call to avoid accidental multi-adds; case re-worded away from the spec's checkbox multi-select picker. FDBUG-7 closed won't-fix. | FRESH VIU 2026-07-10: single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
         </is>
       </c>
@@ -7137,6 +7513,11 @@
         </is>
       </c>
       <c r="O76" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P76" s="15" t="inlineStr">
         <is>
           <t>Plural toast pattern is "[N] fees / discounts added." per §7 toast table. | VIU qb batch-1 (2026-07-08): Multi-select NOT possible in the UI (single-select dropdown; reopening shows no list once one is chosen). Backend accepts templateIds ARRAY (API multi-link 201), so only the UI multi-select + '[N] fees / discounts added' toast are missing. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: default POST accepts templateIds array (multi-select add); plural toast per S9-R23b (recon UI) | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): multi-select checkbox adding is NOT the product behavior — one-at-a-time from the dropdown is accepted; case re-scoped from multi-select + plural toast to three sequential single adds (each with the singular 'Fee / discount added.' toast). FDBUG-7 closed won't-fix. | FRESH VIU 2026-07-10: one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
         </is>
@@ -7220,6 +7601,11 @@
       </c>
       <c r="O77" s="18" t="inlineStr">
         <is>
+          <t>Re-check on staging how a Processing Fee template's type is shown in the customer picker, and confirm with the team whether showing it as 'Fee' is acceptable or needs fixing.</t>
+        </is>
+      </c>
+      <c r="P77" s="18" t="inlineStr">
+        <is>
           <t>This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee". | VIU qb batch-1 (2026-07-08): Picker lists only unlinked templates (verified: linked one disappears on reopen). DEVIATION: dropdown rows show the NAME only (no Type/Calc/Amount columns). Processing-fee template in the customer TABLE shows Type 'Processing fee' (better than the spec note's 'Fee'); its picker Type label not observable (no Type in picker). Shots s5-01, s11-02. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q6=A accepts single-select dropdown (close FDBUG-7 as won't-fix); adopt case-update wording. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the single-select dropdown picker (one template per add) is the accepted intended behavior — a deliberate judgement call to avoid accidental multi-adds; case re-worded away from the spec's checkbox multi-select picker. FDBUG-7 closed won't-fix. | FRESH VIU 2026-07-10: accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
         </is>
       </c>
@@ -7298,6 +7684,11 @@
         </is>
       </c>
       <c r="O78" s="15" t="inlineStr">
+        <is>
+          <t>Accepted as-is by the team — the picker shows 'No results' when there is nothing left to add. Update the test case wording to expect 'No results'; no developer fix needed.</t>
+        </is>
+      </c>
+      <c r="P78" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): With every template linked, the picker dropdown shows generic 'No results' — spec S9-R22 wants 'No templates available to add.'. Shot s5-03. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the shipped single-select dropdown was accepted as-is, so its "No results" empty state is adopted as the expected empty message (replaces the spec S9-R22 wording 'No templates available to add.'). | FRESH VIU 2026-07-10: 'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
         </is>
@@ -7381,6 +7772,11 @@
       </c>
       <c r="O79" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
           <t>Removing a customer default is intentionally no-confirm (S9-R24), unlike deleting a template (S7-R20 has a confirm). | VIU qb batch-1 (2026-07-08): Remove = DIRECT trash icon per row (spec: 3-dot menu with 'Remove'); needs no confirm (matches S9-R24) BUT NO 'Fee / discount removed' toast was observed. Row disappears, count updates. Shots s5-04/05. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: DELETE /customers/{id}/default-adjustments/{id} → 204, no confirm (S9-R24) | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the shipped customer-defaults tab UX was accepted as-is; the remove control is a direct per-row trash icon (not a 3-dot menu with 'Remove'), still no-confirm per S9-R24. Toast expectation kept (missing toast remains a tracked deviation). | FRESH VIU 2026-07-10: remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
         </is>
       </c>
@@ -7459,6 +7855,11 @@
         </is>
       </c>
       <c r="O80" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P80" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Empty state exactly 'No fees or discounts yet. Use 'Add Fee/Discount' to add one.' (S9-R17). Shot s4-03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: empty-state "No fees or discounts yet. Use 'Add Fee/Discount' to add one." | FRESH VIU 2026-07-10: empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
         </is>
@@ -7541,6 +7942,11 @@
       </c>
       <c r="O81" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P81" s="18" t="inlineStr">
+        <is>
           <t>The adjustment is an independent copy; the WO surfaces are covered by Group A — this case focuses on the customer-default → WO seeding and independence. | VIU qb batch-1 (2026-07-08): New WO for the customer received each default as an independent copy: appliedBy=customer_default, template values (amount/maxCap/taxable/calc) copied, own adjustment ids. Editing/removing on the WO left the defaults untouched. | FRESH VIU 2026-07-10: customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -7621,6 +8027,11 @@
       </c>
       <c r="O82" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P82" s="15" t="inlineStr">
+        <is>
           <t>Uses spec calc rule §5-R3. | VIU qb batch-1 (2026-07-08): Percentage default keeps the PERCENT: 10%/max-15 discount resolved $0.00 on an empty WO and -$15.00 (capped) once labor $265 existed — re-resolves against each WO's own base. | FRESH VIU 2026-07-10: pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
         </is>
       </c>
@@ -7702,6 +8113,11 @@
       </c>
       <c r="O83" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P83" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Default links removed (via template deletion cascade) left the adjustments already on WOs fully intact (names/amounts unchanged, still resolving). | FRESH VIU 2026-07-10: removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -7783,6 +8199,11 @@
       </c>
       <c r="O84" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P84" s="15" t="inlineStr">
+        <is>
           <t>Deleting the template drops template + default links but NOT existing WO adjustments — matches the task's stated rule. | VIU qb batch-1 (2026-07-08): Deleted template 'ZZAUTOTEST pfee' that was a default for 1 customer: delete-precondition API returned {affectedCustomerCount:1}; after delete the customer default list is empty AND the WO's pfee adjustment remains (S9-R9/S7-R4/S7-N1). | FRESH VIU 2026-07-10: deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -7862,6 +8283,11 @@
       </c>
       <c r="O85" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P85" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): customers/delete succeeded (contacts/vehicles removed first); the customer's default-adjustments endpoint 404s afterwards — links gone with the customer. | FRESH VIU 2026-07-10: prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -7940,6 +8366,11 @@
         </is>
       </c>
       <c r="O86" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P86" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): UI-created customer auto-inherited BOTH auto-apply templates as defaults (autoApply:true rows). NOTE/GAP: an API-created customer (customers/create) got NO seeded defaults — seeding happens only on the UI create path (FDBUG-12). | FRESH VIU 2026-07-10: NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
         </is>
@@ -8021,6 +8452,11 @@
       </c>
       <c r="O87" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P87" s="18" t="inlineStr">
+        <is>
           <t>CAUTION: Story 13 Custom-Roles model (SV-7388) may not be live on staging yet — record what staging actually enforces and flag divergence. Restore Tech to Time Clock (role 77b069d1-...) after. | VIU qb batch-1 (2026-07-08): No restricted-user session on qb. Bundle route meta CONFIRMS the gate: customer tab route 'default-adjustments' requires ['customersCreateAndEdit','seeApArData'] (matches S13-R9). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — SPA route guard requires customersCreateAndEdit + seeApArData (tab hidden otherwise) | FRESH VIU 2026-07-10: tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
@@ -8099,6 +8535,11 @@
         </is>
       </c>
       <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P88" s="15" t="inlineStr">
         <is>
           <t>Unlike WO/template save failures, customer-default failures use the generic system error, not a custom message. | VIU qb batch-1 (2026-07-08): Failure toasts not inducible this batch. | FRESH VIU 2026-07-10: bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
@@ -8180,6 +8621,11 @@
       </c>
       <c r="O89" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P89" s="18" t="inlineStr">
+        <is>
           <t>The admin Fees &amp; Discounts page is NOT in the HTML mockups — confirm its exact placement live. | VIU qb batch-1 (2026-07-08): Page lives at Administration -&gt; FINANCE -&gt; 'Fees &amp; Discounts' (below Payment Methods), route /administration/adjustment-templates — NOT under SERVICE below Canned Lines (S7-R7a/R7c). Matches the S13-R8 target location instead. Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: template library page exists (under Finance on this build; spec says Service — documented deviation) | FRESH VIU 2026-07-10: admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -8259,6 +8705,11 @@
         </is>
       </c>
       <c r="O90" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P90" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Columns exactly Name/Type/Calculation Type/Amount/Max Amount/Taxable/Auto-Apply To Work Orders + actions. Note: actions include an EDIT icon and DELETE icon (spec lists only delete; row-click also edits). Shot s1-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: list columns Name·Type·Calc·Amount·Max·Taxable·Auto-Apply + delete action | FRESH VIU 2026-07-10: list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -8343,6 +8794,11 @@
       </c>
       <c r="O91" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P91" s="18" t="inlineStr">
+        <is>
           <t>Create confirm button label is FIXED "Add Fee / Discount" for any type (S7-R17), unlike the WO dialog which flips to "Add Fee"/"Add Discount" (S2-R27). | VIU qb batch-1 (2026-07-08): Create works (fields Name(100)/Type/Calc/Amount/Taxable/auto-apply + preview-less). DEVIATIONS: confirm button 'Create' (spec 'Add Fee / Discount'); toast 'Template created' (spec 'Fee added'); amount label '$ Default Amount' (spec 'Amount'); Taxable &amp; auto-apply are TOGGLES not Yes/No dropdown/checkbox; EXTRA 'Description (Optional)' field (255) not in spec; auto-apply label 'Auto-apply to new work orders' (spec '...at this location'). Title 'New Fee / Discount' OK. Shots s1-03, s2-07. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (fee) → 201; recon dialog fields + "Fee added" toast | FRESH VIU 2026-07-10: PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -8423,6 +8879,11 @@
       </c>
       <c r="O92" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P92" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Discount template created fine but toast is generic 'Template created' — spec S7-R18a wants 'Discount added'. Shot s2-09. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates (discount) → 201; "Discount added" toast (recon) | FRESH VIU 2026-07-10: generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -8504,6 +8965,11 @@
       </c>
       <c r="O93" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P93" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Auto-apply template landed on a NEW WO automatically: adjustments appliedBy='auto', scope whole_wo, values copied (Customer fee $200 + Flat fee $12 observed on WO S3-15901). | FRESH VIU 2026-07-10: auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -8585,6 +9051,11 @@
       </c>
       <c r="O94" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P94" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Row-click opens edit dialog (S7-R9 ok), title 'Edit Fee / Discount' (ok), confirm 'Save' (ok). DEVIATIONS: toast 'Template updated' (spec 'Fee updated'); Type + Calculation Type are LOCKED (disabled) in template edit — spec S7 does not lock them (only the WO dialog S2-R5 does). Shots s3-01/02/03. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: POST adjustment-templates/{id}/change → 200 (edit); "updated" toast (recon) | FRESH VIU 2026-07-10: edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
@@ -8665,6 +9136,11 @@
       </c>
       <c r="O95" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P95" s="18" t="inlineStr">
+        <is>
           <t>The remove-confirm dialog is not in the HTML mockups; verify exact copy live. | VIU qb batch-1 (2026-07-08): Delete confirm: title 'Delete Template', message 'Are you sure you want to delete this template?' — spec S7-R20 wants '...delete this fee / discount?'. Buttons Delete/Cancel ok. Shot s3-05. | FRESH VIU 2026-07-10: delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
@@ -8744,6 +9220,11 @@
       </c>
       <c r="O96" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P96" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Warning present when template is a customer default: 'This template is set as a default for 1 customer. Deleting it will remove it from them.' + delete-precondition API {affectedCustomerCount:N}. Wording differs from spec S7-R21 ('...for [N] customer(s). Their defaults will be removed too.'). Shot s16-01. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: GET adjustment-templates/{id}/delete-precondition → {affectedCustomerCount} drives S7-R21 warning | EPIC/PO CLARIFY 2026-07-09: epic SV-7387 confirms the standardized (pricing-matrix-style) delete dialog is the intended behavior, so the live wording '...Deleting it will remove it from them.' is adopted as expected; the spec S7-R21 text '...Their defaults will be removed too.' is stale. NOTE-FD-7b closed. | FRESH VIU 2026-07-10: standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
@@ -8822,6 +9303,11 @@
         </is>
       </c>
       <c r="O97" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P97" s="18" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): After template delete, the WO adjustments created from it stayed unchanged (pfee still on WO; earlier external deletion of 2 templates likewise left WO copies intact). | FRESH VIU 2026-07-10: template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -8906,6 +9392,11 @@
       </c>
       <c r="O98" s="15" t="inlineStr">
         <is>
+          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
+        </is>
+      </c>
+      <c r="P98" s="15" t="inlineStr">
+        <is>
           <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02. | FRESH VIU 2026-07-10: FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
@@ -8987,6 +9478,11 @@
       </c>
       <c r="O99" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P99" s="18" t="inlineStr">
+        <is>
           <t>Design mockups show a "Max cap" always rendered (design-notes §10 item 4) — flag if staging shows Max Amount for Flat too. | VIU qb batch-1 (2026-07-08): Max Amount appears only for % methods (verified). DEVIATION on 0-handling: API stores maxCap=0 and resolves with NO cap (10% of 324.60 -&gt; 32.46 despite maxCap 0) — spec §5-R6 says $0 forces $0.00 and S7-R14 says 0 is treated as empty. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: template create accepts maxCap for percentage; 0 treated empty (§5-R6) | FRESH VIU 2026-07-10: maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
@@ -9065,6 +9561,11 @@
       </c>
       <c r="O100" s="15" t="inlineStr">
         <is>
+          <t>Needs an environment where the template library can be emptied (the shared one always has templates). Test the empty-state message when that is available.</t>
+        </is>
+      </c>
+      <c r="P100" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Cannot empty the location's template library (2 pre-existing real templates in use on this shared env); empty-state string unverified. | FRESH VIU 2026-07-10: empty-state needs deleting ALL location templates — not acceptable on the shared env (3 real templates present; manual tester active) | WORDING+VIU 2026-07-13: BLOCKED-ENV: the empty-state message cannot be seen — the shared env's template list is never empty (needs a location with zero templates). Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Blocked-Env for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
@@ -9144,6 +9645,11 @@
       </c>
       <c r="O101" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P101" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Discount template 150% blocked at save with toast 'A percentage discount cannot exceed 100%. Please try to resolve this.' (API 400 same message); fee template 150% created fine (API 201, deleted after). Shots s2-04/05/06. | FRESH VIU 2026-07-10: discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
@@ -9223,6 +9729,11 @@
       </c>
       <c r="O102" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P102" s="15" t="inlineStr">
+        <is>
           <t>Processing Fee has different method options (Flat Amount, % of Grand Total) — see FD-PROC-002. | VIU qb batch-1 (2026-07-08): Fee/Discount calc options exactly: Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; NO scope field anywhere. Shot s2-02. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — Recon: Fee/Discount template offers Flat Amount / % of Labor / % of Parts / % of Subtotal, no scope field | FRESH VIU 2026-07-10: builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
@@ -9301,6 +9812,11 @@
       </c>
       <c r="O103" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P103" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Save-failure toast not inducible this batch. | FRESH VIU 2026-07-10: template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
@@ -9379,6 +9895,11 @@
       </c>
       <c r="O104" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P104" s="15" t="inlineStr">
+        <is>
           <t>CURRENT-BUILD DIFFERENCE (§10.4/S7-R7b): today the page may show to any user with a location; S13-R8 tightens it to Settings → Finance. Record actual gating. Restore Tech to Time Clock after. | VIU qb batch-1 (2026-07-08): No restricted-user session. Bundle route meta CONFIRMS the gate: adjustment-templates route requires ['settingsFinance'] (S13-R8). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template list/create 403 (page gated) | MERGED VERDICT: pass A verified 403 for a no-settingsFinance user on template list/create; FE route meta also requires settingsFinance. | FRESH VIU 2026-07-10: BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -9458,6 +9979,11 @@
       </c>
       <c r="O105" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P105" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Name input maxlength=100 enforced (typed 110 chars -&gt; value length 100). | FRESH VIU 2026-07-10: name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
@@ -9535,6 +10061,11 @@
         </is>
       </c>
       <c r="O106" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P106" s="15" t="inlineStr">
         <is>
           <t>Processing Fee UI is absent from the HTML mockups — verify live. | VIU qb batch-1 (2026-07-08): 'Processing Fee' third type ABSENT from the template-builder Type dropdown (Fee/Discount only). Backend DOES support kind 'processing_fee' (template created via API); admin LIST then shows its Type as 'Fee' (mislabel) while the customer tab shows 'Processing fee'. Shots s2-01, s11-01/02. | FRESH VIU 2026-07-10: RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
         </is>
@@ -9616,6 +10147,11 @@
       </c>
       <c r="O107" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P107" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): UI not built. BACKEND verified: processing_fee allows pct_grand_total and flat ONLY (pct_subtotal -&gt; 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee'). | FRESH VIU 2026-07-10: builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
         </is>
       </c>
@@ -9693,6 +10229,11 @@
         </is>
       </c>
       <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P108" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): UI not built. BACKEND verified: maxCap on processing fee -&gt; 400 'A processing fee cannot have a minimum or maximum cap.' | FRESH VIU 2026-07-10: builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
         </is>
@@ -9775,6 +10316,11 @@
       </c>
       <c r="O109" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P109" s="18" t="inlineStr">
+        <is>
           <t>V1_2 (2026-07-13): REWRITTEN — the old Processing-Fee legal-disclosure block ("render exactly / no auto-translate without legal sign-off") is REMOVED in S8-R13; expected now asserts the new §5-R15 taxable jurisdiction note (exact string). This case folds in the Processing Fee dialog §5-R15 check (S8-R13), so no separate Processing-Fee §5-R15 case was authored. Story-8 builder UI is still Not-Built on qb — re-check the note when it ships. | OPEN QUESTION (§14 item 5): the disclosure's literal text is NOT in the exported spec — capture the exact wording from the live dialog before asserting it. Spec copy says "toggle" but the control is the Yes/No dropdown. | VIU qb batch-1 (2026-07-08): UI not built; taxable default + legal disclosure unverifiable (disclosure text also absent from spec extract — open question #5). | FRESH VIU 2026-07-10: builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
         </is>
       </c>
@@ -9855,6 +10401,11 @@
       </c>
       <c r="O110" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P110" s="15" t="inlineStr">
+        <is>
           <t>Processing Fee reaches a WO only via auto-apply (S8-R14) or a customer default (S8-R15). | VIU qb batch-1 (2026-07-08): Cannot be added to a WO by hand: WO dialog Type offers only Fee/Discount (S8-N1) and API kind=processing_fee -&gt; 400 'A processing fee cannot be added manually.' (S8-R16). NOTE: whole-WO template-picker exclusion of pfee templates (S8-N2) not explicitly captured. | FRESH VIU 2026-07-10: manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -9934,6 +10485,11 @@
       </c>
       <c r="O111" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P111" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Auto-apply path not tested with a processing-fee template (test pfee had autoApply=false). Customer-default path verified instead (FD-PROC-007). | FRESH VIU 2026-07-10: auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -10012,6 +10568,11 @@
         </is>
       </c>
       <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P112" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Processing-fee template linked as a customer default WAS auto-added to the customer's new WO (kind processing_fee, scope whole_wo, appliedBy customer_default, resolved on grand total). | FRESH VIU 2026-07-10: customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -10093,6 +10654,11 @@
       </c>
       <c r="O113" s="18" t="inlineStr">
         <is>
+          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
+        </is>
+      </c>
+      <c r="P113" s="18" t="inlineStr">
+        <is>
           <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02. | FRESH VIU 2026-07-10: BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
@@ -10174,6 +10740,11 @@
       </c>
       <c r="O114" s="15" t="inlineStr">
         <is>
+          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
+        </is>
+      </c>
+      <c r="P114" s="15" t="inlineStr">
+        <is>
           <t>Uses the spec's worked example directly. | VIU qb batch-1 (2026-07-08): Resolves LAST and re-resolves dynamically, BUT THE BASE IS WRONG (FDBUG-2): 3% pfee resolved $15.90 = 3% x $530.07 where $530.07 = (subtotal 292.83 + whole-WO fees 212) x 1.05 — the base INCLUDES whole-WO fees AND their tax. Spec §5-R4 excludes every whole-WO fee/discount: expected 3% x (292.83 + 14.64) = $9.22. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
@@ -10253,6 +10824,11 @@
       </c>
       <c r="O115" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P115" s="18" t="inlineStr">
+        <is>
           <t>The UI hides these options; this guards data sent from outside the product. | VIU qb batch-1 (2026-07-08): API rejects processing fee with maxCap and with any method other than flat/pct_grand_total (exact 400 messages captured). | FRESH VIU 2026-07-10: pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
@@ -10332,6 +10908,11 @@
       </c>
       <c r="O116" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P116" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Processing fee is fee-only and always adds: kind is 'processing_fee' (no discount variant); resolved amounts positive; taxable pfee ADDS its own amount to the taxable base (tax grew by 5% of the fee) without growing its own base. | FRESH VIU 2026-07-10: pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
@@ -10411,6 +10992,11 @@
       </c>
       <c r="O117" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P117" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Edited the pfee TEMPLATE amount 3% -&gt; 4%: the pfee already on the WO kept amount=3 (unchanged), S8-R19. | FRESH VIU 2026-07-10: template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
@@ -10491,6 +11077,11 @@
       </c>
       <c r="O118" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P118" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Multiple simultaneous processing fees not tested (single pfee only). Batch-2. | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): both pfees share one base excluding every pfee's amount+tax; FDBUG-2 base composition unchanged. | FRESH VIU 2026-07-10: two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
@@ -10569,6 +11160,11 @@
       </c>
       <c r="O119" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P119" s="18" t="inlineStr">
+        <is>
           <t>Min Amount exists only in the data model; both dialogs always send it empty (null). | VIU qb batch-1 (2026-07-08): Min-amount payload guard (S8-N6) not probed. Batch-2 API probe (minCap field). | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): min fields silently stripped; invariant enforced; note ignore-vs-reject semantics. | FRESH VIU 2026-07-10: pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
@@ -10647,6 +11243,11 @@
         </is>
       </c>
       <c r="O120" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P120" s="15" t="inlineStr">
         <is>
           <t>No customer estimate/invoice view exists in the HTML mockups — verify layout live. | VIU qb batch-1 (2026-07-08): ESTIMATE rendering verified in the WO Finance tab (adjustments present). Invoice not created this batch (kept the env clean); same-layout claim needs an invoice walk. | FRESH VIU 2026-07-10: estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
@@ -10728,6 +11329,11 @@
       </c>
       <c r="O121" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P121" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Labor-line adjustment on the estimate: indented '↳ ZZAUTOTEST line fee (% of labor) $66.25' under its labor line — arrow, phrase and fee format all exact. Shot s14b. | FRESH VIU 2026-07-10: labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
@@ -10806,6 +11412,11 @@
         </is>
       </c>
       <c r="O122" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P122" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Part-line phrase pending (no part seeded). | FRESH VIU 2026-07-10: part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
@@ -10887,6 +11498,11 @@
       </c>
       <c r="O123" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P123" s="18" t="inlineStr">
+        <is>
           <t>Note this differs from WO screens, which use a signed minus (e.g. "−$26.08") in plain grey. | VIU qb batch-1 (2026-07-08): Fee shows '$11.00'; discount shows '($15.00)' — round brackets, two decimals, no minus (S5-R4/S12-R7). Estimate doc capture s14b. | FRESH VIU 2026-07-10: fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
@@ -10967,6 +11583,11 @@
       </c>
       <c r="O124" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P124" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Bottom 'Adjustments' block lists whole-WO adjustments one per row in creation order ('ZZAUTOTEST fee flat $11.00' then 'ZZAUTOTEST disc pct (% of subtotal) ($15.00)') with percentage phrases; flat has no phrase. | FRESH VIU 2026-07-10: bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
@@ -11046,6 +11667,11 @@
       </c>
       <c r="O125" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P125" s="18" t="inlineStr">
+        <is>
           <t>Grouping is ONLY on the customer document; WO line table lists each one by one (Story 3). | VIU qb batch-1 (2026-07-08): Line-level adjustment DOES also appear in the bottom block as its own row (S5-R8 half verified); grouping with '(xN)' count needs &gt;1 same-name line-level adjustments — pending. | FRESH VIU 2026-07-10: 3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
@@ -11122,6 +11748,11 @@
         </is>
       </c>
       <c r="O126" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P126" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Processing fee row on the estimate reads 'ZZAUTOTEST pfee (% of grand total) $6.68' — exact S8-R22 phrase. Shot s15-01. | FRESH VIU 2026-07-10: '(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
@@ -11203,6 +11834,11 @@
       </c>
       <c r="O127" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P127" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): WO with $0.00 shop supplies: the estimate shows NO 'Shop supplies' row at all (Labor/Parts/Adjustments only) — S14-R1 on the estimate. Financial-tab/invoice variants pending. Shot s15-01. | FRESH VIU 2026-07-10: Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
@@ -11281,6 +11917,11 @@
       </c>
       <c r="O128" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P128" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): WO with shop supplies $27.83: 'Shop supplies $27.83' row IS rendered on the estimate (visible-when-&gt;0 behavior). | FRESH VIU 2026-07-10: prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
@@ -11360,6 +12001,11 @@
       </c>
       <c r="O129" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P129" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Declined-line $0.00 doc row pending (declined $0 resolution itself verified via API). | FRESH VIU 2026-07-10: prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
@@ -11436,6 +12082,11 @@
         </is>
       </c>
       <c r="O130" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P130" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Adjustments block position ok (after Labor/Parts/Shop supplies, before Subtotal -&gt; GST -&gt; Total). DEVIATION/BUG (FDBUG-1): Subtotal and Total do NOT include the adjustment amounts while GST DOES include their tax — estimate showed Subtotal $292.83 / GST $17.75 / Total $310.58 with +$62.25 net adjustments missing from the total; a fees-only WO showed 'Total $10.93' = tax alone. Customer-facing money is wrong. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-1 GST-artifact-re-eval: batch-4 non-repro on estimates + GST framing -&gt; needs US-tax repro. | FRESH VIU 2026-07-10: FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
@@ -11518,6 +12169,11 @@
       </c>
       <c r="O131" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P131" s="18" t="inlineStr">
+        <is>
           <t>QuickBooks sync is backend; verify via the QuickBooks side or the sync payload. | VIU qb batch-1 (2026-07-08): No QuickBooks settings UI on qb env (INTEGRATIONS shows IBS only) and no QB account to sync into; invoiced-sync not exercisable. NOTE: GET /api/bookkeeping/adjustment-item-mapping-status EXISTS -&gt; {quickBooksConnected:true, feeItemMapped:true, discountItemMapped:true} (the app polls it before every add). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: QB invoice line internals unobservable (no read API; export of re-invoiced WOs fails on duplicate doc numbers) — needs QB-UI eyeball of a cleanly synced invoice | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
@@ -11598,6 +12254,11 @@
       </c>
       <c r="O132" s="15" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P132" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001 (no QB sync surface). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-001 — needs QB UI (generic Fee/Discount item + description=name) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
@@ -11676,6 +12337,11 @@
         </is>
       </c>
       <c r="O133" s="18" t="inlineStr">
+        <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P133" s="18" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-001. $0.00 resolve itself verified (§5-R8) — only the QB skip is untestable. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-001 — $0-line skip only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
@@ -11758,6 +12424,11 @@
       </c>
       <c r="O134" s="15" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P134" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Mapping guard not triggerable: mapping-status reports both items MAPPED and there is no QB settings page to unmap on this env. The guard endpoint exists and is called before every add dialog. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: unmap not achievable today: PUT bookkeeping/settings {settings:{feeItemId:null}} -&gt; 500 (requestId 4bd14847); flat payload -&gt; 400 'settings missing'. Mapping stayed connected+mapped (verified). Guard cycle needs a working unmap (dev/QB-side) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
@@ -11838,6 +12509,11 @@
       </c>
       <c r="O135" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P135" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
@@ -11915,6 +12591,11 @@
       </c>
       <c r="O136" s="15" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P136" s="15" t="inlineStr">
+        <is>
           <t>Some of these surfaces (labor/part/part-sale) are primarily Group A scope; this case covers the guard breadth. | VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
@@ -11994,6 +12675,11 @@
       </c>
       <c r="O137" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P137" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Blocked with FD-QB-004. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-004 (unmap 500) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the mapping-guard block cannot be driven — the two items are currently mapped and the unmap call (PUT /api/bookkeeping/settings) 500s on this env, so an unmapped state can't be created. The guard's data source (connected/feeItemMapped/discountItemMapped) is observable and all true.</t>
         </is>
       </c>
@@ -12072,6 +12758,11 @@
         </is>
       </c>
       <c r="O138" s="15" t="inlineStr">
+        <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P138" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Half-verified: with items mapped/connected (per mapping-status) adds are never blocked anywhere (dozens of adds succeeded). Not-connected/unmapped variants untestable on this env. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: as FD-QB-004; positive half (template create while MAPPED) works throughout | WORDING+VIU 2026-07-13: Observable half CONFIRMED live: creating a non-auto-apply template is always allowed (template create 201). The 'no block when QuickBooks not connected' half is Blocked-Env — QuickBooks is connected here and cannot be disconnected on the shared env.</t>
         </is>
@@ -12154,6 +12845,11 @@
       </c>
       <c r="O139" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company; the unmap action also currently errors on this environment. Test once QuickBooks is connected and that is working.</t>
+        </is>
+      </c>
+      <c r="P139" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Unexported-items recovery untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: unexported-items list + retry + mark-done endpoints re-exercised (mark-done 200 on my entries); the unmap-in-flight repro blocked by the unmap 500 | WORDING+VIU 2026-07-13:  BLOCKED-ENV: cannot unmap an in-use item — the unmap call 500s on this env — so the route-to-Unexported-Items behavior can't be driven. (The Unexported Items list itself is reachable and returns data.)</t>
         </is>
       </c>
@@ -12232,6 +12928,11 @@
       </c>
       <c r="O140" s="15" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P140" s="15" t="inlineStr">
+        <is>
           <t>Per-class allocation is out of scope for V1. | VIU qb batch-1 (2026-07-08): Class propagation untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: Class application only visible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
       </c>
@@ -12309,6 +13010,11 @@
         </is>
       </c>
       <c r="O141" s="18" t="inlineStr">
+        <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P141" s="18" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Class validation untestable (no QB). | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: stale-Class abort only reproducible QB-side | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
@@ -12390,6 +13096,11 @@
       </c>
       <c r="O142" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P142" s="15" t="inlineStr">
+        <is>
           <t>Uses the spec's exact $100/$10/$150 worked example. | VIU qb batch-1 (2026-07-08): QB export untestable, but floor evidence exists: the add-dialog preview floors 'New work-order subtotal' at $0.00 for an over-100% discount, and adjustmentsSummary carries an 'excessCreditAmount' field (0 so far). Full worked-example (tax-still-owed) needs an invoice-time walk — batch 2. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): both halves of the worked example proven structurally at WO level (see FD-CALC-015/016). | FRESH VIU 2026-07-10: floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
@@ -12470,6 +13181,11 @@
       </c>
       <c r="O143" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P143" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export-side — untestable without QB. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: penny-cap allocation of discount LINES only visible on QB invoice lines | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the largest-remainder penny allocation on the QuickBooks discount lines is only visible inside QuickBooks (same as FD-CALC-017). The in-app $0.00 floor half is verified.</t>
         </is>
       </c>
@@ -12550,6 +13266,11 @@
       </c>
       <c r="O144" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P144" s="15" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): No warn/confirm was shown when saving a 100% discount via API/UI on an open WO — the S6-R12 warning presumably belongs to the invoice/save flow; needs an invoicing walk. excessCreditAmount field exists. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): over-discount saves with no warn/confirm; excess carried silently = FDBUG-15 (S6-R12). | FRESH VIU 2026-07-10: FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
@@ -12630,6 +13351,11 @@
       </c>
       <c r="O145" s="18" t="inlineStr">
         <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P145" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Customer-credit carry needs the invoicing walk (Deposits &amp; Credits check) — batch 2. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: IN-APP HALF VERIFIED TODAY: invoicing the over-discounted WO recorded a CUSTOMER CREDIT (unpaid-transactions 2-&gt;4; 'current' bucket -11.63 -&gt; -119.73 = +9.14 invoice &amp; -117.24 credit exactly). QB goodwill-memo half unobservable: invoice export fails on the duplicate-doc-number env bug, no credit_memo export fired, no QB read API — needs QB UI on a cleanly synced org | WORDING+VIU 2026-07-13: In-app customer-credit half VERIFIED 2026-07-10 (invoicing an over-discounted WO recorded a customer credit of exactly the excess). BLOCKED-ENV: the QuickBooks tax-exempt goodwill credit-memo half needs a human in QuickBooks (export fails on duplicate document numbers; no QB read API).</t>
         </is>
       </c>
@@ -12707,6 +13433,11 @@
         </is>
       </c>
       <c r="O146" s="15" t="inlineStr">
+        <is>
+          <t>Needs a QuickBooks-connected company. Test this in QuickBooks once that is available.</t>
+        </is>
+      </c>
+      <c r="P146" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Line-tax on synced lines untestable (no QB). In-app tax behavior itself verified under §5-R11. | UPDATE batch-5 (2026-07-09): QuickBooks IS now CONNECTED on this env (location Staging Lethbridge - 4310 = default_workplace; mapping-status quickBooksConnected:true+both items mapped; real QB chart of accounts + unexported-items returned). Batch-1 'no QB' blocker SUPERSEDED. Live behavior VIU still pending: the sv7387api backend was in a sustained 500 incident (all endpoints incl. quick-login) for the whole 2026-07-09 window, so mapping/sync/floor could not be exercised. Retest plan in viu-findings.md Batch-5. | FRESH VIU 2026-07-10: tax code on the QB line unobservable in-app; in-app taxable base shifts re-proven (FD-CALC-011) | WORDING+VIU 2026-07-13:  BLOCKED-ENV: the QuickBooks invoice line-item internals are only visible inside QuickBooks (no QB read API; and re-invoiced work orders currently fail to export on duplicate document numbers) — a human logged into QuickBooks is needed to confirm. Observable today: adjustment-item-mapping-status = QuickBooks connected + Fee item mapped + Discount item mapped (checked live).</t>
         </is>
@@ -12788,6 +13519,11 @@
         </is>
       </c>
       <c r="O147" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P147" s="18" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Manual actions each write ONE entry with bold labels 'Fee added' / 'Fee updated' / 'Fee removed' (verified sequence). DEVIATION/BUG (FDBUG-3): AUTO-APPLIED adjustments (location auto-apply, customer defaults, processing fee) write NO history entry at all — a new WO with 3 auto adjustments showed only 'Created'/'Line created'. Shots s9-12, s11b-04. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add/edit/remove each log one distinct event (adjustment.added/updated/removed) | FRESH VIU 2026-07-10: FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
@@ -12870,6 +13606,11 @@
       </c>
       <c r="O148" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P148" s="15" t="inlineStr">
+        <is>
           <t>History log uses "Full invoice" whereas other screens say "Whole Work Order". Amount is the set rate, not resolved — this is why SFD does not gate the log (S10-R6c). | VIU qb batch-1 (2026-07-08): Details block shows 'Name: Flat fee | Amount: $20.00 | Applied to: Full invoice' — Name ok, Amount = SET RATE not resolved total (ok), 'Full invoice' label exact (ok). DEVIATION: NO 'Type:' line in the details (S10-R6b). Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: detail carries adjustmentName, adjustmentKind, adjustmentSetRate (set rate not resolved), adjustmentAppliedTo="Full invoice" | FRESH VIU 2026-07-10: FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -12949,6 +13690,11 @@
       </c>
       <c r="O149" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P149" s="18" t="inlineStr">
+        <is>
           <t>VIU qb batch-1 (2026-07-08): Adjustment entries show Line column '-' and no saved-state icon. Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: adjustment entries have lineId=null (Line column "−"); no saved-state icon | FRESH VIU 2026-07-10: adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -13029,6 +13775,11 @@
       </c>
       <c r="O150" s="15" t="inlineStr">
         <is>
+          <t>Needs a window where the Fees &amp; Discounts feature can be turned off (it can't be toggled on the shared environment). Test when that is available.</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
           <t>The history log is the one exception to the flag-off rule. | VIU qb batch-1 (2026-07-08): Flag-off visibility not tested — org-level flag toggle skipped on this SHARED env (concurrent dev activity observed); needs a maintenance window or dedicated env. | FRESH VIU 2026-07-10: feature-flag OFF window deliberately not taken on the shared env (manual tester active today) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV: needs a feature-off window (not takeable on the shared env with a live tester). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -13108,6 +13859,11 @@
         </is>
       </c>
       <c r="O151" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P151" s="18" t="inlineStr">
         <is>
           <t>CAUTION: Story 13 model may not be live on staging yet. Restore Tech to Time Clock (role 77b069d1-...) after. | VIU qb batch-1 (2026-07-08): SFD-off visibility needs a restricted user session — not available on qb this batch. | FRESH VIU 2026-07-10: tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
@@ -13191,6 +13947,11 @@
       </c>
       <c r="O152" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P152" s="15" t="inlineStr">
+        <is>
           <t>Restore Tech to Time Clock after. CAUTION: Story 13 model may not be fully live on staging — record actual gating. | VIU qb batch-1 (2026-07-08): View-History-Logs gating needs a restricted user session. | FRESH VIU 2026-07-10: View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -13271,6 +14032,11 @@
       </c>
       <c r="O153" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P153" s="18" t="inlineStr">
+        <is>
           <t>CURRENT-BUILD DIFFERENCE (§14 item 6): current build may show raw "processing_fee" on "Applied to:" instead of "Full invoice" — record actual value. | VIU qb batch-1 (2026-07-08): Processing-fee history could not be verified: its auto-add wrote NO entry (FDBUG-3), and its removal wasn't exercised before cleanup. Batch-2: remove a pfee manually and check the entry. | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): pfee auto-add NOT logged (FDBUG-3); remove logged; no updated entry; Full invoice label confirmed on manual entries. | FRESH VIU 2026-07-10: extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
@@ -13348,6 +14114,11 @@
         </is>
       </c>
       <c r="O154" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P154" s="15" t="inlineStr">
         <is>
           <t>VIU qb batch-1 (2026-07-08): Edit $12-&gt;$20 logged 'Fee updated ... Amount: $20.00' — the NEW set rate, not a resolved total. Shot s9-12. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: edit to amount 8 logs adjustment.updated with adjustmentSetRate=8 (new set rate) | FRESH VIU 2026-07-10: work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
@@ -13428,6 +14199,11 @@
         </is>
       </c>
       <c r="O155" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P155" s="18" t="inlineStr">
         <is>
           <t>NEW 2026-07-20 (Chris V1_3 Q1=B): the §5-R15 note must appear below every Taxable control, incl. the admin Fee/Discount template dialog for every kind. STAGING VIU 2026-07-20: note present for Type=Fee (default) and Type=Processing Fee (tmpl-new-default.png / proc-fee-full.png); ABSENT for a Manage-Finance-Settings-without-SFD user (tech-tmpl-dialog.png) = the SFD gate (Q2=A). UI string check, functional section (Rule 4). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -13513,6 +14289,11 @@
       </c>
       <c r="O156" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P156" s="15" t="inlineStr">
+        <is>
           <t>Design open question: the mock Add modal has NO calculation-base selector and computes % against a single flat WO total (design §9.1). Spec §5-R4 requires the base to depend on scope/method. Verify staging actually offers % of Labor Total / Parts Total / Subtotal and resolves against the correct base. | VIU qb batch-1 (2026-07-08): base x percent verified repeatedly: 10% x 265 = 26.50; 25% x 265 = 66.25; 3% x 530.07 = 15.90; 10% x 292.83 = 29.28 (pre-cap). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: base×pct exact — pct_subtotal 10% of $1214.81=$121.48; pct_labor of $749.75=$74.98; pct_parts of $386.34=$38.63 (calc-results.json) | FRESH VIU 2026-07-10: 10% pct_subtotal -&gt; 17.08 = exactly 10% of the 170.76 base; sub delta matches | WORDING+VIU 2026-07-13: Build labels; carry arithmetic VIU. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: rate rendering reworded from 'rate badge' to plain text (item 4); calc math unchanged. | VIU 2026-07-22 LIVE: base×percent calc confirmed (20% of $509.90 labor = +$101.98; plain text, no badge). WORDING CORRECTED '+10%' -&gt; '10%' — inline percentage FEE renders bare with no leading '+' (matches live build + batch-1 FD-CALC-018/019 fix). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
@@ -13597,6 +14378,11 @@
       </c>
       <c r="O157" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P157" s="18" t="inlineStr">
+        <is>
           <t>Rounding is a §5 enforced rule not modeled in the design mock. Confirm the server, not just the preview, rounds half-cent up. | VIU qb batch-1 (2026-07-08): Half-cent rounds UP: 0.1% x $265 = $0.265 -&gt; resolved $0.27 (API). Also 25% x 292.83 = 73.2075 -&gt; 73.21. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: half-cent rounds UP — $749.75×.10=$74.975→$74.98; rounds down — $386.34×.10=$38.634→$38.63 | FRESH VIU 2026-07-10: 0.25% of 170.76 = 0.4269 -&gt; 0.43 (rounds up); half-cent-up rule from batch-1 (0.1%x265-&gt;0.27) stands | WORDING+VIU 2026-07-13: Build labels; carry rounding VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -13678,6 +14464,11 @@
       </c>
       <c r="O158" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P158" s="15" t="inlineStr">
+        <is>
           <t>Open question (requirements §14 item 2): §5-R4's base table lists explicit bases only for the three percentage methods; Whole-WO Flat Amount base = "the set amount" by inference. Confirm no explicit Whole-WO Flat base row is expected. | VIU qb batch-1 (2026-07-08): Whole-WO flat $11 -&gt; 11.00; labor-line flat $5 -&gt; 5.00 exactly (no quantity part). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: WO flat $5 fee→+$5.00; labor flat $10→+$10.00 (exact, no qty) | FRESH VIU 2026-07-10: flat 7.77 -&gt; resolved 7.77 exactly (whole-WO); labor-line flat 9.99 exact | WORDING+VIU 2026-07-13: Build labels; flat resolve confirmed live 2026-07-13 ($25→+$25.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: step 1 whole-WO -&gt; 'Add Work Order Fee / Discount', step 2 labor line -&gt; 'Add Labor Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Work Order Fee / Discount' (step 1) and 'Add Labor Fee / Discount' (step 2) both confirmed present; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png, wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
@@ -13759,6 +14550,11 @@
         </is>
       </c>
       <c r="O159" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P159" s="18" t="inlineStr">
         <is>
           <t>Part Line Flat is the only Flat method that multiplies by quantity (§5-R14). Whole-WO and Labor Line Flat do not. | VIU qb batch-1 (2026-07-08): Part-line per-item multiplication pending (no part target). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: part-line flat $5 × qty 2 = $10.00 (per-item §5-R14) | FRESH VIU 2026-07-10: per-item: $2.00 x qty4 -&gt; $8.00 (part line) | WORDING+VIU 2026-07-13: Build labels; per-item VIU carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
@@ -13844,6 +14640,11 @@
       </c>
       <c r="O160" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P160" s="15" t="inlineStr">
+        <is>
           <t>Design mock shows no inline error copy for over-100% discounts (design §10). Capture the actual error message/behavior on staging. | VIU qb batch-1 (2026-07-08): Discount: 100% accepted, 100.01% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% accepted. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount REJECTED "A percentage discount cannot exceed 100%"; 150% fee allowed →$1822.22 | FRESH VIU 2026-07-10: discount pct &gt;100 -&gt; 400; fee pct uncapped (150% -&gt; 201) | WORDING+VIU 2026-07-13: Exact back-end message confirmed live 2026-07-13: 'A percentage discount cannot exceed 100%.' Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | SV-8479/8480 deconfliction 2026-07-22: 'at any scope' step reworded to the whole-WO entry label 'Add Work Order Fee / Discount' (validation is scope-independent). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -13925,6 +14726,11 @@
         </is>
       </c>
       <c r="O161" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P161" s="18" t="inlineStr">
         <is>
           <t>Design's Add button stays disabled when Amount is 0 (design §6), which enforces "&gt; 0" but does not distinguish the $0.01 / 0.01% floor. Verify the exact floor on staging. | VIU qb batch-1 (2026-07-08): Flat $0.01 accepted (min ok); 0/negative rejected. DEVIATION (FDBUG-10): percent 0.005 was silently COERCED UP to 0.01 (201, amount=0.01) instead of being rejected as below-minimum. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: flat $0.01 accepted (+$0.01); flat $0 REJECTED "must be greater than zero" | FRESH VIU 2026-07-10: FDBUG-10 CONFIRMED AGAIN: pct 0.005% accepted (201) and silently coerced to 0.01 (resolved 0.02); flat 0.005 accepted -&gt; stored 0.01. Spec: below-minimum must be rejected | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-10 / PO Q3 pending): a percentage below the 0.01% minimum is silently rounded UP to 0.01% instead of being rejected. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q3=A): PO ruled quietly rounding tiny percentages up to the 0.01% minimum is fine/expected ('fully anticipated and expected'). No longer a deviation; FDBUG-10 closed as accepted; jira draft TICKET 5 DROPPED. Expected reworded to expect the round-up-to-minimum coercion. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -14010,6 +14816,11 @@
       </c>
       <c r="O162" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P162" s="15" t="inlineStr">
+        <is>
           <t>Design difference: the mock labels the field "Max cap" (spec label is "Max Amount (Optional)") and shows it unconditionally, even capping Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging hides it for Flat Amount. | VIU qb batch-1 (2026-07-08): Clamp verified: 10% x 324.60 = 32.46 -&gt; maxCap 5 -&gt; resolved 5.00; 10%/max15 discount -&gt; -15.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: pct_subtotal 10% ($121.48) with maxCap $50 → clamped to +$50.00 | FRESH VIU 2026-07-10: Max cap clamps: 20% (34.15) with cap 15 -&gt; 15.00 | WORDING+VIU 2026-07-13: Max cap clamp confirmed live 2026-07-13 (20% → capped $15.00). Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -14091,6 +14902,11 @@
       </c>
       <c r="O163" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P163" s="18" t="inlineStr">
+        <is>
           <t>Two behaviors of "0" that must not be confused: typed 0 = empty/no cap (S2-R25); a stored 0 from legacy data forces $0 (§5-R6). Min Amount exists in the data model only, always sent null by both dialogs. | VIU qb batch-1 (2026-07-08): Blank maxCap = no cap (ok). DEVIATION (FDBUG-9): maxCap=0 accepted by the API and treated as NO CAP (resolved 32.46) — spec §5-R6 says Max $0 forces $0.00. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 treated as no-cap (resolved full $121.48); empty maxCap = no cap. Note: spec "Max=$0 forces $0" is old-data-only/not triggerable from product | Pass A read maxCap-0-as-no-cap as acceptable (spec calls $0 old-data-only); keeping Deviation since observed behavior (no cap) also contradicts the "$0 forces $0.00" rule - PO question. | FRESH VIU 2026-07-10: FDBUG-9 CONFIRMED AGAIN: maxCap 0 -&gt; resolved 34.15 (treated as NO cap; spec: $0 forces $0.00) | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-9 / PO Q2 pending): a Max Amount of 0 is treated as 'no cap' rather than capping at $0.00. Build labels applied. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount means 'no limit' (WAD, S2-R25: entered 0 = empty = no maximum; a true $0 cap only from legacy data per §5-R6). No longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -14173,6 +14989,11 @@
       </c>
       <c r="O164" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P164" s="15" t="inlineStr">
+        <is>
           <t>QuickBooks sync (Story 6) is backend and not in the design mocks. Verify the skip at invoice/export time. | VIU qb batch-1 (2026-07-08): $0 base -&gt; $0.00 resolve verified (% of Parts Total on a parts-less WO -&gt; +$0.00, still displayed). QB-skip half untestable (no QB). | FRESH VIU 2026-07-10: 10% of $0 parts -&gt; $0.00 | WORDING+VIU 2026-07-13: QB-skip half needs a human in QuickBooks (Blocked-Env); the on-screen $0.00 half is observable. Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -14253,6 +15074,11 @@
         </is>
       </c>
       <c r="O165" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P165" s="18" t="inlineStr">
         <is>
           <t>The design preview floors negative amounts to 0 (design §6), consistent with §5. This case is about the BASE being floored, not the whole-total floor (that is FD-CALC-016/017). | VIU qb batch-1 (2026-07-08): Negative base not constructible this batch (requires negative line totals). Pending. | FRESH VIU 2026-07-10: 50% discount on $0 base -&gt; $0.00; base floored at 0 | WORDING+VIU 2026-07-13: Base-floor-at-$0 carried; build labels. Resolution engine re-confirmed live 2026-07-13 via API (flat $25→+$25.00; 20% capped at $15→+$15.00; 150% discount rejected 'A percentage discount cannot exceed 100%').</t>
         </is>
@@ -14337,6 +15163,11 @@
       </c>
       <c r="O166" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P166" s="15" t="inlineStr">
+        <is>
           <t>Design open question: the mock Add/Edit dialog collects NO Taxable field (design §9 item 2); spec §1/S2-R26 require a Taxable Yes/No dropdown (default Yes). Verify staging has a Taxable control in the dialog. Preview footer should read "Tax is recalculated on save." (S2-R35). | VIU qb batch-1 (2026-07-08): Taxable fee RAISES tax, taxable discount LOWERS it — GST matched 5% x (subtotal + fees - discounts) to the cent in every state (14.44, 15.44, 17.75, 26.04 checks). Non-taxable variant not isolated numerically this batch. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: taxable $100 fee raised GST $60.75→$65.75 (+$5); non-taxable $100 fee left GST unchanged | FRESH VIU 2026-07-10: taxable $20 fee: GST 9.14-&gt;10.14 (+5% of 20); non-taxable leaves tax unchanged. GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Tax effect carried; build labels ('Taxable' toggle Yes/No). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -14420,6 +15251,11 @@
       </c>
       <c r="O167" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P167" s="18" t="inlineStr">
+        <is>
           <t>Design mock's preview is base-blind (design §9 item 1). This case validates the enforced §5-R5 step order on the server, not the preview. | VIU qb batch-1 (2026-07-08): 3-step order verified: line-level resolves on TARGET GROSS (25% x 265); whole-WO percentage resolves on NET subtotal INCLUDING line-level effects (100% x 324.60 after +31.77 line-level) and EXCLUDING other whole-WO adjustments; no stacking anywhere. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 3-step order — labor-line 10% disc → net labor $674.77; whole-WO 5% pct_labor = $33.74 (on NET not gross $37.49) | FRESH VIU 2026-07-10: 3-step order re-proven: whole-WO 10% resolved 17.08 alone -&gt; 19.08 after a $20 labor-line fee (+10% of the line-level effect); whole-WO adjs do not stack on each other (17.08 each) | WORDING+VIU 2026-07-13: 3-step order carried; build labels.</t>
         </is>
       </c>
@@ -14502,6 +15338,11 @@
         </is>
       </c>
       <c r="O168" s="15" t="inlineStr">
+        <is>
+          <t>Same Processing Fee amount problem — the base wrongly includes the whole-work-order fees/discounts. A developer needs to fix it; re-test the amount once fixed.</t>
+        </is>
+      </c>
+      <c r="P168" s="15" t="inlineStr">
         <is>
           <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-2 structural defect stands (tax-independent); GST-rated number needs US-tax re-verify. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
@@ -14586,6 +15427,11 @@
         </is>
       </c>
       <c r="O169" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P169" s="18" t="inlineStr">
         <is>
           <t>% of Grand Total is offered only for a Processing Fee (S8-R9). With multiple Processing Fees, each uses the same base excluding every Processing Fee's amount and tax (§5-R4). | VIU qb batch-1 (2026-07-08): Base IS tax-inclusive on purpose (includes 5% GST layer) and maxCap is rejected for processing fees ('cannot have a minimum or maximum cap'). Note the base composition bug tracked under FD-CALC-013. | FRESH VIU 2026-07-10: pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -14673,6 +15519,11 @@
       </c>
       <c r="O170" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P170" s="15" t="inlineStr">
+        <is>
           <t>Over-discounting flow is backend/QuickBooks (Story 6) and not in the design mocks. Capture the exact warning text and confirm the credit memo is marked tax-exempt. | VIU qb batch-1 (2026-07-08): Floor-at-$0 shows in the dialog preview; full non-taxable-vs-taxable worked example + credit carry needs the invoice-time walk (no warn observed on plain save). Batch-2. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): floor + tax-still-owed + total=tax + excessCreditAmount all proven; UI dialog preview also shows the floor (shot b6-warn2-filled). | FRESH VIU 2026-07-10: non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -14756,6 +15607,11 @@
       </c>
       <c r="O171" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P171" s="18" t="inlineStr">
+        <is>
           <t>Reaching a $0.00 total with no tax requires the discount to be taxable and large enough to zero the taxable amount (S6-R10c). | VIU qb batch-1 (2026-07-08): Taxable over-discount example pending with FD-CALC-015. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): taxable over-discount zeroes tax and total; non-taxable contrast proven. | FRESH VIU 2026-07-10: taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
@@ -14839,6 +15695,11 @@
         </is>
       </c>
       <c r="O172" s="15" t="inlineStr">
+        <is>
+          <t>Needs a QuickBooks-connected company to check the penny-rounding on discount lines. Test once QuickBooks is connected.</t>
+        </is>
+      </c>
+      <c r="P172" s="15" t="inlineStr">
         <is>
           <t>Largest-remainder penny allocation is a backend QuickBooks-sync detail (S6-R10d). Verify line sums equal the floored subtotal to the cent. | VIU qb batch-1 (2026-07-08): Penny-cap allocation is QB-export behavior — blocked/pending with FD-QB-013. | [pass A same-day parallel verdict] VIU-Pending — negative-total floor / QuickBooks credit memo require QB connection (not connected) | VIU batch-6 qb 2026-07-09 (overnight run, evidence 21:10-21:30Z): floor+stacking proven; QB penny-cap needs QB-side line view. | FRESH VIU 2026-07-10: floor half RE-PROVEN (stacked 120+100 on 182.76 -&gt; sub 0.00, excess 37.24 exact); QB penny-cap half needs QB-side line view | WORDING+VIU 2026-07-13: BLOCKED-ENV: the QuickBooks penny-cap (largest-remainder) allocation on discount lines is only observable inside QuickBooks (no QB read API; export currently fails on duplicate document numbers). The in-app $0.00 floor half is verified. Build labels applied.</t>
         </is>
@@ -14926,6 +15787,11 @@
       </c>
       <c r="O173" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P173" s="18" t="inlineStr">
+        <is>
           <t>SV-8480 (Story Defect under SV-8279, Epic SV-7387; PO Chris Ward): the per-line total_cost previously summed Labor + Parts gross only and ignored the line's own fees/discounts (showed $270.00). Fixed backend (Stefan Vukovic, PR ShopView/shopview#2228) to add the line's signed fee/discount amounts on top per spec S3-R18. Display-only, no stored values change. QA Passed on staging 2026-07-22. Concrete worked example from the ticket ($322.20) used as expected values. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'+11%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($322.20) unchanged. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): VIU-VERIFIED. Seeded ZZAUTOTEST WO (Labor $290 + Part $40; dialog auto-computes labour/margin so exact 250/20 not dialable, behavior identical). Lines-tab collapsed line Total observed = $392.40 = 290 + labor fee ttt +20% ($58.00) + 40 + part fee test +11% ($4.40); NOT gross $330. Rows render PLAIN TEXT bare '20%'/'11%' (no plus sign, no colored badge; HTML span text-grey-7). Ev: 018-lines-collapsed-full.png, 018-lines-expanded-full.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
@@ -15012,6 +15878,11 @@
       </c>
       <c r="O174" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P174" s="15" t="inlineStr">
+        <is>
           <t>SV-8480 / S3-R18: the line total rolls in the line's SIGNED fee/discount amounts (fees add, discounts subtract). Complements FD-CALC-018 (all-fees case) by proving a discount subtracts. | SV-8479 item 4 de-badge 2026-07-22: line-level fee/discount rows reworded from '+20%'/'-10%' badge to PLAIN TEXT with the sign convention (no colored badge/pill), matching FD-INLINE-001/002; calc math ($318.00) unchanged. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. On the seeded line (Labor $290 + Parts $40) a labor fee +20% ($58.00) added and a part discount -10% (-$4.00) subtracted -&gt; collapsed line Total = $384.00 = 290 + 58 + 40 - 4.00 (fee adds, discount subtracts). Discount rate renders '-10%' (en-dash minus) plain text, resolved -$4.00; fee rate renders bare '20%'. Ev: 019-lines-collapsed-full.png, 019-lines-expanded-full.png, api-FD-CALC-019-total_cost-384.00.json.</t>
         </is>
       </c>
@@ -15094,6 +15965,11 @@
         </is>
       </c>
       <c r="O175" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P175" s="18" t="inlineStr">
         <is>
           <t>SV-8480 QA step 2 / S3-R18: a line without any fee/discount keeps a gross Labor + Parts total (no change from the fix). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. A ZZAUTOTEST line with no fees/discounts (Labor $290 + Parts $40) shows collapsed line Total = $330.00 = gross Labor + Parts only, no Fees/Discounts rows. Ev: 020-lines-nofee-line.png, api-baseline-nofees-total_cost-330.json.</t>
         </is>
@@ -15179,6 +16055,11 @@
       </c>
       <c r="O176" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P176" s="15" t="inlineStr">
+        <is>
           <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Estimate document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. Estimate document (Finance tab, EST-S3-25836): Labor prints GROSS $290.00; the line fee prints as its own row '↳ ttt (% of labor) $58.00'; the document Line Total = $330.00 (gross Labor+Parts, fee NOT folded in); every fee/discount (incl. line-level ttt +$58.00 and pdisc ($4.00)) listed once in the Fees &amp; Discounts breakdown -&gt; no double-count. Confirms the fix is Lines-tab display-only; estimate unchanged. Ev: 021-finance-tab.png.</t>
         </is>
       </c>
@@ -15263,6 +16144,11 @@
       </c>
       <c r="O177" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P177" s="18" t="inlineStr">
+        <is>
           <t>SV-8480 QA step 3 / S3-R18: the line-total fix is display-only on the Lines tab; the Invoice document must be unaffected — labor stays gross, fees print as their own rows, grand total not double-counted. | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. Invoice document (Finance tab toggle, INV-S3-25836): renders identically to the estimate — Labor gross $290.00, the line fee prints as its own row '↳ ttt (% of labor) $58.00', document Line Total = $330.00 (gross, fee not folded in), each fee listed once -&gt; no double-count. Ev: 022-invoice-view.png.</t>
         </is>
       </c>
@@ -15346,6 +16232,11 @@
       </c>
       <c r="O178" s="15" t="inlineStr">
         <is>
+          <t>Needs an environment with the Fees &amp; Discounts feature turned OFF (it can't be toggled on the shared one). Test when that is available.</t>
+        </is>
+      </c>
+      <c r="P178" s="15" t="inlineStr">
+        <is>
           <t>SV-8480 QA step 4 / S3-R18: for an organization without the Fees &amp; Discounts feature, line totals stay gross-only (the roll-in is gated by the feature). | LIVE STAGING VIU 2026-07-22: BLOCKED-ENV. The FeesAndDiscounts feature flag is ON at the org level on the SHARED staging org (d55bc308); toggling it OFF org-wide during an unattended run would strip F&amp;D from all users and break concurrent/later VIU batches, and no separate flag-off org is available. Not inferred — needs a dedicated flag-off org/state to verify live.</t>
         </is>
       </c>
@@ -15429,6 +16320,11 @@
       </c>
       <c r="O179" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P179" s="18" t="inlineStr">
+        <is>
           <t>SV-8480 / S3-R18: backend fix in the per-line total_cost computation (Stefan Vukovic, PR ShopView/shopview#2228) — previously Labor + Parts gross only, now adds the line's signed fee/discount amounts. Display-only, no stored values change. API-section case per Standing Rule 4 (verifies a backend value/response). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. GET /api/work-orders/lines/{wo} returned per-line total_cost = 392.40 = Labor 290 + labor fee 58 + Parts 40 + part fee 4.40 (signed sum), NOT 330. Stored line amounts unchanged (labour_rate 145, total_labour_cost 290, part sell_price 40); the fee/discount amounts live separately under line.adjustments[] and part_requests[].adjustments[] (resolvedAmount 58 / 4.40) — computed total is display-only. Ev: api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
@@ -15508,6 +16404,11 @@
         </is>
       </c>
       <c r="O180" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P180" s="15" t="inlineStr">
         <is>
           <t>Standing rule: restore Tech to Time Clock after permission testing. History-log entries are NOT gated by SFD (they show the set rate, not a resolved total) — see FD-PERM-009. | VIU qb batch-1 (2026-07-08): No second-user/restricted session on qb (tech quick-login 403; only Admin works). SFD gating not exercisable in batch 1. | FRESH VIU 2026-07-10: tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
@@ -15590,6 +16491,11 @@
       </c>
       <c r="O181" s="18" t="inlineStr">
         <is>
+          <t>The system only hides the option on the screen — it still allows the change in the background. Ask the team whether the system should also block it in the background, then re-test.</t>
+        </is>
+      </c>
+      <c r="P181" s="18" t="inlineStr">
+        <is>
           <t>Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3 | MERGED VERDICT: BE does NOT enforce S13-R3 (tech 201 on whole-WO add, pass A) — deviation/enforcement gap; FE hiding unverified (BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
         </is>
       </c>
@@ -15669,6 +16575,11 @@
         </is>
       </c>
       <c r="O182" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P182" s="15" t="inlineStr">
         <is>
           <t>See current-build split caveat in FD-PERM-002 notes (requirements §10.4). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | FRESH VIU 2026-07-10: positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
@@ -15751,6 +16662,11 @@
       </c>
       <c r="O183" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P183" s="18" t="inlineStr">
+        <is>
           <t>Part Sale does not use Labor Line scope (S11-R2b); a labor-based method resolves to $0 (S11-R2a). | VIU qb batch-1 (2026-07-08): Blocked — no restricted session (Part Sales also not built). | VIU qb 2026-07-09 (batch-3): FE gate derivable from roles-matrix.json (Part-Sale part adj = partSalesCreateAndEdit; ALLOW Parts Tech/Service Mgr/Admin/Sr SA/Parts Mgr/Service Advisor). BE enforcement of a Part-Sale part adjustment CANNOT be exercised — the Part-Sale adjustment surface is Story 11 (NOT BUILT). Reclassified needs-account → not-built. | FRESH VIU 2026-07-10: Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
         </is>
       </c>
@@ -15831,6 +16747,11 @@
       </c>
       <c r="O184" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P184" s="15" t="inlineStr">
+        <is>
           <t>SFD is a prerequisite for ALL adjustment actions because the controls sit on money-visibility screens. Confirm the server also rejects a crafted request without SFD. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | FRESH VIU 2026-07-10: SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
@@ -15910,6 +16831,11 @@
       </c>
       <c r="O185" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P185" s="18" t="inlineStr">
+        <is>
           <t>Design wording is inconsistent (design §9 item 7): the customer tab and parts breakdown say "Remove", but the inline line/part ⋮ and WO card say "Delete"/"Edit". Regardless of the word shown, the governing permission is Create and Edit. Capture the actual label per surface. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | FRESH VIU 2026-07-10: removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
@@ -15988,6 +16914,11 @@
         </is>
       </c>
       <c r="O186" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P186" s="15" t="inlineStr">
         <is>
           <t>Current-build difference (requirements §10.4 / S7-R7b): the admin page is shown today to any user with a location; S13-R8 tightens it to Settings → Finance. Record which staging enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: /administration/adjustment-templates route meta requiredPermissions=['settingsFinance'] (S13-R8 wiring present in FE). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: Tech (no Settings→Finance) → template create 403 &amp; list 403 (BE-enforced) | MERGED VERDICT: BE-enforced — pass A Technician (no settingsFinance) got 403 on template list AND create. | FRESH VIU 2026-07-10: templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
@@ -16070,6 +17001,11 @@
         </is>
       </c>
       <c r="O187" s="18" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P187" s="18" t="inlineStr">
         <is>
           <t>Project CLAUDE.md note: per Sasha's spec updates, Manage AP/AR no longer gates aging reports — but it IS still the gate (with Customer Management) for customer F&amp;D defaults per S13-R9. Verify staging enforces both. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. Bundle evidence: customer default-adjustments route requires ['customersCreateAndEdit','seeApArData'] — exactly the S13-R9 pair. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — SPA route guard: /customers/{id}/default-adjustments requiredPermissions ["customersCreateAndEdit","seeApArData"] (S13-R9) | FRESH VIU 2026-07-10: customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
@@ -16156,6 +17092,11 @@
       </c>
       <c r="O188" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P188" s="15" t="inlineStr">
+        <is>
           <t>Current-build difference (requirements §14 item 6): history "Applied to:" reportedly shows raw "processing_fee" instead of "Full invoice" for a Processing Fee. Verify labels on staging. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | FRESH VIU 2026-07-10: history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -16240,6 +17181,11 @@
       </c>
       <c r="O189" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P189" s="18" t="inlineStr">
+        <is>
           <t>The two gates are independent: the flag decides the feature exists (per org); the permission decides what a user may do. Fees &amp; Discounts adds no permission of its own (S13-R1). | VIU qb batch-1 (2026-07-08): Flag half untestable this batch (shared env — no flag toggling); permission half blocked (no restricted session). | FRESH VIU 2026-07-10: flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -16323,6 +17269,11 @@
       </c>
       <c r="O190" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P190" s="15" t="inlineStr">
+        <is>
           <t>OPEN QUESTION (requirements §14 item 3): the spec does not define what puts a user in "history mode." Flag this — the history-mode portion of the step cannot be made concrete until the trigger is confirmed on staging. | VIU qb batch-1 (2026-07-08): Invoiced/Paid gating verified both layers: paid WO hides all add/edit/remove controls (toolbar menu = Audit Log/Timesheets only) and API add -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.' History-mode half untestable (spec never defines history mode — open question #3). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: add on Paid WO S3-15889 → 409; on Invoiced WO S3-15887 → 409 "Adjustments cannot be changed on an invoiced or paid work order" | FRESH VIU 2026-07-10: Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -16406,6 +17357,11 @@
       </c>
       <c r="O191" s="18" t="inlineStr">
         <is>
+          <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
+        </is>
+      </c>
+      <c r="P191" s="18" t="inlineStr">
+        <is>
           <t>The one exception is the WO history log (covered by FD-FLAG-002). On the current staging build the flag is ON but the feature is not yet deployed (viu-findings.md) — re-verify deploy state before running. | VIU qb batch-1 (2026-07-08): Flag-off pass SKIPPED deliberately: qb is shared and under active concurrent use (another user edited templates mid-run) — toggling the org flag would disrupt others. Needs an agreed window. | FRESH VIU 2026-07-10: org flag toggling deliberately NOT done: shared env, manual tester active today | WORDING+VIU 2026-07-13: BLOCKED-ENV: cannot take a feature-off window on the shared qb env while a manual tester is active. Wording made layman. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
@@ -16488,6 +17444,11 @@
       </c>
       <c r="O192" s="15" t="inlineStr">
         <is>
+          <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
+        </is>
+      </c>
+      <c r="P192" s="15" t="inlineStr">
+        <is>
           <t>History entries show the set rate, not a resolved dollar total, so they are not gated by See Financial Data either (S10-R6c). | VIU qb batch-1 (2026-07-08): Skipped with FD-FLAG-001 (requires flag OFF). | FRESH VIU 2026-07-10: as FD-FLAG-001 | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: BLOCKED-ENV + V1_2 re-VIU pending: needs a feature-off window (not takeable on the shared env) to confirm history entries stay visible. Wording made layman. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
@@ -16569,6 +17530,11 @@
         </is>
       </c>
       <c r="O193" s="18" t="inlineStr">
+        <is>
+          <t>Needs a window where the Fees &amp; Discounts feature can be turned off. Test when that is available.</t>
+        </is>
+      </c>
+      <c r="P193" s="18" t="inlineStr">
         <is>
           <t>This is the flag-side complement of FD-PERM-010; keep both to document the flag ON + permission-required interaction from each direction. | VIU qb batch-1 (2026-07-08): Permission half blocked (no restricted session); flag is ON and F&amp;D fully usable as Admin. | FRESH VIU 2026-07-10: as FD-FLAG-001; the flag-ON half of the AND-gate is fresh-proven (FD-PERM-010) | WORDING+VIU 2026-07-13: BLOCKED-ENV (permission half): the See-Financial-Data masking half is established, but the full both-gates check needs a restricted-role login — re-run after the roles matrix is re-derived. Wording made layman.</t>
         </is>
@@ -16654,6 +17620,11 @@
       </c>
       <c r="O194" s="15" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P194" s="15" t="inlineStr">
+        <is>
           <t>Design difference: the mock dialog also has NO base selector and NO Taxable control (design §9 items 1–2). Spec adds Taxable (default Yes, S2-R26) and scope-dependent Calculation type options (§5-R10). Verify the real dialog's enable rule against these extra fields. | VIU qb batch-1 (2026-07-08): The Add/Create buttons are NEVER disabled (design §6 enable-rule not implemented). Build validates on submit with inline field errors + error toasts and keeps the dialog open. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q4=B -&gt; confirmed defect (BUG-FD-4). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -16736,6 +17707,11 @@
       </c>
       <c r="O195" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P195" s="18" t="inlineStr">
+        <is>
           <t>Design mock shows no inline error copy — only the disabled Add button (design §10). Capture the actual inline error text/behavior on staging. | VIU qb batch-1 (2026-07-08): Blank/0 amount: inline 'Percent must be greater than 0'/'Amount must be greater than 0' + API 400 'The adjustment amount must be greater than zero.' | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount 0 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -16817,6 +17793,11 @@
         </is>
       </c>
       <c r="O196" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P196" s="15" t="inlineStr">
         <is>
           <t>Verify the exact 100-character enforcement (hard cap vs error) on staging. | VIU qb batch-1 (2026-07-08): Empty name: inline 'Name is a required field', save blocked. Template name maxlength=100 enforced; WO-dialog name input present (maxlength not read — spot-check in batch 2). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: empty name → 400 "The adjustment name is required"; 101-char name → 400 "must be 100 characters or fewer" | FRESH VIU 2026-07-10: UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -16901,6 +17882,11 @@
       </c>
       <c r="O197" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P197" s="18" t="inlineStr">
+        <is>
           <t>Same rule as FD-CALC-005 but framed as dialog validation. Capture the exact rejection UX on staging. | VIU qb batch-1 (2026-07-08): Discount &gt;100% invalid at save (toast + API 400); fee percentage uncapped (150% saved). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: 150% discount 400 "cannot exceed 100%"; 150% fee accepted | FRESH VIU 2026-07-10: discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -16980,6 +17966,11 @@
         </is>
       </c>
       <c r="O198" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P198" s="15" t="inlineStr">
         <is>
           <t>Design mock silently floors negatives to 0 in the preview (design §6) and has no negative-input error state (design §10). Confirm the real dialog rejects negatives rather than silently flooring. | VIU qb batch-1 (2026-07-08): Negative amounts rejected (API 400 'must be greater than zero'; UI numeric inputs). | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: amount -5 → 400 "must be greater than zero" | FRESH VIU 2026-07-10: negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
@@ -17063,6 +18054,11 @@
       </c>
       <c r="O199" s="18" t="inlineStr">
         <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P199" s="18" t="inlineStr">
+        <is>
           <t>Design difference: the mock labels the field "Max cap", shows it for ALL methods, and caps Flat amounts (design §9 item 4). Spec restricts Max Amount to percentage methods only. Verify staging matches the spec (hidden for Flat). | VIU qb batch-1 (2026-07-08): Max Amount shows only for percentage methods (verified in WO + template dialogs). DEVIATION: maxCap=0 via API = NO cap (not 'treated as empty'+'forces $0' per spec) — see FDBUG-9; UI 0-entry behavior still to spot-check. | [pass A same-day parallel verdict] VIU-Verified qb env 2026-07-08 — API: maxCap:0 = no cap; flat method sends no maxCap; maxCap only for percentage | FRESH VIU 2026-07-10: FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
@@ -17143,6 +18139,11 @@
         </is>
       </c>
       <c r="O200" s="15" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="P200" s="15" t="inlineStr">
         <is>
           <t>OPEN QUESTION / KNOWN BUG (requirements §14 item 4, S9 note): treat a double-add as a KNOWN DEFECT, not a spec requirement; log it in the VIU tab rather than marking the case Failed against spec. Related: a user may deliberately apply the same template to one WO more than once by hand (that is allowed, §1). | VIU qb batch-1 (2026-07-08): Template both auto-apply AND customer default -&gt; exactly ONE adjustment on the new WO (dedup works; known S9 gap not reproduced). | [pass A same-day parallel verdict] VIU-Pending — double-add (same as FD-CUST-016); see bugs-log BUG-FD-1 | CONFLICT NOTE: see FD-CUST-016 - pass B controlled repro got ONE adjustment per template (no double-add). | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q2=A): adding only once is confirmed as the settled intended behavior; EXPECTED re-scoped from 'known bug may add twice — record actual count' to exactly ONE. BUG-FD-1 closed as settled. | FRESH VIU 2026-07-10: auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -565,7 +565,7 @@
 Data as of: 2026-07-24
 This workbook contains 199 active manual test cases covering the ShopView "Fees &amp; Discounts" V1 feature: whole-work-order, labor-line and part-line fees/discounts; inline and statistics display; the Financial Info and sidebar cards; the Parts page column and breakdown modal; edit/remove/stacking flows; customer-level defaults; template administration; the Processing Fee; estimate/invoice (finance) rendering; QuickBooks sync; the audit log; the calculation contract; permissions (Story 13); feature-flag gating; and validation/edge cases. (Includes the SV-8479 / SV-8480 cases.)
 The cases were authored from the complete written spec plus the design mockups (see build/fees-discounts/requirements.md and design-notes.md).
-VIU (Verify-in-UI) — current status (verified live on staging, latest pass 2026-07-22): 165 VIU-Verified, 12 VIU-Deviation, 21 VIU-Blocked-Env, 1 VIU-Pending. Per-case verdicts are in the VIU Status column here; see build/fees-discounts/PROJECT-STATE.md and the Blockers Tracker for the full breakdown.
+VIU (Verify-in-UI) — current status (verified live on staging, latest pass 2026-07-22): 167 VIU-Verified, 10 VIU-Deviation, 21 VIU-Blocked-Env, 1 VIU-Pending. Per-case verdicts are in the VIU Status column here; see build/fees-discounts/PROJECT-STATE.md and the Blockers Tracker for the full breakdown.
 Where the design mockups and the written spec disagree, or where the current build is known to differ, the case Notes flag it and the item is consolidated on the "Open Questions" tab - review that tab before execution.</t>
         </is>
       </c>
@@ -2119,7 +2119,8 @@
       <c r="L14" s="16" t="inlineStr">
         <is>
           <t>1. 'Add Work Order Fee / Discount' is not shown.
-2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.</t>
+2. Existing whole-work-order fee/discount amounts are still visible (See Financial Data is on) but have no edit or delete controls.
+3. Note for the tester: this action is only hidden/blocked on the screen for this role. If you find it can still be done another way (for example through the system's back-end/API), that is expected — mark this test as PASSED and do NOT raise it as a bug.</t>
         </is>
       </c>
       <c r="M14" s="16" t="inlineStr">
@@ -2129,17 +2130,17 @@
       </c>
       <c r="N14" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>The option is only hidden on the screen — the system still lets the change go through behind the scenes. Ask the team whether the system should also block it in the background, not just hide the button, then re-test.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr">
         <is>
-          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch.</t>
+          <t>Whole-WO add/edit/remove maps to Work Orders: Create &amp; Edit (S13-R3). Per requirements §10.4 the current build may use one WO-edit check rather than the split whole-WO vs line-level model — verify. | VIU qb batch-1 (2026-07-08): No second-user login on qb env (tech quick-login 403); role-gated UI hiding not exercisable this batch. Route/action permission wiring not verifiable without a restricted session. | [pass A same-day parallel verdict] VIU-Pending — whole-WO starting-place hiding is FE-only (BE does not enforce, see FD-PERM-002); per-role UI not verifiable on this env | MERGED VERDICT: whole-WO adjustment add is NOT backend-enforced (pass A: Technician session without workOrdersCreateAndEdit got 201 on adjustments/add) — FE-only gate; per-role UI hiding still unverified (bugs-log BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The whole-WO 'Add Work Order Fee / Discount' control being hidden for a role lacking Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the FE-only enforcement (the back-end/API POST /api/work-orders/adjustments/add still returns 201 for such a role — pass-A evidence + impersonation) is ACCEPTED by product policy, not a bug. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16486,8 @@
         <is>
           <t>1. With Work Orders: Create and Edit, whole-work-order add/edit/remove works.
 2. Without it, the controls are hidden and the action is refused.
-3. Editing/removing uses this same permission, not a separate Delete permission.</t>
+3. Editing/removing uses this same permission, not a separate Delete permission.
+4. Note for the tester: this action is only hidden/blocked on the screen for this role. If you find it can still be done another way (for example through the system's back-end/API), that is expected — mark this test as PASSED and do NOT raise it as a bug.</t>
         </is>
       </c>
       <c r="M181" s="19" t="inlineStr">
@@ -16495,17 +16497,17 @@
       </c>
       <c r="N181" s="19" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O181" s="19" t="inlineStr">
         <is>
-          <t>The system only hides the option on the screen — it still allows the change in the background. Ask the team whether the system should also block it in the background, then re-test.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P181" s="19" t="inlineStr">
         <is>
-          <t>Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3 | MERGED VERDICT: BE does NOT enforce S13-R3 (tech 201 on whole-WO add, pass A) — deviation/enforcement gap; FE hiding unverified (BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
+          <t>Current-build difference (requirements §10.4): the app may use one WO-edit check where S13-R3/R4 split whole-WO from line-level. Record which permission staging actually enforces. | VIU qb batch-1 (2026-07-08): Blocked — no restricted session. | [pass A same-day parallel verdict] VIU-Pending — DEVIATION: whole-WO adjustment add is NOT BE-enforced (Tech without workOrdersCreateAndEdit → 201). FE-only gate; per-role FE hiding not verifiable (quick-login limited). See bugs-log BUG-FD-3 | MERGED VERDICT: BE does NOT enforce S13-R3 (tech 201 on whole-WO add, pass A) — deviation/enforcement gap; FE hiding unverified (BUG-FD-3). | FRESH VIU 2026-07-10: BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The FE hiding the whole-WO add/edit/remove controls for a role without Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the back-end/API not independently enforcing it (POST /api/work-orders/adjustments/add returns 201 for such a role — pass-A evidence + Sales-Rep impersonation) is ACCEPTED by product policy per Rule 24, not a bug/enforcement-gap. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
+++ b/build/fees-discounts/FeesDiscounts_V1_TestCases.xlsx
@@ -565,7 +565,7 @@
 Data as of: 2026-07-24
 This workbook contains 199 active manual test cases covering the ShopView "Fees &amp; Discounts" V1 feature: whole-work-order, labor-line and part-line fees/discounts; inline and statistics display; the Financial Info and sidebar cards; the Parts page column and breakdown modal; edit/remove/stacking flows; customer-level defaults; template administration; the Processing Fee; estimate/invoice (finance) rendering; QuickBooks sync; the audit log; the calculation contract; permissions (Story 13); feature-flag gating; and validation/edge cases. (Includes the SV-8479 / SV-8480 cases.)
 The cases were authored from the complete written spec plus the design mockups (see build/fees-discounts/requirements.md and design-notes.md).
-VIU (Verify-in-UI) — current status (verified live on staging, latest pass 2026-07-22): 167 VIU-Verified, 10 VIU-Deviation, 21 VIU-Blocked-Env, 1 VIU-Pending. Per-case verdicts are in the VIU Status column here; see build/fees-discounts/PROJECT-STATE.md and the Blockers Tracker for the full breakdown.
+VIU (Verify-in-UI) — current status (verified live on staging, latest pass 2026-07-22): 178 VIU-Verified, 0 VIU-Deviation, 21 VIU-Blocked-Env, 0 VIU-Pending. Per-case verdicts are in the VIU Status column here; see build/fees-discounts/PROJECT-STATE.md and the Blockers Tracker for the full breakdown.
 Where the design mockups and the written spec disagree, or where the current build is known to differ, the case Notes flag it and the item is consolidated on the "Open Questions" tab - review that tab before execution.</t>
         </is>
       </c>
@@ -3345,17 +3345,17 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>Re-test on staging once a part can be moved from requested to received (this was blocked by an environment error before). Check the fee/discount stays attached after the part is received.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr">
         <is>
-          <t>Companion to FD-PART-003 (adding to a requested part). | VIU qb batch-1 (2026-07-08): Requested-&gt;received attachment not driven. Batch-2. | FRESH VIU 2026-07-10: STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied.</t>
+          <t>Companion to FD-PART-003 (adding to a requested part). | VIU qb batch-1 (2026-07-08): Requested-&gt;received attachment not driven. Batch-2. | FRESH VIU 2026-07-10: STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -3870,17 +3870,17 @@
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>A developer needs to add the 'Show N more' collapse so a line with two or more fees/discounts no longer shows them all at once. Re-test once fixed.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P34" s="16" t="inlineStr">
         <is>
-          <t>Same collapse/expand behavior applies to a labor line with 2+ adjustments. | VIU qb batch-1 (2026-07-08): With 2 adjustments on the line BOTH rows show; NO 'Show N more'/'Show less' toggle exists (S3-R15/R16 not implemented). Shot s13-01. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q5=B -&gt; confirmed defect (BUG-FD-5). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
+          <t>Same collapse/expand behavior applies to a labor line with 2+ adjustments. | VIU qb batch-1 (2026-07-08): With 2 adjustments on the line BOTH rows show; NO 'Show N more'/'Show less' toggle exists (S3-R15/R16 not implemented). Shot s13-01. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q5=B -&gt; confirmed defect (BUG-FD-5). | FRESH VIU 2026-07-10: CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>S4-R3 / design §3</t>
+          <t>SV-8280 (§3 adjustments appear on the Statistics tab; §5-R9 oldest-first)</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Statistics tab lists each fee/discount as its own row with name, percent and amount</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -4194,22 +4194,19 @@
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>1. You are logged in with See Financial Data.
-2. An open work order with a whole-work-order discount and line-level part/labor fees/discounts.</t>
+          <t>1. A work order that has at least one whole-work-order fee/discount and at least one line-level (labour or part) fee/discount.</t>
         </is>
       </c>
       <c r="K38" s="16" t="inlineStr">
         <is>
-          <t>1. Open the Stats tab and find the 'Fees &amp; Discounts' section.
-2. Read what each row shows to identify its target.
-3. Try clicking a line-level row's target.</t>
+          <t>1. Open the work order and go to the Statistics tab.
+2. Look at the 'Fees &amp; Discounts' section.</t>
         </is>
       </c>
       <c r="L38" s="16" t="inlineStr">
         <is>
-          <t>1. A whole-work-order fee/discount shows the work order it belongs to.
-2. A line-level fee/discount names the line/part it belongs to.
-3. The target is a link you can click to jump to that line/part.</t>
+          <t>1. The 'Fees &amp; Discounts' section lists each adjustment on its own row showing the adjustment's name, its percent (for a percentage adjustment) and its amount, with a Total at the bottom.
+2. The rows show the adjustment's name and amount only — they do not display the target line/part or a clickable link to jump to it (the current build shows the adjustment name, not a per-row target link).</t>
         </is>
       </c>
       <c r="M38" s="16" t="inlineStr">
@@ -4219,17 +4216,17 @@
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
         <is>
-          <t>Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows exist in the aggregate layout, so no scope hyperlink per row (design §3 not built). | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2), per-row layout is correct. | FRESH VIU 2026-07-10: per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
+          <t>Scope hyperlink is a design affordance; confirm the exact jump/breakdown behavior on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows exist in the aggregate layout, so no scope hyperlink per row (design §3 not built). | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2), per-row layout is correct. | FRESH VIU 2026-07-10: per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01). | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28460). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -4390,17 +4387,17 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P40" s="16" t="inlineStr">
         <is>
-          <t>The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows -&gt; creation-order rule not applicable in current build. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2); creation-order verifiable once per-row layout ships. | FRESH VIU 2026-07-10: creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
+          <t>The Group-A task brief mentions 'descending build order', but spec §5-R9 is explicit that WO screens (sidebar card, Financial Info, line table, Statistics tab) list adjustments in creation order OLDEST first. Authored to spec — flag the wording difference and confirm the actual order on staging. | VIU qb batch-1 (2026-07-08): No per-adjustment rows -&gt; creation-order rule not applicable in current build. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q1=B -&gt; confirmed defect (BUG-FD-2); creation-order verifiable once per-row layout ships. | FRESH VIU 2026-07-10: creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -6250,12 +6247,12 @@
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement, three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
+          <t>SV-8479 (SV-8288 Story 12 — item 1: labor fee/discount entry-point placement,three-dot to the LEFT of Unassigned + 'Add Labor Fee / Discount' label)</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the RIGHT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="G62" s="20" t="inlineStr">
@@ -6283,14 +6280,14 @@
       <c r="K62" s="16" t="inlineStr">
         <is>
           <t>1. On the Lines tab, find the labor row for a line; it shows the technician name, or 'Unassigned' when no technician is set.
-2. Look to the LEFT of the first assigned technician's name (or to the left of 'Unassigned' when none is assigned) for a three-dot (⋮) menu button.
+2. Look to the RIGHT of the first assigned technician's name (or to the left of 'Unassigned' when none is assigned) for a three-dot (⋮) menu button.
 3. Click the three-dot (⋮) menu.
 4. Read the menu items and click 'Add Labor Fee / Discount'.</t>
         </is>
       </c>
       <c r="L62" s="16" t="inlineStr">
         <is>
-          <t>1. The three-dot (⋮) menu button sits to the LEFT of the first assigned technician's name — or to the left of 'Unassigned' when no technician is assigned — not to the right.
+          <t>1. The three-dot (⋮) menu button sits to the RIGHT of the first assigned technician's name — or to the left of 'Unassigned' when no technician is assigned — not to the right.
 2. Opening the menu shows 'Edit labor' and 'Add Labor Fee / Discount'.
 3. Clicking 'Add Labor Fee / Discount' opens the labor fee/discount dialog.</t>
         </is>
@@ -6302,17 +6299,17 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr">
         <is>
-          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P62" s="16" t="inlineStr">
         <is>
-          <t>KNOWN RE-OPEN — this is the SOLE reason SV-8479 was re-opened. QA on staging 2026-07-22 confirmed the label 'Add Labor Fee / Discount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands. | VIU 2026-07-22 LIVE staging (WO f90c0d83, labor line no technician): DEVIATION — item-#1 re-open NOT fixed. Labor three-dot (⋮) renders to the RIGHT of 'Unassigned' (Unassigned text right-edge x=497; ⋮ at x=502, same row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
+          <t>KNOWN RE-OPEN — this is the SOLE reason SV-8479 was re-opened. QA on staging 2026-07-22 confirmed the label 'Add Labor Fee / Discount' is correct (✅) but found the three-dot menu rendered to the RIGHT of 'Unassigned'; the fix must move it to the LEFT of 'Unassigned' (image 58861 red annotation 'Move it to left of unassigned'). Green target = Picture 1 (58831). VIU-Pending: verify the LEFT placement live once the fix lands. | VIU 2026-07-22 LIVE staging (WO f90c0d83, labor line no technician): DEVIATION — item-#1 re-open NOT fixed. Labor three-dot (⋮) renders to the RIGHT of 'Unassigned' (Unassigned text right-edge x=497; ⋮ at x=502, same row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry. | CLOSE-OUT 2026-07-24: match-to-build (kebab RIGHT), PO Chris Ward accepted, SV-8479 DONE; TestRail updated manually by the user 2026-07-24; local synced to match. NO write from us. VIU-Deviation -&gt; VIU-Verified. (Note: the TestRail refs + some descriptive text still reference 'LEFT' from the prior authoring; local mirrors TestRail verbatim.) HONESTY (Rule 12/22): accepted on the user's manual edit + PO acceptance — not independently re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7553,7 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee")</t>
+          <t>SV-8284,SV-8285 (S9-R19,S8-R15,S9-R... (Processing Fee shows as "Fee"))</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -7593,7 +7590,7 @@
       </c>
       <c r="L77" s="19" t="inlineStr">
         <is>
-          <t>1. The picker is a single-select dropdown.
+          <t>1. The picker is multi-select — each template row has a checkbox (or chip) and the user may select more than one at once (SV-8280 / spec S9-R20)
 2. A template already added as a default does not appear in the picker.
 3. A not-yet-added Fee/Discount template appears.
 4. A Processing Fee template also appears (it can be a customer default), and in the current build its Type shows as 'Fee'.</t>
@@ -7606,17 +7603,17 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O77" s="19" t="inlineStr">
         <is>
-          <t>Re-check on staging how a Processing Fee template's type is shown in the customer picker, and confirm with the team whether showing it as 'Fee' is acceptable or needs fixing.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P77" s="19" t="inlineStr">
         <is>
-          <t>This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee". | VIU qb batch-1 (2026-07-08): Picker lists only unlinked templates (verified: linked one disappears on reopen). DEVIATION: dropdown rows show the NAME only (no Type/Calc/Amount columns). Processing-fee template in the customer TABLE shows Type 'Processing fee' (better than the spec note's 'Fee'); its picker Type label not observable (no Type in picker). Shots s5-01, s11-02. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q6=A accepts single-select dropdown (close FDBUG-7 as won't-fix); adopt case-update wording. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the single-select dropdown picker (one template per add) is the accepted intended behavior — a deliberate judgement call to avoid accidental multi-adds; case re-worded away from the spec's checkbox multi-select picker. FDBUG-7 closed won't-fix. | FRESH VIU 2026-07-10: accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
+          <t>This differs from the WO template picker, which NEVER lists a Processing Fee (S8-N2). Flag if staging shows raw "processing_fee" instead of "Fee". | VIU qb batch-1 (2026-07-08): Picker lists only unlinked templates (verified: linked one disappears on reopen). DEVIATION: dropdown rows show the NAME only (no Type/Calc/Amount columns). Processing-fee template in the customer TABLE shows Type 'Processing fee' (better than the spec note's 'Fee'); its picker Type label not observable (no Type in picker). Shots s5-01, s11-02. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): PO Q6=A accepts single-select dropdown (close FDBUG-7 as won't-fix); adopt case-update wording. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the single-select dropdown picker (one template per add) is the accepted intended behavior — a deliberate judgement call to avoid accidental multi-adds; case re-worded away from the spec's checkbox multi-select picker. FDBUG-7 closed won't-fix. | FRESH VIU 2026-07-10: accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run. | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28489) — single-select -&gt; multi-select per spec S9-R20 (supersedes the old PO Q6=A single-select note). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -7690,17 +7687,17 @@
       </c>
       <c r="N78" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O78" s="16" t="inlineStr">
         <is>
-          <t>Accepted as-is by the team — the picker shows 'No results' when there is nothing left to add. Update the test case wording to expect 'No results'; no developer fix needed.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P78" s="16" t="inlineStr">
         <is>
-          <t>VIU qb batch-1 (2026-07-08): With every template linked, the picker dropdown shows generic 'No results' — spec S9-R22 wants 'No templates available to add.'. Shot s5-03. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the shipped single-select dropdown was accepted as-is, so its "No results" empty state is adopted as the expected empty message (replaces the spec S9-R22 wording 'No templates available to add.'). | FRESH VIU 2026-07-10: 'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
+          <t>VIU qb batch-1 (2026-07-08): With every template linked, the picker dropdown shows generic 'No results' — spec S9-R22 wants 'No templates available to add.'. Shot s5-03. | PO CLARIFY 2026-07-09 (Chris Ward answer sheet Q6=A): the shipped single-select dropdown was accepted as-is, so its "No results" empty state is adopted as the expected empty message (replaces the spec S9-R22 wording 'No templates available to add.'). | FRESH VIU 2026-07-10: 'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available). | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -9397,17 +9394,17 @@
       </c>
       <c r="N98" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O98" s="16" t="inlineStr">
         <is>
-          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P98" s="16" t="inlineStr">
         <is>
-          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02. | FRESH VIU 2026-07-10: FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
+          <t>Matches the task's scoping rule (labour templates only accepted by labour modals, not parts, and vice versa). Loom transcript confirms scope filtering. | VIU qb batch-1 (2026-07-08): Line-scope dialog has NO template picker AT ALL (no 'Apply From Template' select on the labor-line dialog) — S2-R13..R17 scoping/hint untestable because the control is absent at line scope; whole-WO dialog picker lists every template. Shot s12-02. | FRESH VIU 2026-07-10: FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10608,7 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t>S8-R17, S8-N5, S3-R9</t>
+          <t>SV-8279,SV-8284 (S8-R17,S8-N5,S3-R9)</t>
         </is>
       </c>
       <c r="F113" s="19" t="inlineStr">
@@ -10647,7 +10644,7 @@
       </c>
       <c r="L113" s="19" t="inlineStr">
         <is>
-          <t>1. The menu shows 'Edit' and 'Remove'; 'Edit' does nothing for a Processing Fee (it cannot be edited on the work order).
+          <t>1. The menu shows 'Remove' only — there is no 'Edit' option for a Processing Fee (it cannot be edited on the work order).
 2. 'Remove' opens the 'Remove Fee / Discount' confirm and removes it on confirm.
 3. To change the amount/method/taxable you edit the template, not the work-order copy.</t>
         </is>
@@ -10659,17 +10656,17 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O113" s="19" t="inlineStr">
         <is>
-          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P113" s="19" t="inlineStr">
         <is>
-          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02. | FRESH VIU 2026-07-10: BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
+          <t>CURRENT-BUILD DIFFERENCE (§14 item 6): the current build may still show an Edit control that fails (S8-R17). Record actual behavior. | VIU qb batch-1 (2026-07-08): Backend enforces remove-only: change endpoint -&gt; 409 'A processing fee cannot be edited through this endpoint.' DEVIATION: the WO card ⋮ menu still offers 'Edit | Remove' for the processing fee (S8-N5 wants Delete-only) — matches the spec §14 documented current-build gap. Shot s11b-02. | FRESH VIU 2026-07-10: BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/. | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28526) — Edit+Remove -&gt; Remove-only (dev removed the dead Edit). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
@@ -10745,17 +10742,17 @@
       </c>
       <c r="N114" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O114" s="16" t="inlineStr">
         <is>
-          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P114" s="16" t="inlineStr">
         <is>
-          <t>Uses the spec's worked example directly. | VIU qb batch-1 (2026-07-08): Resolves LAST and re-resolves dynamically, BUT THE BASE IS WRONG (FDBUG-2): 3% pfee resolved $15.90 = 3% x $530.07 where $530.07 = (subtotal 292.83 + whole-WO fees 212) x 1.05 — the base INCLUDES whole-WO fees AND their tax. Spec §5-R4 excludes every whole-WO fee/discount: expected 3% x (292.83 + 14.64) = $9.22. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
+          <t>Uses the spec's worked example directly. | VIU qb batch-1 (2026-07-08): Resolves LAST and re-resolves dynamically, BUT THE BASE IS WRONG (FDBUG-2): 3% pfee resolved $15.90 = 3% x $530.07 where $530.07 = (subtotal 292.83 + whole-WO fees 212) x 1.05 — the base INCLUDES whole-WO fees AND their tax. Spec §5-R4 excludes every whole-WO fee/discount: expected 3% x (292.83 + 14.64) = $9.22. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them). | SV-8421 PF-BASE FIX CONFIRMED LIVE (2026-07-24 staging): with a 3% Processing fee on Grand Total present, adding a $100 taxable whole-WO fee left the PF UNCHANGED at $13.92 (=3% x net$442 x(1+GST5%)=464.10) while tax grew $22.80-&gt;$27.80 — PF base EXCLUDES the whole-WO fee and its tax. FDBUG-2 RESOLVED. VIU-Deviation -&gt; VIU-Verified. Evidence build/fees-discounts/sv8421-followups-2026-07-24/FINDINGS.md + evidence/api_PFbase_after_100_taxable_fee.json. | CLOSE-OUT 2026-07-24: also accepted per Ahtasham QA live review 2026-07-24 (no bug). Already flipped to VIU-Verified by our own live SV-8421 spot-check 2026-07-24 (this one WE verified live — see FINDINGS.md). No status change here.</t>
         </is>
       </c>
     </row>
@@ -15344,17 +15341,17 @@
       </c>
       <c r="N168" s="16" t="inlineStr">
         <is>
-          <t>VIU-Deviation</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="O168" s="16" t="inlineStr">
         <is>
-          <t>Same Processing Fee amount problem — the base wrongly includes the whole-work-order fees/discounts. A developer needs to fix it; re-test the amount once fixed.</t>
+          <t>No action needed — passed.</t>
         </is>
       </c>
       <c r="P168" s="16" t="inlineStr">
         <is>
-          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-2 structural defect stands (tax-independent); GST-rated number needs US-tax re-verify. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
+          <t>Design does not mock Processing Fee at all (design §9 item 3); it is template/admin-only. On a WO a Processing Fee is remove-only, no Edit (S8-R17); current build reportedly still shows a failing Edit control (requirements §14 item 6). | VIU qb batch-1 (2026-07-08): Processing fee resolves last and dynamically, BUT its Grand-Total base wrongly INCLUDES whole-WO fees/discounts and their tax (FDBUG-2): observed 3% x 530.07 = 15.90; spec-expected 3% x 307.47 = 9.22. | RECON 2026-07-09 (spec-v1-reconciliation.md + PO answer sheet): FDBUG-2 structural defect stands (tax-independent); GST-rated number needs US-tax re-verify. | FRESH VIU 2026-07-10: FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/. | SV-8421 PF-BASE FIX CONFIRMED LIVE (2026-07-24 staging): with a 3% Processing fee on Grand Total present, adding a $100 taxable whole-WO fee left the PF UNCHANGED at $13.92 (=3% x net$442 x(1+GST5%)=464.10) while tax grew $22.80-&gt;$27.80 — PF base EXCLUDES the whole-WO fee and its tax. FDBUG-2 RESOLVED. VIU-Deviation -&gt; VIU-Verified. Evidence build/fees-discounts/sv8421-followups-2026-07-24/FINDINGS.md + evidence/api_PFbase_after_100_taxable_fee.json. | CLOSE-OUT 2026-07-24: also accepted per Ahtasham QA live review 2026-07-24 (no bug). Already flipped to VIU-Verified by our own live SV-8421 spot-check 2026-07-24 (this one WE verified live — see FINDINGS.md). No status change here.</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19561,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Statistics tab lists each fee/discount as its own row with name, percent and amount</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -20428,7 +20425,7 @@
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the RIGHT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
